--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="130">
   <si>
     <t>Дата</t>
   </si>
@@ -53,45 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-02</t>
-  </si>
-  <si>
-    <t>2026-05-03</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-09</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
-  </si>
-  <si>
-    <t>2026-05-12</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
-    <t>2026-05-15</t>
   </si>
   <si>
     <t>В2852РК</t>
@@ -449,8 +410,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -536,11 +498,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -548,9 +511,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -904,20 +867,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46143</v>
       </c>
       <c r="B2">
         <v>1199</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F2">
         <v>59.362</v>
@@ -935,7 +898,7 @@
         <v>90.23</v>
       </c>
       <c r="K2" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -945,20 +908,20 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
+      <c r="A3" s="2">
+        <v>46144</v>
       </c>
       <c r="B3">
         <v>1199</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F3">
         <v>32.697</v>
@@ -976,7 +939,7 @@
         <v>49.7</v>
       </c>
       <c r="K3" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -986,20 +949,20 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>15</v>
+      <c r="A4" s="2">
+        <v>46145</v>
       </c>
       <c r="B4">
         <v>1158</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F4">
         <v>31.964</v>
@@ -1017,7 +980,7 @@
         <v>26.53</v>
       </c>
       <c r="K4" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1027,20 +990,20 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>15</v>
+      <c r="A5" s="2">
+        <v>46145</v>
       </c>
       <c r="B5">
         <v>1911</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="F5">
         <v>40.878</v>
@@ -1058,7 +1021,7 @@
         <v>83.8</v>
       </c>
       <c r="K5" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1068,20 +1031,20 @@
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>16</v>
+      <c r="A6" s="2">
+        <v>46146</v>
       </c>
       <c r="B6">
         <v>1148</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F6">
         <v>41.572</v>
@@ -1099,7 +1062,7 @@
         <v>63.19</v>
       </c>
       <c r="K6" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1109,20 +1072,20 @@
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>16</v>
+      <c r="A7" s="2">
+        <v>46146</v>
       </c>
       <c r="B7">
         <v>1148</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F7">
         <v>30.747</v>
@@ -1140,7 +1103,7 @@
         <v>25.52</v>
       </c>
       <c r="K7" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1150,20 +1113,20 @@
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>16</v>
+      <c r="A8" s="2">
+        <v>46146</v>
       </c>
       <c r="B8">
         <v>1158</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F8">
         <v>33</v>
@@ -1181,7 +1144,7 @@
         <v>50.16</v>
       </c>
       <c r="K8" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1191,20 +1154,20 @@
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>16</v>
+      <c r="A9" s="2">
+        <v>46146</v>
       </c>
       <c r="B9">
         <v>1158</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F9">
         <v>25</v>
@@ -1222,7 +1185,7 @@
         <v>38</v>
       </c>
       <c r="K9" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -1232,20 +1195,20 @@
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" t="s">
-        <v>17</v>
+      <c r="A10" s="2">
+        <v>46147</v>
       </c>
       <c r="B10">
         <v>1158</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F10">
         <v>32.217</v>
@@ -1263,7 +1226,7 @@
         <v>48.97</v>
       </c>
       <c r="K10" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1273,20 +1236,20 @@
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" t="s">
-        <v>17</v>
+      <c r="A11" s="2">
+        <v>46147</v>
       </c>
       <c r="B11">
         <v>1158</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F11">
         <v>31.349</v>
@@ -1304,7 +1267,7 @@
         <v>26.02</v>
       </c>
       <c r="K11" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1314,20 +1277,20 @@
       </c>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" t="s">
-        <v>17</v>
+      <c r="A12" s="2">
+        <v>46147</v>
       </c>
       <c r="B12">
         <v>1158</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F12">
         <v>37.013</v>
@@ -1345,7 +1308,7 @@
         <v>56.26</v>
       </c>
       <c r="K12" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1355,20 +1318,20 @@
       </c>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" t="s">
-        <v>17</v>
+      <c r="A13" s="2">
+        <v>46147</v>
       </c>
       <c r="B13">
         <v>1158</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F13">
         <v>33.157</v>
@@ -1386,7 +1349,7 @@
         <v>27.52</v>
       </c>
       <c r="K13" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1396,20 +1359,20 @@
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" t="s">
-        <v>17</v>
+      <c r="A14" s="2">
+        <v>46147</v>
       </c>
       <c r="B14">
         <v>1158</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="F14">
         <v>56.85</v>
@@ -1427,7 +1390,7 @@
         <v>102.33</v>
       </c>
       <c r="K14" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1437,20 +1400,20 @@
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" t="s">
-        <v>17</v>
+      <c r="A15" s="2">
+        <v>46147</v>
       </c>
       <c r="B15">
         <v>1158</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F15">
         <v>58.678</v>
@@ -1468,7 +1431,7 @@
         <v>89.19</v>
       </c>
       <c r="K15" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1478,20 +1441,20 @@
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" t="s">
-        <v>18</v>
+      <c r="A16" s="2">
+        <v>46149</v>
       </c>
       <c r="B16">
         <v>1146</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F16">
         <v>30.446</v>
@@ -1509,7 +1472,7 @@
         <v>25.27</v>
       </c>
       <c r="K16" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1519,20 +1482,20 @@
       </c>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" t="s">
-        <v>18</v>
+      <c r="A17" s="2">
+        <v>46149</v>
       </c>
       <c r="B17">
         <v>1158</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E17" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F17">
         <v>20.446</v>
@@ -1550,7 +1513,7 @@
         <v>16.97</v>
       </c>
       <c r="K17" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -1560,20 +1523,20 @@
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" t="s">
-        <v>18</v>
+      <c r="A18" s="2">
+        <v>46149</v>
       </c>
       <c r="B18">
         <v>1911</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E18" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F18">
         <v>31.916</v>
@@ -1591,7 +1554,7 @@
         <v>26.49</v>
       </c>
       <c r="K18" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -1601,20 +1564,20 @@
       </c>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" t="s">
-        <v>19</v>
+      <c r="A19" s="2">
+        <v>46150</v>
       </c>
       <c r="B19">
         <v>1147</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F19">
         <v>27.386</v>
@@ -1632,7 +1595,7 @@
         <v>22.73</v>
       </c>
       <c r="K19" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -1642,20 +1605,20 @@
       </c>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" t="s">
-        <v>19</v>
+      <c r="A20" s="2">
+        <v>46150</v>
       </c>
       <c r="B20">
         <v>1148</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E20" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="F20">
         <v>41.33</v>
@@ -1673,7 +1636,7 @@
         <v>73.98</v>
       </c>
       <c r="K20" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1683,20 +1646,20 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" t="s">
-        <v>19</v>
+      <c r="A21" s="2">
+        <v>46150</v>
       </c>
       <c r="B21">
         <v>1158</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="F21">
         <v>60.939</v>
@@ -1714,7 +1677,7 @@
         <v>109.08</v>
       </c>
       <c r="K21" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1724,20 +1687,20 @@
       </c>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" t="s">
-        <v>19</v>
+      <c r="A22" s="2">
+        <v>46150</v>
       </c>
       <c r="B22">
         <v>1158</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F22">
         <v>60</v>
@@ -1755,7 +1718,7 @@
         <v>91.8</v>
       </c>
       <c r="K22" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1765,20 +1728,20 @@
       </c>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" t="s">
-        <v>20</v>
+      <c r="A23" s="2">
+        <v>46151</v>
       </c>
       <c r="B23">
         <v>1911</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E23" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F23">
         <v>10</v>
@@ -1796,7 +1759,7 @@
         <v>15.4</v>
       </c>
       <c r="K23" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1806,20 +1769,20 @@
       </c>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" t="s">
-        <v>21</v>
+      <c r="A24" s="2">
+        <v>46153</v>
       </c>
       <c r="B24">
         <v>1147</v>
       </c>
       <c r="C24" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E24" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F24">
         <v>30</v>
@@ -1837,7 +1800,7 @@
         <v>24.9</v>
       </c>
       <c r="K24" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1847,20 +1810,20 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" t="s">
-        <v>21</v>
+      <c r="A25" s="2">
+        <v>46153</v>
       </c>
       <c r="B25">
         <v>1148</v>
       </c>
       <c r="C25" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E25" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F25">
         <v>25</v>
@@ -1878,7 +1841,7 @@
         <v>38.5</v>
       </c>
       <c r="K25" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1888,20 +1851,20 @@
       </c>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" t="s">
-        <v>21</v>
+      <c r="A26" s="2">
+        <v>46153</v>
       </c>
       <c r="B26">
         <v>1148</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E26" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="F26">
         <v>46.211</v>
@@ -1919,7 +1882,7 @@
         <v>94.27</v>
       </c>
       <c r="K26" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -1929,20 +1892,20 @@
       </c>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" t="s">
-        <v>21</v>
+      <c r="A27" s="2">
+        <v>46153</v>
       </c>
       <c r="B27">
         <v>1911</v>
       </c>
       <c r="C27" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E27" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="F27">
         <v>52.469</v>
@@ -1960,7 +1923,7 @@
         <v>93.92</v>
       </c>
       <c r="K27" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -1970,20 +1933,20 @@
       </c>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" t="s">
-        <v>22</v>
+      <c r="A28" s="2">
+        <v>46154</v>
       </c>
       <c r="B28">
         <v>1146</v>
       </c>
       <c r="C28" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E28" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F28">
         <v>10</v>
@@ -2001,7 +1964,7 @@
         <v>15.4</v>
       </c>
       <c r="K28" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -2011,20 +1974,20 @@
       </c>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" t="s">
-        <v>22</v>
+      <c r="A29" s="2">
+        <v>46154</v>
       </c>
       <c r="B29">
         <v>1146</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E29" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F29">
         <v>38.159</v>
@@ -2042,7 +2005,7 @@
         <v>31.29</v>
       </c>
       <c r="K29" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -2052,20 +2015,20 @@
       </c>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" t="s">
-        <v>22</v>
+      <c r="A30" s="2">
+        <v>46154</v>
       </c>
       <c r="B30">
         <v>1148</v>
       </c>
       <c r="C30" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D30" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E30" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F30">
         <v>35.72</v>
@@ -2083,7 +2046,7 @@
         <v>29.29</v>
       </c>
       <c r="K30" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -2093,20 +2056,20 @@
       </c>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" t="s">
-        <v>22</v>
+      <c r="A31" s="2">
+        <v>46154</v>
       </c>
       <c r="B31">
         <v>1148</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E31" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F31">
         <v>32.558</v>
@@ -2124,7 +2087,7 @@
         <v>50.14</v>
       </c>
       <c r="K31" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -2134,20 +2097,20 @@
       </c>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" t="s">
-        <v>22</v>
+      <c r="A32" s="2">
+        <v>46154</v>
       </c>
       <c r="B32">
         <v>1148</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D32" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E32" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F32">
         <v>25.512</v>
@@ -2165,7 +2128,7 @@
         <v>20.92</v>
       </c>
       <c r="K32" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -2175,20 +2138,20 @@
       </c>
     </row>
     <row r="33" spans="1:13">
-      <c r="A33" t="s">
-        <v>22</v>
+      <c r="A33" s="2">
+        <v>46154</v>
       </c>
       <c r="B33">
         <v>1158</v>
       </c>
       <c r="C33" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E33" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F33">
         <v>59.987</v>
@@ -2206,7 +2169,7 @@
         <v>92.38</v>
       </c>
       <c r="K33" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -2216,20 +2179,20 @@
       </c>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" t="s">
-        <v>22</v>
+      <c r="A34" s="2">
+        <v>46154</v>
       </c>
       <c r="B34">
         <v>1158</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D34" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="E34" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F34">
         <v>11.732</v>
@@ -2247,7 +2210,7 @@
         <v>9.619999999999999</v>
       </c>
       <c r="K34" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -2257,20 +2220,20 @@
       </c>
     </row>
     <row r="35" spans="1:13">
-      <c r="A35" t="s">
-        <v>22</v>
+      <c r="A35" s="2">
+        <v>46154</v>
       </c>
       <c r="B35">
         <v>1158</v>
       </c>
       <c r="C35" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D35" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F35">
         <v>19.244</v>
@@ -2288,7 +2251,7 @@
         <v>15.78</v>
       </c>
       <c r="K35" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -2298,20 +2261,20 @@
       </c>
     </row>
     <row r="36" spans="1:13">
-      <c r="A36" t="s">
-        <v>22</v>
+      <c r="A36" s="2">
+        <v>46154</v>
       </c>
       <c r="B36">
         <v>1158</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E36" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F36">
         <v>10</v>
@@ -2329,7 +2292,7 @@
         <v>15.4</v>
       </c>
       <c r="K36" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -2339,20 +2302,20 @@
       </c>
     </row>
     <row r="37" spans="1:13">
-      <c r="A37" t="s">
-        <v>22</v>
+      <c r="A37" s="2">
+        <v>46154</v>
       </c>
       <c r="B37">
         <v>1158</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D37" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E37" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F37">
         <v>25.143</v>
@@ -2370,7 +2333,7 @@
         <v>38.72</v>
       </c>
       <c r="K37" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -2380,20 +2343,20 @@
       </c>
     </row>
     <row r="38" spans="1:13">
-      <c r="A38" t="s">
-        <v>23</v>
+      <c r="A38" s="2">
+        <v>46155</v>
       </c>
       <c r="B38">
         <v>1148</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="E38" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F38">
         <v>30</v>
@@ -2411,7 +2374,7 @@
         <v>24.6</v>
       </c>
       <c r="K38" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -2421,20 +2384,20 @@
       </c>
     </row>
     <row r="39" spans="1:13">
-      <c r="A39" t="s">
-        <v>23</v>
+      <c r="A39" s="2">
+        <v>46155</v>
       </c>
       <c r="B39">
         <v>1148</v>
       </c>
       <c r="C39" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D39" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="E39" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F39">
         <v>10</v>
@@ -2452,7 +2415,7 @@
         <v>15.4</v>
       </c>
       <c r="K39" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -2462,20 +2425,20 @@
       </c>
     </row>
     <row r="40" spans="1:13">
-      <c r="A40" t="s">
-        <v>23</v>
+      <c r="A40" s="2">
+        <v>46155</v>
       </c>
       <c r="B40">
         <v>1148</v>
       </c>
       <c r="C40" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D40" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E40" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F40">
         <v>10</v>
@@ -2493,7 +2456,7 @@
         <v>15.4</v>
       </c>
       <c r="K40" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -2503,20 +2466,20 @@
       </c>
     </row>
     <row r="41" spans="1:13">
-      <c r="A41" t="s">
-        <v>23</v>
+      <c r="A41" s="2">
+        <v>46155</v>
       </c>
       <c r="B41">
         <v>1911</v>
       </c>
       <c r="C41" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D41" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E41" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F41">
         <v>33</v>
@@ -2534,7 +2497,7 @@
         <v>50.82</v>
       </c>
       <c r="K41" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2544,20 +2507,20 @@
       </c>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" t="s">
-        <v>24</v>
+      <c r="A42" s="2">
+        <v>46156</v>
       </c>
       <c r="B42">
         <v>1146</v>
       </c>
       <c r="C42" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D42" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E42" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F42">
         <v>27.815</v>
@@ -2575,7 +2538,7 @@
         <v>22.53</v>
       </c>
       <c r="K42" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2585,20 +2548,20 @@
       </c>
     </row>
     <row r="43" spans="1:13">
-      <c r="A43" t="s">
-        <v>24</v>
+      <c r="A43" s="2">
+        <v>46156</v>
       </c>
       <c r="B43">
         <v>1148</v>
       </c>
       <c r="C43" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E43" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F43">
         <v>30</v>
@@ -2616,7 +2579,7 @@
         <v>46.2</v>
       </c>
       <c r="K43" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -2626,20 +2589,20 @@
       </c>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" t="s">
-        <v>24</v>
+      <c r="A44" s="2">
+        <v>46156</v>
       </c>
       <c r="B44">
         <v>1148</v>
       </c>
       <c r="C44" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D44" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="E44" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F44">
         <v>19.407</v>
@@ -2657,7 +2620,7 @@
         <v>15.72</v>
       </c>
       <c r="K44" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2667,20 +2630,20 @@
       </c>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" t="s">
-        <v>24</v>
+      <c r="A45" s="2">
+        <v>46156</v>
       </c>
       <c r="B45">
         <v>1148</v>
       </c>
       <c r="C45" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D45" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="E45" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F45">
         <v>10</v>
@@ -2698,7 +2661,7 @@
         <v>15.4</v>
       </c>
       <c r="K45" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2708,20 +2671,20 @@
       </c>
     </row>
     <row r="46" spans="1:13">
-      <c r="A46" t="s">
-        <v>24</v>
+      <c r="A46" s="2">
+        <v>46156</v>
       </c>
       <c r="B46">
         <v>1158</v>
       </c>
       <c r="C46" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D46" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E46" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F46">
         <v>31.185</v>
@@ -2739,7 +2702,7 @@
         <v>25.26</v>
       </c>
       <c r="K46" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -2749,20 +2712,20 @@
       </c>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" t="s">
-        <v>25</v>
+      <c r="A47" s="2">
+        <v>46157</v>
       </c>
       <c r="B47">
         <v>1148</v>
       </c>
       <c r="C47" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D47" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E47" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F47">
         <v>25.013</v>
@@ -2780,7 +2743,7 @@
         <v>38.52</v>
       </c>
       <c r="K47" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -2790,20 +2753,20 @@
       </c>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" t="s">
-        <v>25</v>
+      <c r="A48" s="2">
+        <v>46157</v>
       </c>
       <c r="B48">
         <v>1148</v>
       </c>
       <c r="C48" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E48" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F48">
         <v>32.475</v>
@@ -2821,7 +2784,7 @@
         <v>25.98</v>
       </c>
       <c r="K48" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -2831,20 +2794,20 @@
       </c>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" t="s">
-        <v>25</v>
+      <c r="A49" s="2">
+        <v>46157</v>
       </c>
       <c r="B49">
         <v>1158</v>
       </c>
       <c r="C49" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E49" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F49">
         <v>59.987</v>
@@ -2862,7 +2825,7 @@
         <v>92.38</v>
       </c>
       <c r="K49" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -2872,20 +2835,20 @@
       </c>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" t="s">
-        <v>25</v>
+      <c r="A50" s="2">
+        <v>46157</v>
       </c>
       <c r="B50">
         <v>1158</v>
       </c>
       <c r="C50" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="E50" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F50">
         <v>34.763</v>
@@ -2903,7 +2866,7 @@
         <v>27.81</v>
       </c>
       <c r="K50" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -2913,20 +2876,20 @@
       </c>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" t="s">
-        <v>25</v>
+      <c r="A51" s="2">
+        <v>46157</v>
       </c>
       <c r="B51">
         <v>1908</v>
       </c>
       <c r="C51" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D51" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E51" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F51">
         <v>25.5</v>
@@ -2944,7 +2907,7 @@
         <v>20.4</v>
       </c>
       <c r="K51" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -2954,172 +2917,172 @@
       </c>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
+      <c r="A54" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>141</v>
+      <c r="A55" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B56" s="5">
+      <c r="A56" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56" s="6">
         <v>730.227</v>
       </c>
-      <c r="C56" s="5">
+      <c r="C56" s="6">
         <v>23</v>
       </c>
-      <c r="D56" s="5">
+      <c r="D56" s="6">
         <v>1.5004</v>
       </c>
-      <c r="E56" s="5">
+      <c r="E56" s="6">
         <v>1095.65</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F56" s="6">
         <v>1117.56</v>
       </c>
-      <c r="G56" s="5">
+      <c r="G56" s="6">
         <v>21.91</v>
       </c>
     </row>
     <row r="57" spans="1:13">
-      <c r="A57" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B57" s="5">
+      <c r="A57" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B57" s="6">
         <v>598.923</v>
       </c>
-      <c r="C57" s="5">
+      <c r="C57" s="6">
         <v>21</v>
       </c>
-      <c r="D57" s="5">
+      <c r="D57" s="6">
         <v>0.8101</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="6">
         <v>485.17</v>
       </c>
-      <c r="F57" s="5">
+      <c r="F57" s="6">
         <v>491.15</v>
       </c>
-      <c r="G57" s="5">
+      <c r="G57" s="6">
         <v>5.98</v>
       </c>
     </row>
     <row r="58" spans="1:13">
-      <c r="A58" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B58" s="5">
+      <c r="A58" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B58" s="6">
         <v>159.119</v>
       </c>
-      <c r="C58" s="5">
+      <c r="C58" s="6">
         <v>3</v>
       </c>
-      <c r="D58" s="5">
+      <c r="D58" s="6">
         <v>1.7635</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="6">
         <v>280.61</v>
       </c>
-      <c r="F58" s="5">
+      <c r="F58" s="6">
         <v>285.39</v>
       </c>
-      <c r="G58" s="5">
+      <c r="G58" s="6">
         <v>4.78</v>
       </c>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B59" s="5">
+      <c r="A59" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="6">
         <v>87.089</v>
       </c>
-      <c r="C59" s="5">
+      <c r="C59" s="6">
         <v>2</v>
       </c>
-      <c r="D59" s="5">
+      <c r="D59" s="6">
         <v>2.0447</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59" s="6">
         <v>178.07</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F59" s="6">
         <v>178.07</v>
       </c>
-      <c r="G59" s="5">
+      <c r="G59" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B60" s="5">
+      <c r="A60" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B60" s="6">
         <v>52.469</v>
       </c>
-      <c r="C60" s="5">
+      <c r="C60" s="6">
         <v>1</v>
       </c>
-      <c r="D60" s="5">
+      <c r="D60" s="6">
         <v>1.75</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="6">
         <v>91.81999999999999</v>
       </c>
-      <c r="F60" s="5">
+      <c r="F60" s="6">
         <v>93.92</v>
       </c>
-      <c r="G60" s="5">
+      <c r="G60" s="6">
         <v>2.1</v>
       </c>
     </row>
     <row r="61" spans="1:13">
-      <c r="A61" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B61" s="7">
+      <c r="A61" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B61" s="8">
         <v>1627.827</v>
       </c>
-      <c r="C61" s="7">
+      <c r="C61" s="8">
         <v>50</v>
       </c>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7">
+      <c r="D61" s="8"/>
+      <c r="E61" s="8">
         <v>2131.32</v>
       </c>
-      <c r="F61" s="7">
+      <c r="F61" s="8">
         <v>2166.09</v>
       </c>
-      <c r="G61" s="7">
+      <c r="G61" s="8">
         <v>34.77</v>
       </c>
     </row>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
@@ -500,7 +500,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -510,12 +510,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,17 +560,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="139">
   <si>
     <t>Дата</t>
   </si>
@@ -46,16 +46,22 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Чайка</t>
   </si>
   <si>
     <t>Варна Порт</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>Варна Цар Освободител</t>
   </si>
   <si>
     <t>Варна Сливница</t>
@@ -64,6 +70,9 @@
     <t>Варна Варненчик</t>
   </si>
   <si>
+    <t>Варна Евkсиноград</t>
+  </si>
+  <si>
     <t>Ахелой</t>
   </si>
   <si>
@@ -259,7 +268,151 @@
     <t>EKO RACING 100</t>
   </si>
   <si>
-    <t>DIESEL DOUBLE FILTERED</t>
+    <t>DIESEL DOUBLE FILTER</t>
+  </si>
+  <si>
+    <t>11:06</t>
+  </si>
+  <si>
+    <t>08:46</t>
+  </si>
+  <si>
+    <t>10:22</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>14:17</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>09:16</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:16</t>
+  </si>
+  <si>
+    <t>11:26</t>
+  </si>
+  <si>
+    <t>11:28</t>
+  </si>
+  <si>
+    <t>13:17</t>
+  </si>
+  <si>
+    <t>13:43</t>
+  </si>
+  <si>
+    <t>14:22</t>
+  </si>
+  <si>
+    <t>16:49</t>
+  </si>
+  <si>
+    <t>18:16</t>
+  </si>
+  <si>
+    <t>13:14</t>
+  </si>
+  <si>
+    <t>10:53</t>
+  </si>
+  <si>
+    <t>11:42</t>
+  </si>
+  <si>
+    <t>12:49</t>
+  </si>
+  <si>
+    <t>16:18</t>
+  </si>
+  <si>
+    <t>17:26</t>
+  </si>
+  <si>
+    <t>09:39</t>
+  </si>
+  <si>
+    <t>09:33</t>
+  </si>
+  <si>
+    <t>10:48</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>14:46</t>
+  </si>
+  <si>
+    <t>15:22</t>
+  </si>
+  <si>
+    <t>16:04</t>
+  </si>
+  <si>
+    <t>08:53</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:02</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>12:41</t>
+  </si>
+  <si>
+    <t>15:06</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>16:06</t>
+  </si>
+  <si>
+    <t>11:13</t>
+  </si>
+  <si>
+    <t>16:02</t>
+  </si>
+  <si>
+    <t>16:24</t>
+  </si>
+  <si>
+    <t>17:16</t>
+  </si>
+  <si>
+    <t>11:27</t>
+  </si>
+  <si>
+    <t>06:19</t>
+  </si>
+  <si>
+    <t>08:29</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>15:07</t>
+  </si>
+  <si>
+    <t>15:18</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА % 1 - АВТОПАРК</t>
@@ -679,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -692,10 +845,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -729,22 +884,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46174</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F2">
         <v>34.86</v>
@@ -761,25 +922,31 @@
       <c r="J2">
         <v>26.84</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2">
         <v>76403</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>105833</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46175</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F3">
         <v>25</v>
@@ -796,25 +963,31 @@
       <c r="J3">
         <v>39.25</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>213794</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46175</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F4">
         <v>37.94</v>
@@ -831,25 +1004,31 @@
       <c r="J4">
         <v>29.21</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>271795</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46175</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F5">
         <v>32.87</v>
@@ -866,25 +1045,31 @@
       <c r="J5">
         <v>24.65</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>88</v>
+      </c>
+      <c r="L5">
         <v>41600</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="M5">
+        <v>213896</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46175</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F6">
         <v>27.89</v>
@@ -901,25 +1086,31 @@
       <c r="J6">
         <v>20.92</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="s">
+        <v>89</v>
+      </c>
+      <c r="L6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="M6">
+        <v>137798</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46175</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F7">
         <v>55.06</v>
@@ -936,25 +1127,31 @@
       <c r="J7">
         <v>86.44</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="s">
+        <v>90</v>
+      </c>
+      <c r="L7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="M7">
+        <v>106573</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46176</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F8">
         <v>27.29</v>
@@ -971,25 +1168,31 @@
       <c r="J8">
         <v>42.85</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="M8">
+        <v>214222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="3">
         <v>46176</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F9">
         <v>28.46</v>
@@ -1006,25 +1209,31 @@
       <c r="J9">
         <v>21.06</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="s">
+        <v>92</v>
+      </c>
+      <c r="L9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="M9">
+        <v>192214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="3">
         <v>46176</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F10">
         <v>10</v>
@@ -1041,25 +1250,31 @@
       <c r="J10">
         <v>15.7</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="s">
+        <v>93</v>
+      </c>
+      <c r="L10">
         <v>50330</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="M10">
+        <v>214305</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="3">
         <v>46176</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F11">
         <v>20.05</v>
@@ -1076,25 +1291,31 @@
       <c r="J11">
         <v>14.84</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="s">
+        <v>94</v>
+      </c>
+      <c r="L11">
         <v>50330</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="M11">
+        <v>214318</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="3">
         <v>46176</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F12">
         <v>29.6</v>
@@ -1111,25 +1332,31 @@
       <c r="J12">
         <v>21.9</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="s">
+        <v>95</v>
+      </c>
+      <c r="L12">
         <v>38055</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="M12">
+        <v>138058</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="3">
         <v>46176</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F13">
         <v>10</v>
@@ -1146,25 +1373,31 @@
       <c r="J13">
         <v>15.7</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="s">
+        <v>95</v>
+      </c>
+      <c r="L13">
         <v>38055</v>
       </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="M13">
+        <v>138058</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="3">
         <v>46176</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F14">
         <v>53.92</v>
@@ -1181,25 +1414,31 @@
       <c r="J14">
         <v>91.12</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="s">
+        <v>96</v>
+      </c>
+      <c r="L14">
         <v>494787</v>
       </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="M14">
+        <v>106975</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="3">
         <v>46176</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F15">
         <v>54.98</v>
@@ -1216,25 +1455,31 @@
       <c r="J15">
         <v>92.92</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="s">
+        <v>97</v>
+      </c>
+      <c r="L15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="M15">
+        <v>107002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="3">
         <v>46176</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F16">
         <v>16.62</v>
@@ -1251,25 +1496,31 @@
       <c r="J16">
         <v>26.09</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="s">
+        <v>98</v>
+      </c>
+      <c r="L16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="M16">
+        <v>107026</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="3">
         <v>46176</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F17">
         <v>35</v>
@@ -1286,25 +1537,31 @@
       <c r="J17">
         <v>54.95</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="s">
+        <v>99</v>
+      </c>
+      <c r="L17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="M17">
+        <v>107095</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="3">
         <v>46176</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E18" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F18">
         <v>47.47</v>
@@ -1321,25 +1578,31 @@
       <c r="J18">
         <v>86.40000000000001</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="s">
+        <v>100</v>
+      </c>
+      <c r="L18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="M18">
+        <v>113102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="3">
         <v>46177</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F19">
         <v>36</v>
@@ -1356,25 +1619,31 @@
       <c r="J19">
         <v>56.52</v>
       </c>
-      <c r="K19">
+      <c r="K19" t="s">
+        <v>101</v>
+      </c>
+      <c r="L19">
         <v>475900</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="M19">
+        <v>107483</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="3">
         <v>46178</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E20" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F20">
         <v>32.38</v>
@@ -1391,25 +1660,31 @@
       <c r="J20">
         <v>50.84</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="s">
+        <v>102</v>
+      </c>
+      <c r="L20">
         <v>52410</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="M20">
+        <v>107936</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="3">
         <v>46178</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D21" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E21" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F21">
         <v>27.92</v>
@@ -1426,25 +1701,31 @@
       <c r="J21">
         <v>20.66</v>
       </c>
-      <c r="K21">
+      <c r="K21" t="s">
+        <v>103</v>
+      </c>
+      <c r="L21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="M21">
+        <v>215172</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="3">
         <v>46178</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E22" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F22">
         <v>25</v>
@@ -1461,25 +1742,31 @@
       <c r="J22">
         <v>39.25</v>
       </c>
-      <c r="K22">
+      <c r="K22" t="s">
+        <v>104</v>
+      </c>
+      <c r="L22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="M22">
+        <v>108018</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="3">
         <v>46178</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E23" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F23">
         <v>30.27</v>
@@ -1496,25 +1783,31 @@
       <c r="J23">
         <v>22.4</v>
       </c>
-      <c r="K23">
+      <c r="K23" t="s">
+        <v>105</v>
+      </c>
+      <c r="L23">
         <v>97120</v>
       </c>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="M23">
+        <v>139009</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="3">
         <v>46178</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F24">
         <v>59</v>
@@ -1531,34 +1824,40 @@
       <c r="J24">
         <v>92.63</v>
       </c>
-      <c r="K24">
+      <c r="K24" t="s">
+        <v>106</v>
+      </c>
+      <c r="L24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="M24">
+        <v>272859</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="3">
         <v>46181</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E25" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F25">
         <v>42.86</v>
       </c>
       <c r="G25" s="1">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="H25">
-        <v>79.72</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="I25" s="1">
         <v>1.89</v>
@@ -1566,25 +1865,31 @@
       <c r="J25">
         <v>81.01000000000001</v>
       </c>
-      <c r="K25">
+      <c r="K25" t="s">
+        <v>107</v>
+      </c>
+      <c r="L25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="M25">
+        <v>216224</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="3">
         <v>46182</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E26" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F26">
         <v>20</v>
@@ -1601,25 +1906,31 @@
       <c r="J26">
         <v>31.2</v>
       </c>
-      <c r="K26">
+      <c r="K26" t="s">
+        <v>108</v>
+      </c>
+      <c r="L26">
         <v>256360</v>
       </c>
-    </row>
-    <row r="27" spans="1:11">
+      <c r="M26">
+        <v>216647</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="3">
         <v>46182</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E27" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F27">
         <v>38.06</v>
@@ -1636,25 +1947,31 @@
       <c r="J27">
         <v>27.4</v>
       </c>
-      <c r="K27">
+      <c r="K27" t="s">
+        <v>101</v>
+      </c>
+      <c r="L27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:11">
+      <c r="M27">
+        <v>216809</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="3">
         <v>46183</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E28" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F28">
         <v>30.21</v>
@@ -1671,25 +1988,31 @@
       <c r="J28">
         <v>47.13</v>
       </c>
-      <c r="K28">
+      <c r="K28" t="s">
+        <v>109</v>
+      </c>
+      <c r="L28">
         <v>40666</v>
       </c>
-    </row>
-    <row r="29" spans="1:11">
+      <c r="M28">
+        <v>217157</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="3">
         <v>46183</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E29" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F29">
         <v>20</v>
@@ -1706,25 +2029,31 @@
       <c r="J29">
         <v>14.2</v>
       </c>
-      <c r="K29">
+      <c r="K29" t="s">
+        <v>110</v>
+      </c>
+      <c r="L29">
         <v>5500</v>
       </c>
-    </row>
-    <row r="30" spans="1:11">
+      <c r="M29">
+        <v>217171</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="3">
         <v>46183</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D30" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F30">
         <v>59.85</v>
@@ -1741,25 +2070,31 @@
       <c r="J30">
         <v>97.56</v>
       </c>
-      <c r="K30">
+      <c r="K30" t="s">
+        <v>98</v>
+      </c>
+      <c r="L30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="M30">
+        <v>274100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="3">
         <v>46183</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E31" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F31">
         <v>32.17</v>
@@ -1776,25 +2111,31 @@
       <c r="J31">
         <v>22.84</v>
       </c>
-      <c r="K31">
+      <c r="K31" t="s">
+        <v>111</v>
+      </c>
+      <c r="L31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="M31">
+        <v>110805</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="3">
         <v>46183</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E32" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F32">
         <v>91.16</v>
@@ -1811,25 +2152,31 @@
       <c r="J32">
         <v>165</v>
       </c>
-      <c r="K32">
+      <c r="K32" t="s">
+        <v>112</v>
+      </c>
+      <c r="L32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="M32">
+        <v>217362</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="3">
         <v>46183</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E33" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F33">
         <v>29.16</v>
@@ -1846,25 +2193,31 @@
       <c r="J33">
         <v>20.7</v>
       </c>
-      <c r="K33">
+      <c r="K33" t="s">
+        <v>113</v>
+      </c>
+      <c r="L33">
         <v>36160</v>
       </c>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="M33">
+        <v>110840</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="3">
         <v>46184</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D34" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E34" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F34">
         <v>29.87</v>
@@ -1881,25 +2234,31 @@
       <c r="J34">
         <v>20.61</v>
       </c>
-      <c r="K34">
+      <c r="K34" t="s">
+        <v>114</v>
+      </c>
+      <c r="L34">
         <v>42102</v>
       </c>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="M34">
+        <v>217630</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="3">
         <v>46184</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D35" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E35" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F35">
         <v>33.7</v>
@@ -1916,25 +2275,31 @@
       <c r="J35">
         <v>23.25</v>
       </c>
-      <c r="K35">
+      <c r="K35" t="s">
+        <v>115</v>
+      </c>
+      <c r="L35">
         <v>68896</v>
       </c>
-    </row>
-    <row r="36" spans="1:11">
+      <c r="M35">
+        <v>111172</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="3">
         <v>46184</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D36" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E36" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F36">
         <v>10</v>
@@ -1951,25 +2316,31 @@
       <c r="J36">
         <v>15.6</v>
       </c>
-      <c r="K36">
+      <c r="K36" t="s">
+        <v>116</v>
+      </c>
+      <c r="L36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:11">
+      <c r="M36">
+        <v>217685</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="3">
         <v>46184</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D37" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E37" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F37">
         <v>41.69</v>
@@ -1986,25 +2357,31 @@
       <c r="J37">
         <v>65.04000000000001</v>
       </c>
-      <c r="K37">
+      <c r="K37" t="s">
+        <v>117</v>
+      </c>
+      <c r="L37">
         <v>332666</v>
       </c>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="M37">
+        <v>194790</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="3">
         <v>46184</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D38" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E38" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F38">
         <v>10</v>
@@ -2021,25 +2398,31 @@
       <c r="J38">
         <v>15.6</v>
       </c>
-      <c r="K38">
+      <c r="K38" t="s">
+        <v>110</v>
+      </c>
+      <c r="L38">
         <v>97420</v>
       </c>
-    </row>
-    <row r="39" spans="1:11">
+      <c r="M38">
+        <v>140900</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="3">
         <v>46184</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E39" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F39">
         <v>33.8</v>
@@ -2056,25 +2439,31 @@
       <c r="J39">
         <v>23.32</v>
       </c>
-      <c r="K39">
+      <c r="K39" t="s">
+        <v>110</v>
+      </c>
+      <c r="L39">
         <v>97420</v>
       </c>
-    </row>
-    <row r="40" spans="1:11">
+      <c r="M39">
+        <v>140900</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="3">
         <v>46184</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E40" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F40">
         <v>17.14</v>
@@ -2091,25 +2480,31 @@
       <c r="J40">
         <v>26.74</v>
       </c>
-      <c r="K40">
+      <c r="K40" t="s">
+        <v>118</v>
+      </c>
+      <c r="L40">
         <v>256435</v>
       </c>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="M40">
+        <v>115456</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="3">
         <v>46184</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D41" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E41" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F41">
         <v>30.28</v>
@@ -2126,25 +2521,31 @@
       <c r="J41">
         <v>20.89</v>
       </c>
-      <c r="K41">
+      <c r="K41" t="s">
+        <v>119</v>
+      </c>
+      <c r="L41">
         <v>61999</v>
       </c>
-    </row>
-    <row r="42" spans="1:11">
+      <c r="M41">
+        <v>217738</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="3">
         <v>46184</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D42" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E42" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F42">
         <v>27.29</v>
@@ -2161,25 +2562,31 @@
       <c r="J42">
         <v>18.83</v>
       </c>
-      <c r="K42">
+      <c r="K42" t="s">
+        <v>120</v>
+      </c>
+      <c r="L42">
         <v>23200</v>
       </c>
-    </row>
-    <row r="43" spans="1:11">
+      <c r="M42">
+        <v>141054</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="3">
         <v>46184</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D43" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E43" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F43">
         <v>10.83</v>
@@ -2196,25 +2603,31 @@
       <c r="J43">
         <v>17.54</v>
       </c>
-      <c r="K43">
+      <c r="K43" t="s">
+        <v>121</v>
+      </c>
+      <c r="L43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:11">
+      <c r="M43">
+        <v>194911</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="3">
         <v>46184</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E44" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F44">
         <v>29.09</v>
@@ -2231,25 +2644,31 @@
       <c r="J44">
         <v>20.07</v>
       </c>
-      <c r="K44">
+      <c r="K44" t="s">
+        <v>122</v>
+      </c>
+      <c r="L44">
         <v>76690</v>
       </c>
-    </row>
-    <row r="45" spans="1:11">
+      <c r="M44">
+        <v>274440</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="3">
         <v>46185</v>
       </c>
       <c r="B45" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D45" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E45" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F45">
         <v>20.25</v>
@@ -2266,25 +2685,31 @@
       <c r="J45">
         <v>31.59</v>
       </c>
-      <c r="K45">
+      <c r="K45" t="s">
+        <v>123</v>
+      </c>
+      <c r="L45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:11">
+      <c r="M45">
+        <v>141306</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="3">
         <v>46185</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E46" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F46">
         <v>32.41</v>
@@ -2301,25 +2726,31 @@
       <c r="J46">
         <v>50.56</v>
       </c>
-      <c r="K46">
+      <c r="K46" t="s">
+        <v>124</v>
+      </c>
+      <c r="L46">
         <v>52905</v>
       </c>
-    </row>
-    <row r="47" spans="1:11">
+      <c r="M46">
+        <v>111963</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="3">
         <v>46185</v>
       </c>
       <c r="B47" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D47" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E47" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F47">
         <v>61.91</v>
@@ -2336,25 +2767,31 @@
       <c r="J47">
         <v>99.68000000000001</v>
       </c>
-      <c r="K47">
+      <c r="K47" t="s">
+        <v>125</v>
+      </c>
+      <c r="L47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:11">
+      <c r="M47">
+        <v>141492</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="3">
         <v>46185</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E48" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F48">
         <v>60</v>
@@ -2371,25 +2808,31 @@
       <c r="J48">
         <v>93.59999999999999</v>
       </c>
-      <c r="K48">
+      <c r="K48" t="s">
+        <v>126</v>
+      </c>
+      <c r="L48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:11">
+      <c r="M48">
+        <v>112023</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="3">
         <v>46187</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C49" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E49" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F49">
         <v>27.78</v>
@@ -2406,25 +2849,31 @@
       <c r="J49">
         <v>18.89</v>
       </c>
-      <c r="K49">
+      <c r="K49" t="s">
+        <v>127</v>
+      </c>
+      <c r="L49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:11">
+      <c r="M49">
+        <v>275125</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="3">
         <v>46188</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D50" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E50" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F50">
         <v>14.54</v>
@@ -2441,25 +2890,31 @@
       <c r="J50">
         <v>26.32</v>
       </c>
-      <c r="K50">
+      <c r="K50" t="s">
+        <v>128</v>
+      </c>
+      <c r="L50">
         <v>315041</v>
       </c>
-    </row>
-    <row r="51" spans="1:11">
+      <c r="M50">
+        <v>219145</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="3">
         <v>46188</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C51" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D51" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E51" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F51">
         <v>25</v>
@@ -2476,25 +2931,31 @@
       <c r="J51">
         <v>39</v>
       </c>
-      <c r="K51">
+      <c r="K51" t="s">
+        <v>129</v>
+      </c>
+      <c r="L51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:11">
+      <c r="M51">
+        <v>219187</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="3">
         <v>46188</v>
       </c>
       <c r="B52" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C52" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D52" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E52" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F52">
         <v>34</v>
@@ -2511,25 +2972,31 @@
       <c r="J52">
         <v>53.04</v>
       </c>
-      <c r="K52">
+      <c r="K52" t="s">
+        <v>130</v>
+      </c>
+      <c r="L52">
         <v>476140</v>
       </c>
-    </row>
-    <row r="53" spans="1:11">
+      <c r="M52">
+        <v>219250</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="3">
         <v>46188</v>
       </c>
       <c r="B53" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C53" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D53" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E53" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F53">
         <v>40.16</v>
@@ -2546,25 +3013,31 @@
       <c r="J53">
         <v>62.65</v>
       </c>
-      <c r="K53">
+      <c r="K53" t="s">
+        <v>131</v>
+      </c>
+      <c r="L53">
         <v>315163</v>
       </c>
-    </row>
-    <row r="54" spans="1:11">
+      <c r="M53">
+        <v>90187</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="3">
         <v>46188</v>
       </c>
       <c r="B54" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D54" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E54" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F54">
         <v>27</v>
@@ -2581,13 +3054,19 @@
       <c r="J54">
         <v>42.12</v>
       </c>
-      <c r="K54">
+      <c r="K54" t="s">
+        <v>132</v>
+      </c>
+      <c r="L54">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:11">
+      <c r="M54">
+        <v>113468</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" s="4" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -2595,18 +3074,18 @@
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:13">
       <c r="A58" s="5" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>84</v>
+        <v>135</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>85</v>
+        <v>136</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>7</v>
@@ -2615,9 +3094,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:13">
       <c r="A59" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B59" s="7">
         <v>699.21</v>
@@ -2635,9 +3114,9 @@
         <v>1094.09</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:13">
       <c r="A60" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B60" s="7">
         <v>601.0599999999999</v>
@@ -2655,9 +3134,9 @@
         <v>433.48</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:13">
       <c r="A61" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B61" s="7">
         <v>241.49</v>
@@ -2675,9 +3154,9 @@
         <v>398.82</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:13">
       <c r="A62" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B62" s="7">
         <v>153.17</v>
@@ -2695,9 +3174,9 @@
         <v>277.72</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:13">
       <c r="A63" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B63" s="7">
         <v>42.86</v>
@@ -2706,18 +3185,18 @@
         <v>1</v>
       </c>
       <c r="D63" s="8">
-        <v>1.86</v>
+        <v>1.8901</v>
       </c>
       <c r="E63" s="7">
-        <v>79.72</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="F63" s="7">
         <v>81.01000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:13">
       <c r="A64" s="9" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="B64" s="10">
         <v>1737.79</v>
@@ -2727,7 +3206,7 @@
       </c>
       <c r="D64" s="8"/>
       <c r="E64" s="10">
-        <v>2243.48</v>
+        <v>2244.77</v>
       </c>
       <c r="F64" s="10">
         <v>2285.12</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="209">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,72 +52,81 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Радиново</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Тракия</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>АМ Тракия</t>
-  </si>
-  <si>
-    <t>Казанлък</t>
-  </si>
-  <si>
-    <t>Ихтиман</t>
-  </si>
-  <si>
-    <t>Тракия Езеро</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1120 Пловдив Радиново</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1157 Пловдив Тракия</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1925 HW Trakia, 243 km. Sofia direc</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1193 Казанлък</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
+    <t>В1977ВМ</t>
   </si>
   <si>
     <t>В7721ВВ</t>
   </si>
   <si>
-    <t>В1977ВМ</t>
+    <t>В7242ВР</t>
   </si>
   <si>
     <t>В0592ВТ</t>
   </si>
   <si>
-    <t>В7242ВР</t>
-  </si>
-  <si>
     <t>В4814КВ</t>
   </si>
   <si>
     <t>СлужебнаОВ1</t>
   </si>
   <si>
+    <t>В8974ВР</t>
+  </si>
+  <si>
+    <t>В8985ВР</t>
+  </si>
+  <si>
+    <t>В7230ВР</t>
+  </si>
+  <si>
     <t>В2852РК</t>
   </si>
   <si>
-    <t>В7230ВР</t>
-  </si>
-  <si>
     <t>В8979ВР</t>
   </si>
   <si>
-    <t>В8974ВР</t>
-  </si>
-  <si>
-    <t>В8985ВР</t>
-  </si>
-  <si>
     <t>В8978ВР</t>
   </si>
   <si>
@@ -127,18 +139,21 @@
     <t>В7224ВР</t>
   </si>
   <si>
+    <t>В7233ВР</t>
+  </si>
+  <si>
+    <t>В6565КМ</t>
+  </si>
+  <si>
     <t>В7236ВР</t>
   </si>
   <si>
-    <t>В7233ВР</t>
-  </si>
-  <si>
-    <t>В6565КМ</t>
-  </si>
-  <si>
     <t>В8853ХК</t>
   </si>
   <si>
+    <t>В7106НН</t>
+  </si>
+  <si>
     <t>В6633СН</t>
   </si>
   <si>
@@ -148,45 +163,66 @@
     <t>В0591ВТ</t>
   </si>
   <si>
-    <t>В7106НН</t>
-  </si>
-  <si>
     <t>В9347РН</t>
   </si>
   <si>
+    <t>В4582РР</t>
+  </si>
+  <si>
+    <t>В9337НК</t>
+  </si>
+  <si>
+    <t>В1422РХ</t>
+  </si>
+  <si>
+    <t>В5987РР</t>
+  </si>
+  <si>
+    <t>В6511КС</t>
+  </si>
+  <si>
+    <t>В2802ТХ</t>
+  </si>
+  <si>
+    <t>В1392РК</t>
+  </si>
+  <si>
+    <t>В0595ВТ</t>
+  </si>
+  <si>
+    <t>78970155027722721</t>
+  </si>
+  <si>
     <t>78970155027721632</t>
   </si>
   <si>
-    <t>78970155027722721</t>
+    <t>78970155027721616</t>
   </si>
   <si>
     <t>78970155027722622</t>
   </si>
   <si>
-    <t>78970155027721616</t>
-  </si>
-  <si>
     <t>78970155027721483</t>
   </si>
   <si>
     <t>78970155027721764</t>
   </si>
   <si>
+    <t>78970155027721665</t>
+  </si>
+  <si>
+    <t>78970155027721715</t>
+  </si>
+  <si>
+    <t>78970155027721574</t>
+  </si>
+  <si>
     <t>78970155027721442</t>
   </si>
   <si>
-    <t>78970155027721574</t>
-  </si>
-  <si>
     <t>78970155027721707</t>
   </si>
   <si>
-    <t>78970155027721665</t>
-  </si>
-  <si>
-    <t>78970155027721715</t>
-  </si>
-  <si>
     <t>78970155027721699</t>
   </si>
   <si>
@@ -199,18 +235,21 @@
     <t>78970155027721566</t>
   </si>
   <si>
+    <t>78970155027721582</t>
+  </si>
+  <si>
+    <t>78970155027721533</t>
+  </si>
+  <si>
     <t>78970155027721608</t>
   </si>
   <si>
-    <t>78970155027721582</t>
-  </si>
-  <si>
-    <t>78970155027721533</t>
-  </si>
-  <si>
     <t>78970155027721749</t>
   </si>
   <si>
+    <t>78970155027721558</t>
+  </si>
+  <si>
     <t>78970155027721541</t>
   </si>
   <si>
@@ -220,133 +259,370 @@
     <t>78970155027722614</t>
   </si>
   <si>
-    <t>78970155027721558</t>
-  </si>
-  <si>
     <t>78970155027721731</t>
   </si>
   <si>
+    <t>78970155027721475</t>
+  </si>
+  <si>
+    <t>78970155027721723</t>
+  </si>
+  <si>
+    <t>78970155027722697</t>
+  </si>
+  <si>
+    <t>78970155027721491</t>
+  </si>
+  <si>
+    <t>78970155027721517</t>
+  </si>
+  <si>
+    <t>78970155027721434</t>
+  </si>
+  <si>
+    <t>78970155027722739</t>
+  </si>
+  <si>
+    <t>78970155027722648</t>
+  </si>
+  <si>
+    <t>EKO RACING 100</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>EKO RACING 100</t>
-  </si>
-  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-06-16 10:41:59</t>
-  </si>
-  <si>
-    <t>2026-06-16 11:09:56</t>
-  </si>
-  <si>
-    <t>2026-06-16 14:06:44</t>
-  </si>
-  <si>
-    <t>2026-06-16 14:23:57</t>
-  </si>
-  <si>
-    <t>2026-06-16 15:30:29</t>
-  </si>
-  <si>
-    <t>2026-06-17 12:13:44</t>
-  </si>
-  <si>
-    <t>2026-06-18 08:05:56</t>
-  </si>
-  <si>
-    <t>2026-06-18 09:10:19</t>
-  </si>
-  <si>
-    <t>2026-06-18 11:23:01</t>
-  </si>
-  <si>
-    <t>2026-06-18 11:38:13</t>
-  </si>
-  <si>
-    <t>2026-06-18 14:43:06</t>
-  </si>
-  <si>
-    <t>2026-06-18 15:03:48</t>
-  </si>
-  <si>
-    <t>2026-06-19 10:24:19</t>
-  </si>
-  <si>
-    <t>2026-06-19 11:03:06</t>
-  </si>
-  <si>
-    <t>2026-06-19 15:51:56</t>
-  </si>
-  <si>
-    <t>2026-06-20 12:20:12</t>
-  </si>
-  <si>
-    <t>2026-06-22 09:42:30</t>
-  </si>
-  <si>
-    <t>2026-06-22 09:51:31</t>
-  </si>
-  <si>
-    <t>2026-06-22 14:09:14</t>
-  </si>
-  <si>
-    <t>2026-06-23 09:32:26</t>
-  </si>
-  <si>
-    <t>2026-06-23 11:23:21</t>
-  </si>
-  <si>
-    <t>2026-06-23 14:35:04</t>
-  </si>
-  <si>
-    <t>2026-06-23 15:54:12</t>
-  </si>
-  <si>
-    <t>2026-06-23 18:34:38</t>
-  </si>
-  <si>
-    <t>2026-06-24 10:16:06</t>
-  </si>
-  <si>
-    <t>2026-06-24 11:08:37</t>
-  </si>
-  <si>
-    <t>2026-06-24 11:54:32</t>
-  </si>
-  <si>
-    <t>2026-06-24 12:45:41</t>
-  </si>
-  <si>
-    <t>2026-06-24 13:37:51</t>
-  </si>
-  <si>
-    <t>2026-06-24 14:34:48</t>
-  </si>
-  <si>
-    <t>2026-06-24 16:26:12</t>
-  </si>
-  <si>
-    <t>2026-06-24 17:42:47</t>
-  </si>
-  <si>
-    <t>2026-06-25 09:39:46</t>
-  </si>
-  <si>
-    <t>2026-06-25 09:45:44</t>
-  </si>
-  <si>
-    <t>2026-06-25 10:04:07</t>
-  </si>
-  <si>
-    <t>2026-06-25 10:24:58</t>
-  </si>
-  <si>
-    <t>2026-06-25 11:35:12</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:10:00</t>
+  </si>
+  <si>
+    <t>10:41:00</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>14:19:00</t>
+  </si>
+  <si>
+    <t>14:06:00</t>
+  </si>
+  <si>
+    <t>12:13:00</t>
+  </si>
+  <si>
+    <t>08:05:00</t>
+  </si>
+  <si>
+    <t>14:43:00</t>
+  </si>
+  <si>
+    <t>15:03:00</t>
+  </si>
+  <si>
+    <t>11:22:00</t>
+  </si>
+  <si>
+    <t>09:10:00</t>
+  </si>
+  <si>
+    <t>11:38:00</t>
+  </si>
+  <si>
+    <t>10:24:00</t>
+  </si>
+  <si>
+    <t>11:03:00</t>
+  </si>
+  <si>
+    <t>15:51:00</t>
+  </si>
+  <si>
+    <t>12:20:00</t>
+  </si>
+  <si>
+    <t>09:51:00</t>
+  </si>
+  <si>
+    <t>14:09:00</t>
+  </si>
+  <si>
+    <t>09:43:00</t>
+  </si>
+  <si>
+    <t>14:35:00</t>
+  </si>
+  <si>
+    <t>09:32:00</t>
+  </si>
+  <si>
+    <t>15:54:00</t>
+  </si>
+  <si>
+    <t>11:24:00</t>
+  </si>
+  <si>
+    <t>18:34:00</t>
+  </si>
+  <si>
+    <t>14:33:00</t>
+  </si>
+  <si>
+    <t>13:37:00</t>
+  </si>
+  <si>
+    <t>16:26:00</t>
+  </si>
+  <si>
+    <t>10:16:00</t>
+  </si>
+  <si>
+    <t>11:54:00</t>
+  </si>
+  <si>
+    <t>11:08:00</t>
+  </si>
+  <si>
+    <t>17:41:00</t>
+  </si>
+  <si>
+    <t>12:45:00</t>
+  </si>
+  <si>
+    <t>09:46:00</t>
+  </si>
+  <si>
+    <t>10:25:00</t>
+  </si>
+  <si>
+    <t>09:39:00</t>
+  </si>
+  <si>
+    <t>11:35:00</t>
+  </si>
+  <si>
+    <t>10:04:00</t>
+  </si>
+  <si>
+    <t>10:02:00</t>
+  </si>
+  <si>
+    <t>12:53:00</t>
+  </si>
+  <si>
+    <t>11:19:00</t>
+  </si>
+  <si>
+    <t>17:42:00</t>
+  </si>
+  <si>
+    <t>14:34:00</t>
+  </si>
+  <si>
+    <t>15:11:00</t>
+  </si>
+  <si>
+    <t>08:51:00</t>
+  </si>
+  <si>
+    <t>09:03:00</t>
+  </si>
+  <si>
+    <t>14:48:00</t>
+  </si>
+  <si>
+    <t>11:01:00</t>
+  </si>
+  <si>
+    <t>10:03:00</t>
+  </si>
+  <si>
+    <t>18:06:00</t>
+  </si>
+  <si>
+    <t>14:51:00</t>
+  </si>
+  <si>
+    <t>09:23:00</t>
+  </si>
+  <si>
+    <t>18:18:00</t>
+  </si>
+  <si>
+    <t>3233435057 3233435057</t>
+  </si>
+  <si>
+    <t>3233420126 3233420126</t>
+  </si>
+  <si>
+    <t>3233420379 3233420379</t>
+  </si>
+  <si>
+    <t>3233442505 3233442505</t>
+  </si>
+  <si>
+    <t>3233427177 3233427177</t>
+  </si>
+  <si>
+    <t>3233473075 3233473075</t>
+  </si>
+  <si>
+    <t>3233522219 3233522219</t>
+  </si>
+  <si>
+    <t>3233529160 3233529160</t>
+  </si>
+  <si>
+    <t>3233537334 3233537334</t>
+  </si>
+  <si>
+    <t>3233527240 3233527240</t>
+  </si>
+  <si>
+    <t>3233527425 3233527425</t>
+  </si>
+  <si>
+    <t>3233529187 3233529187</t>
+  </si>
+  <si>
+    <t>3233566380 3233566380</t>
+  </si>
+  <si>
+    <t>3233583569 3233583569</t>
+  </si>
+  <si>
+    <t>3233578496 3233578496</t>
+  </si>
+  <si>
+    <t>3233645483 3233645483</t>
+  </si>
+  <si>
+    <t>3233719634 3233719634</t>
+  </si>
+  <si>
+    <t>3233722445 3233722445</t>
+  </si>
+  <si>
+    <t>3233726056 3233726056</t>
+  </si>
+  <si>
+    <t>3233748714 3233748714</t>
+  </si>
+  <si>
+    <t>3233763379 3233763379</t>
+  </si>
+  <si>
+    <t>3233773236 3233773236</t>
+  </si>
+  <si>
+    <t>3233775906 3233775906</t>
+  </si>
+  <si>
+    <t>3233767297 3233767297</t>
+  </si>
+  <si>
+    <t>3233808438 3233808438</t>
+  </si>
+  <si>
+    <t>3233796161 3233796161</t>
+  </si>
+  <si>
+    <t>3233796517 3233796517</t>
+  </si>
+  <si>
+    <t>3233812501 3233812501</t>
+  </si>
+  <si>
+    <t>3233809063 3233809063</t>
+  </si>
+  <si>
+    <t>3233788882 3233788882</t>
+  </si>
+  <si>
+    <t>3233814729 3233814729</t>
+  </si>
+  <si>
+    <t>3233819165 3233819165</t>
+  </si>
+  <si>
+    <t>3233835180 3233835180</t>
+  </si>
+  <si>
+    <t>3233856178 3233856178</t>
+  </si>
+  <si>
+    <t>3233856268 3233856268</t>
+  </si>
+  <si>
+    <t>3233856973 3233856973</t>
+  </si>
+  <si>
+    <t>3233866140 3233866140</t>
+  </si>
+  <si>
+    <t>3233933493 3233933493</t>
+  </si>
+  <si>
+    <t>3233943601 3233943601</t>
+  </si>
+  <si>
+    <t>3233930421 3233930421</t>
+  </si>
+  <si>
+    <t>3233932678 3233932678</t>
+  </si>
+  <si>
+    <t>3233954359 3233954359</t>
+  </si>
+  <si>
+    <t>3234037906 3234037906</t>
+  </si>
+  <si>
+    <t>3234037917 3234037917</t>
+  </si>
+  <si>
+    <t>3234037918 3234037918</t>
+  </si>
+  <si>
+    <t>3234031196 3234031196</t>
+  </si>
+  <si>
+    <t>3234056130 3234056130</t>
+  </si>
+  <si>
+    <t>3234059480 3234059480</t>
+  </si>
+  <si>
+    <t>3234059912 3234059912</t>
+  </si>
+  <si>
+    <t>3234045594 3234045594</t>
+  </si>
+  <si>
+    <t>3234061090 3234061090</t>
+  </si>
+  <si>
+    <t>3234065138 3234065138</t>
+  </si>
+  <si>
+    <t>3234047067 3234047067</t>
+  </si>
+  <si>
+    <t>3234080170 3234080170</t>
+  </si>
+  <si>
+    <t>3234100359 3234100359</t>
+  </si>
+  <si>
+    <t>3234122400 3234122400</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА % 1 - АВТОПАРК</t>
@@ -766,7 +1042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:N66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -775,14 +1051,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -816,1093 +1095,1381 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F2">
-        <v>39.01</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.53</v>
+        <v>24.8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>94</v>
       </c>
       <c r="H2">
-        <v>59.69</v>
+        <v>1.78</v>
       </c>
       <c r="I2" s="1">
-        <v>1.56</v>
+        <v>44.14</v>
       </c>
       <c r="J2">
-        <v>60.86</v>
-      </c>
-      <c r="K2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>1.82</v>
+      </c>
+      <c r="K2" s="1">
+        <v>45.14</v>
+      </c>
+      <c r="L2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M2">
+        <v>315455</v>
+      </c>
+      <c r="N2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46189</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="F3">
-        <v>24.8</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.78</v>
+        <v>39.01</v>
+      </c>
+      <c r="G3" t="s">
+        <v>94</v>
       </c>
       <c r="H3">
-        <v>44.14</v>
+        <v>1.53</v>
       </c>
       <c r="I3" s="1">
-        <v>1.82</v>
+        <v>59.69</v>
       </c>
       <c r="J3">
-        <v>45.14</v>
-      </c>
-      <c r="K3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>1.56</v>
+      </c>
+      <c r="K3" s="1">
+        <v>60.86</v>
+      </c>
+      <c r="L3" t="s">
+        <v>96</v>
+      </c>
+      <c r="M3">
+        <v>163974</v>
+      </c>
+      <c r="N3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46189</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F4">
-        <v>28.13</v>
-      </c>
-      <c r="G4" s="1">
+        <v>35.4</v>
+      </c>
+      <c r="G4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H4">
         <v>0.66</v>
       </c>
-      <c r="H4">
-        <v>18.57</v>
-      </c>
       <c r="I4" s="1">
+        <v>23.36</v>
+      </c>
+      <c r="J4">
         <v>0.67</v>
       </c>
-      <c r="J4">
-        <v>18.85</v>
-      </c>
-      <c r="K4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="K4" s="1">
+        <v>23.72</v>
+      </c>
+      <c r="L4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46189</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="F5">
         <v>24.87</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H5">
         <v>1.78</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>44.27</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.82</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>45.26</v>
       </c>
-      <c r="K5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>98</v>
+      </c>
+      <c r="M5">
+        <v>315721</v>
+      </c>
+      <c r="N5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46189</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F6">
-        <v>35.4</v>
-      </c>
-      <c r="G6" s="1">
+        <v>28.13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6">
         <v>0.66</v>
       </c>
-      <c r="H6">
-        <v>23.36</v>
-      </c>
       <c r="I6" s="1">
+        <v>18.57</v>
+      </c>
+      <c r="J6">
         <v>0.67</v>
       </c>
-      <c r="J6">
-        <v>23.72</v>
-      </c>
-      <c r="K6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="K6" s="1">
+        <v>18.85</v>
+      </c>
+      <c r="L6" t="s">
+        <v>99</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46190</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="F7">
         <v>59.63</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>94</v>
+      </c>
+      <c r="H7">
         <v>1.56</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>93.02</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.59</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>94.81</v>
       </c>
-      <c r="K7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>100</v>
+      </c>
+      <c r="M7">
+        <v>495250</v>
+      </c>
+      <c r="N7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46191</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="F8">
         <v>36.43</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>94</v>
+      </c>
+      <c r="H8">
         <v>1.55</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>56.47</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.58</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>57.56</v>
       </c>
-      <c r="K8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>101</v>
+      </c>
+      <c r="M8">
+        <v>605</v>
+      </c>
+      <c r="N8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46191</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="F9">
-        <v>60.01</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1.52</v>
+        <v>29.88</v>
+      </c>
+      <c r="G9" t="s">
+        <v>94</v>
       </c>
       <c r="H9">
-        <v>91.22</v>
+        <v>0.65</v>
       </c>
       <c r="I9" s="1">
-        <v>1.55</v>
+        <v>19.42</v>
       </c>
       <c r="J9">
-        <v>93.02</v>
-      </c>
-      <c r="K9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>0.66</v>
+      </c>
+      <c r="K9" s="1">
+        <v>19.72</v>
+      </c>
+      <c r="L9" t="s">
+        <v>102</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46191</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F10">
-        <v>22.02</v>
-      </c>
-      <c r="G10" s="1">
+        <v>29.12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10">
         <v>0.65</v>
       </c>
-      <c r="H10">
-        <v>14.31</v>
-      </c>
       <c r="I10" s="1">
+        <v>18.93</v>
+      </c>
+      <c r="J10">
         <v>0.66</v>
       </c>
-      <c r="J10">
-        <v>14.53</v>
-      </c>
-      <c r="K10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="K10" s="1">
+        <v>19.22</v>
+      </c>
+      <c r="L10" t="s">
+        <v>103</v>
+      </c>
+      <c r="M10">
+        <v>42300</v>
+      </c>
+      <c r="N10" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46191</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F11">
-        <v>29.67</v>
-      </c>
-      <c r="G11" s="1">
+        <v>22.02</v>
+      </c>
+      <c r="G11" t="s">
+        <v>94</v>
+      </c>
+      <c r="H11">
         <v>0.65</v>
       </c>
-      <c r="H11">
-        <v>19.29</v>
-      </c>
       <c r="I11" s="1">
+        <v>14.31</v>
+      </c>
+      <c r="J11">
         <v>0.66</v>
       </c>
-      <c r="J11">
-        <v>19.58</v>
-      </c>
-      <c r="K11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="K11" s="1">
+        <v>14.53</v>
+      </c>
+      <c r="L11" t="s">
+        <v>104</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46191</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="F12">
-        <v>29.88</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0.65</v>
+        <v>60.01</v>
+      </c>
+      <c r="G12" t="s">
+        <v>94</v>
       </c>
       <c r="H12">
-        <v>19.42</v>
+        <v>1.52</v>
       </c>
       <c r="I12" s="1">
-        <v>0.66</v>
+        <v>91.22</v>
       </c>
       <c r="J12">
-        <v>19.72</v>
-      </c>
-      <c r="K12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>1.55</v>
+      </c>
+      <c r="K12" s="1">
+        <v>93.02</v>
+      </c>
+      <c r="L12" t="s">
+        <v>105</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>46191</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F13">
-        <v>29.12</v>
-      </c>
-      <c r="G13" s="1">
+        <v>29.67</v>
+      </c>
+      <c r="G13" t="s">
+        <v>94</v>
+      </c>
+      <c r="H13">
         <v>0.65</v>
       </c>
-      <c r="H13">
-        <v>18.93</v>
-      </c>
       <c r="I13" s="1">
+        <v>19.29</v>
+      </c>
+      <c r="J13">
         <v>0.66</v>
       </c>
-      <c r="J13">
-        <v>19.22</v>
-      </c>
-      <c r="K13" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="K13" s="1">
+        <v>19.58</v>
+      </c>
+      <c r="L13" t="s">
+        <v>106</v>
+      </c>
+      <c r="M13">
+        <v>38395</v>
+      </c>
+      <c r="N13" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>46192</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F14">
         <v>31.38</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>94</v>
+      </c>
+      <c r="H14">
         <v>0.65</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="1">
         <v>20.4</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>0.66</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>20.71</v>
       </c>
-      <c r="K14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14" t="s">
+        <v>107</v>
+      </c>
+      <c r="M14">
+        <v>97700</v>
+      </c>
+      <c r="N14" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>46192</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="F15">
         <v>19.97</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" t="s">
+        <v>94</v>
+      </c>
+      <c r="H15">
         <v>1.51</v>
       </c>
-      <c r="H15">
+      <c r="I15" s="1">
         <v>30.15</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15">
         <v>1.54</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="1">
         <v>30.75</v>
       </c>
-      <c r="K15" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15" t="s">
+        <v>108</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
         <v>46192</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="F16">
         <v>33.26</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H16">
         <v>1.51</v>
       </c>
-      <c r="H16">
+      <c r="I16" s="1">
         <v>50.22</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16">
         <v>1.54</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="1">
         <v>51.22</v>
       </c>
-      <c r="K16" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16">
+        <v>53415</v>
+      </c>
+      <c r="N16" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="3">
         <v>46193</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="F17">
         <v>10</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" t="s">
+        <v>94</v>
+      </c>
+      <c r="H17">
         <v>1.5</v>
       </c>
-      <c r="H17">
+      <c r="I17" s="1">
         <v>15</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17">
         <v>1.53</v>
       </c>
-      <c r="J17">
+      <c r="K17" s="1">
         <v>15.3</v>
       </c>
-      <c r="K17" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17" t="s">
+        <v>110</v>
+      </c>
+      <c r="M17">
+        <v>69187</v>
+      </c>
+      <c r="N17" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="3">
         <v>46195</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F18">
-        <v>27.42</v>
-      </c>
-      <c r="G18" s="1">
+        <v>15.42</v>
+      </c>
+      <c r="G18" t="s">
+        <v>94</v>
+      </c>
+      <c r="H18">
         <v>0.65</v>
       </c>
-      <c r="H18">
-        <v>17.82</v>
-      </c>
       <c r="I18" s="1">
+        <v>10.02</v>
+      </c>
+      <c r="J18">
         <v>0.66</v>
       </c>
-      <c r="J18">
-        <v>18.1</v>
-      </c>
-      <c r="K18" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="K18" s="1">
+        <v>10.18</v>
+      </c>
+      <c r="L18" t="s">
+        <v>111</v>
+      </c>
+      <c r="M18">
+        <v>76443</v>
+      </c>
+      <c r="N18" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="3">
         <v>46195</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="F19">
-        <v>15.42</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0.65</v>
+        <v>25</v>
+      </c>
+      <c r="G19" t="s">
+        <v>94</v>
       </c>
       <c r="H19">
-        <v>10.02</v>
+        <v>1.48</v>
       </c>
       <c r="I19" s="1">
-        <v>0.66</v>
+        <v>37</v>
       </c>
       <c r="J19">
-        <v>10.18</v>
-      </c>
-      <c r="K19" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>1.51</v>
+      </c>
+      <c r="K19" s="1">
+        <v>37.75</v>
+      </c>
+      <c r="L19" t="s">
+        <v>112</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="3">
         <v>46195</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D20" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="F20">
-        <v>25</v>
-      </c>
-      <c r="G20" s="1">
-        <v>1.48</v>
+        <v>27.42</v>
+      </c>
+      <c r="G20" t="s">
+        <v>94</v>
       </c>
       <c r="H20">
-        <v>37</v>
+        <v>0.65</v>
       </c>
       <c r="I20" s="1">
-        <v>1.51</v>
+        <v>17.82</v>
       </c>
       <c r="J20">
-        <v>37.75</v>
-      </c>
-      <c r="K20" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>0.66</v>
+      </c>
+      <c r="K20" s="1">
+        <v>18.1</v>
+      </c>
+      <c r="L20" t="s">
+        <v>113</v>
+      </c>
+      <c r="M20">
+        <v>76940</v>
+      </c>
+      <c r="N20" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="3">
         <v>46196</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E21" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="F21">
-        <v>63.75</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1.73</v>
+        <v>31.56</v>
+      </c>
+      <c r="G21" t="s">
+        <v>94</v>
       </c>
       <c r="H21">
-        <v>110.29</v>
+        <v>0.65</v>
       </c>
       <c r="I21" s="1">
-        <v>1.77</v>
+        <v>20.51</v>
       </c>
       <c r="J21">
-        <v>112.84</v>
-      </c>
-      <c r="K21" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>0.66</v>
+      </c>
+      <c r="K21" s="1">
+        <v>20.83</v>
+      </c>
+      <c r="L21" t="s">
+        <v>114</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="3">
         <v>46196</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="F22">
-        <v>56.2</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1.49</v>
+        <v>63.75</v>
+      </c>
+      <c r="G22" t="s">
+        <v>94</v>
       </c>
       <c r="H22">
-        <v>83.73999999999999</v>
+        <v>1.73</v>
       </c>
       <c r="I22" s="1">
-        <v>1.52</v>
+        <v>110.29</v>
       </c>
       <c r="J22">
-        <v>85.42</v>
-      </c>
-      <c r="K22" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>1.77</v>
+      </c>
+      <c r="K22" s="1">
+        <v>112.84</v>
+      </c>
+      <c r="L22" t="s">
+        <v>115</v>
+      </c>
+      <c r="M22">
+        <v>316200</v>
+      </c>
+      <c r="N22" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="3">
         <v>46196</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D23" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="F23">
-        <v>31.56</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0.65</v>
+        <v>55.78</v>
+      </c>
+      <c r="G23" t="s">
+        <v>94</v>
       </c>
       <c r="H23">
-        <v>20.51</v>
+        <v>1.48</v>
       </c>
       <c r="I23" s="1">
-        <v>0.66</v>
+        <v>82.55</v>
       </c>
       <c r="J23">
-        <v>20.83</v>
-      </c>
-      <c r="K23" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>1.51</v>
+      </c>
+      <c r="K23" s="1">
+        <v>84.23</v>
+      </c>
+      <c r="L23" t="s">
+        <v>116</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="3">
         <v>46196</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="E24" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="F24">
-        <v>55.78</v>
-      </c>
-      <c r="G24" s="1">
-        <v>1.48</v>
+        <v>56.2</v>
+      </c>
+      <c r="G24" t="s">
+        <v>94</v>
       </c>
       <c r="H24">
-        <v>82.55</v>
+        <v>1.49</v>
       </c>
       <c r="I24" s="1">
-        <v>1.51</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="J24">
-        <v>84.23</v>
-      </c>
-      <c r="K24" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>1.52</v>
+      </c>
+      <c r="K24" s="1">
+        <v>85.42</v>
+      </c>
+      <c r="L24" t="s">
+        <v>117</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="3">
         <v>46196</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E25" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F25">
         <v>27.83</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" t="s">
+        <v>94</v>
+      </c>
+      <c r="H25">
         <v>0.65</v>
       </c>
-      <c r="H25">
+      <c r="I25" s="1">
         <v>18.09</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25">
         <v>0.66</v>
       </c>
-      <c r="J25">
+      <c r="K25" s="1">
         <v>18.37</v>
       </c>
-      <c r="K25" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+      <c r="L25" t="s">
+        <v>118</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="3">
         <v>46197</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E26" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="F26">
-        <v>30</v>
-      </c>
-      <c r="G26" s="1">
-        <v>1.48</v>
+        <v>32.73</v>
+      </c>
+      <c r="G26" t="s">
+        <v>94</v>
       </c>
       <c r="H26">
-        <v>44.4</v>
+        <v>0.65</v>
       </c>
       <c r="I26" s="1">
-        <v>1.51</v>
+        <v>21.27</v>
       </c>
       <c r="J26">
-        <v>45.3</v>
-      </c>
-      <c r="K26" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>0.66</v>
+      </c>
+      <c r="K26" s="1">
+        <v>21.6</v>
+      </c>
+      <c r="L26" t="s">
+        <v>119</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="3">
         <v>46197</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E27" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="F27">
-        <v>31.14</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0.65</v>
+        <v>56.97</v>
+      </c>
+      <c r="G27" t="s">
+        <v>94</v>
       </c>
       <c r="H27">
-        <v>20.24</v>
+        <v>1.48</v>
       </c>
       <c r="I27" s="1">
-        <v>0.66</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="J27">
-        <v>20.55</v>
-      </c>
-      <c r="K27" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>1.51</v>
+      </c>
+      <c r="K27" s="1">
+        <v>86.02</v>
+      </c>
+      <c r="L27" t="s">
+        <v>120</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="3">
         <v>46197</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D28" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E28" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="F28">
-        <v>31.75</v>
-      </c>
-      <c r="G28" s="1">
-        <v>1.48</v>
+        <v>21.02</v>
+      </c>
+      <c r="G28" t="s">
+        <v>94</v>
       </c>
       <c r="H28">
-        <v>46.99</v>
+        <v>0.65</v>
       </c>
       <c r="I28" s="1">
-        <v>1.51</v>
+        <v>13.66</v>
       </c>
       <c r="J28">
-        <v>47.94</v>
-      </c>
-      <c r="K28" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+        <v>0.66</v>
+      </c>
+      <c r="K28" s="1">
+        <v>13.87</v>
+      </c>
+      <c r="L28" t="s">
+        <v>121</v>
+      </c>
+      <c r="M28">
+        <v>77072</v>
+      </c>
+      <c r="N28" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="3">
         <v>46197</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D29" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E29" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="F29">
-        <v>33.26</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0.65</v>
+        <v>30</v>
+      </c>
+      <c r="G29" t="s">
+        <v>94</v>
       </c>
       <c r="H29">
-        <v>21.62</v>
+        <v>1.48</v>
       </c>
       <c r="I29" s="1">
-        <v>0.66</v>
+        <v>44.4</v>
       </c>
       <c r="J29">
-        <v>21.95</v>
-      </c>
-      <c r="K29" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+        <v>1.51</v>
+      </c>
+      <c r="K29" s="1">
+        <v>45.3</v>
+      </c>
+      <c r="L29" t="s">
+        <v>122</v>
+      </c>
+      <c r="M29">
+        <v>476400</v>
+      </c>
+      <c r="N29" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="3">
         <v>46197</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E30" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="F30">
-        <v>56.97</v>
-      </c>
-      <c r="G30" s="1">
+        <v>31.75</v>
+      </c>
+      <c r="G30" t="s">
+        <v>94</v>
+      </c>
+      <c r="H30">
         <v>1.48</v>
       </c>
-      <c r="H30">
-        <v>84.31999999999999</v>
-      </c>
       <c r="I30" s="1">
+        <v>46.99</v>
+      </c>
+      <c r="J30">
         <v>1.51</v>
       </c>
-      <c r="J30">
-        <v>86.02</v>
-      </c>
-      <c r="K30" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+      <c r="K30" s="1">
+        <v>47.94</v>
+      </c>
+      <c r="L30" t="s">
+        <v>123</v>
+      </c>
+      <c r="M30">
+        <v>41001</v>
+      </c>
+      <c r="N30" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="3">
         <v>46197</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D31" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="E31" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F31">
-        <v>32.73</v>
-      </c>
-      <c r="G31" s="1">
+        <v>31.14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>94</v>
+      </c>
+      <c r="H31">
         <v>0.65</v>
       </c>
-      <c r="H31">
-        <v>21.27</v>
-      </c>
       <c r="I31" s="1">
+        <v>20.24</v>
+      </c>
+      <c r="J31">
         <v>0.66</v>
       </c>
-      <c r="J31">
-        <v>21.6</v>
-      </c>
-      <c r="K31" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+      <c r="K31" s="1">
+        <v>20.55</v>
+      </c>
+      <c r="L31" t="s">
+        <v>124</v>
+      </c>
+      <c r="M31">
+        <v>55116</v>
+      </c>
+      <c r="N31" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="3">
         <v>46197</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E32" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F32">
-        <v>21.02</v>
-      </c>
-      <c r="G32" s="1">
+        <v>21.29</v>
+      </c>
+      <c r="G32" t="s">
+        <v>94</v>
+      </c>
+      <c r="H32">
         <v>0.65</v>
       </c>
-      <c r="H32">
-        <v>13.66</v>
-      </c>
       <c r="I32" s="1">
+        <v>13.84</v>
+      </c>
+      <c r="J32">
         <v>0.66</v>
       </c>
-      <c r="J32">
-        <v>13.87</v>
-      </c>
-      <c r="K32" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+      <c r="K32" s="1">
+        <v>14.05</v>
+      </c>
+      <c r="L32" t="s">
+        <v>125</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="3">
         <v>46197</v>
       </c>
@@ -1910,339 +2477,1229 @@
         <v>21</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="E33" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F33">
-        <v>21.29</v>
-      </c>
-      <c r="G33" s="1">
+        <v>33.26</v>
+      </c>
+      <c r="G33" t="s">
+        <v>94</v>
+      </c>
+      <c r="H33">
         <v>0.65</v>
       </c>
-      <c r="H33">
-        <v>13.84</v>
-      </c>
       <c r="I33" s="1">
+        <v>21.62</v>
+      </c>
+      <c r="J33">
         <v>0.66</v>
       </c>
-      <c r="J33">
-        <v>14.05</v>
-      </c>
-      <c r="K33" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="K33" s="1">
+        <v>21.95</v>
+      </c>
+      <c r="L33" t="s">
+        <v>126</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="3">
         <v>46198</v>
       </c>
       <c r="B34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D34" t="s">
         <v>69</v>
       </c>
       <c r="E34" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="F34">
-        <v>45.97</v>
-      </c>
-      <c r="G34" s="1">
-        <v>1.48</v>
+        <v>29.02</v>
+      </c>
+      <c r="G34" t="s">
+        <v>94</v>
       </c>
       <c r="H34">
-        <v>68.04000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="I34" s="1">
-        <v>1.51</v>
+        <v>18.86</v>
       </c>
       <c r="J34">
-        <v>69.41</v>
-      </c>
-      <c r="K34" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+        <v>0.66</v>
+      </c>
+      <c r="K34" s="1">
+        <v>19.15</v>
+      </c>
+      <c r="L34" t="s">
+        <v>127</v>
+      </c>
+      <c r="M34">
+        <v>97950</v>
+      </c>
+      <c r="N34" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="3">
         <v>46198</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E35" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F35">
-        <v>29.02</v>
-      </c>
-      <c r="G35" s="1">
+        <v>31.48</v>
+      </c>
+      <c r="G35" t="s">
+        <v>94</v>
+      </c>
+      <c r="H35">
         <v>0.65</v>
       </c>
-      <c r="H35">
-        <v>18.86</v>
-      </c>
       <c r="I35" s="1">
+        <v>20.46</v>
+      </c>
+      <c r="J35">
         <v>0.66</v>
       </c>
-      <c r="J35">
-        <v>19.15</v>
-      </c>
-      <c r="K35" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+      <c r="K35" s="1">
+        <v>20.78</v>
+      </c>
+      <c r="L35" t="s">
+        <v>128</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="3">
         <v>46198</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D36" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="E36" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="F36">
-        <v>29.11</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0.65</v>
+        <v>45.97</v>
+      </c>
+      <c r="G36" t="s">
+        <v>94</v>
       </c>
       <c r="H36">
-        <v>18.92</v>
+        <v>1.48</v>
       </c>
       <c r="I36" s="1">
-        <v>0.66</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="J36">
-        <v>19.21</v>
-      </c>
-      <c r="K36" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+        <v>1.51</v>
+      </c>
+      <c r="K36" s="1">
+        <v>69.41</v>
+      </c>
+      <c r="L36" t="s">
+        <v>129</v>
+      </c>
+      <c r="M36">
+        <v>187520</v>
+      </c>
+      <c r="N36" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" s="3">
         <v>46198</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D37" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="E37" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F37">
-        <v>31.48</v>
-      </c>
-      <c r="G37" s="1">
+        <v>29.95</v>
+      </c>
+      <c r="G37" t="s">
+        <v>94</v>
+      </c>
+      <c r="H37">
         <v>0.65</v>
       </c>
-      <c r="H37">
-        <v>20.46</v>
-      </c>
       <c r="I37" s="1">
+        <v>19.47</v>
+      </c>
+      <c r="J37">
         <v>0.66</v>
       </c>
-      <c r="J37">
-        <v>20.78</v>
-      </c>
-      <c r="K37" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+      <c r="K37" s="1">
+        <v>19.77</v>
+      </c>
+      <c r="L37" t="s">
+        <v>130</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="3">
         <v>46198</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="E38" t="s">
+        <v>92</v>
+      </c>
+      <c r="F38">
+        <v>29.11</v>
+      </c>
+      <c r="G38" t="s">
+        <v>94</v>
+      </c>
+      <c r="H38">
+        <v>0.65</v>
+      </c>
+      <c r="I38" s="1">
+        <v>18.92</v>
+      </c>
+      <c r="J38">
+        <v>0.66</v>
+      </c>
+      <c r="K38" s="1">
+        <v>19.21</v>
+      </c>
+      <c r="L38" t="s">
+        <v>131</v>
+      </c>
+      <c r="M38">
+        <v>69298</v>
+      </c>
+      <c r="N38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B39" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" t="s">
+        <v>91</v>
+      </c>
+      <c r="F39">
+        <v>17</v>
+      </c>
+      <c r="G39" t="s">
+        <v>94</v>
+      </c>
+      <c r="H39">
+        <v>1.47</v>
+      </c>
+      <c r="I39" s="1">
+        <v>24.99</v>
+      </c>
+      <c r="J39">
+        <v>1.5</v>
+      </c>
+      <c r="K39" s="1">
+        <v>25.5</v>
+      </c>
+      <c r="L39" t="s">
+        <v>132</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B40" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" t="s">
+        <v>91</v>
+      </c>
+      <c r="F40">
+        <v>30.16</v>
+      </c>
+      <c r="G40" t="s">
+        <v>94</v>
+      </c>
+      <c r="H40">
+        <v>1.47</v>
+      </c>
+      <c r="I40" s="1">
+        <v>44.34</v>
+      </c>
+      <c r="J40">
+        <v>1.5</v>
+      </c>
+      <c r="K40" s="1">
+        <v>45.24</v>
+      </c>
+      <c r="L40" t="s">
+        <v>133</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41" t="s">
+        <v>91</v>
+      </c>
+      <c r="F41">
+        <v>10</v>
+      </c>
+      <c r="G41" t="s">
+        <v>94</v>
+      </c>
+      <c r="H41">
+        <v>1.47</v>
+      </c>
+      <c r="I41" s="1">
+        <v>14.7</v>
+      </c>
+      <c r="J41">
+        <v>1.5</v>
+      </c>
+      <c r="K41" s="1">
+        <v>15</v>
+      </c>
+      <c r="L41" t="s">
+        <v>134</v>
+      </c>
+      <c r="M41">
+        <v>77080</v>
+      </c>
+      <c r="N41" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" t="s">
+        <v>67</v>
+      </c>
+      <c r="E42" t="s">
+        <v>91</v>
+      </c>
+      <c r="F42">
+        <v>49.47</v>
+      </c>
+      <c r="G42" t="s">
+        <v>94</v>
+      </c>
+      <c r="H42">
+        <v>1.47</v>
+      </c>
+      <c r="I42" s="1">
+        <v>72.72</v>
+      </c>
+      <c r="J42">
+        <v>1.5</v>
+      </c>
+      <c r="K42" s="1">
+        <v>74.2</v>
+      </c>
+      <c r="L42" t="s">
+        <v>135</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="3">
+        <v>46200</v>
+      </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" t="s">
+        <v>93</v>
+      </c>
+      <c r="F43">
+        <v>49.28</v>
+      </c>
+      <c r="G43" t="s">
+        <v>94</v>
+      </c>
+      <c r="H43">
+        <v>1.48</v>
+      </c>
+      <c r="I43" s="1">
+        <v>72.93000000000001</v>
+      </c>
+      <c r="J43">
+        <v>1.51</v>
+      </c>
+      <c r="K43" s="1">
+        <v>74.41</v>
+      </c>
+      <c r="L43" t="s">
+        <v>97</v>
+      </c>
+      <c r="M43">
+        <v>3172</v>
+      </c>
+      <c r="N43" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" t="s">
+        <v>84</v>
+      </c>
+      <c r="E44" t="s">
+        <v>93</v>
+      </c>
+      <c r="F44">
+        <v>27.49</v>
+      </c>
+      <c r="G44" t="s">
+        <v>94</v>
+      </c>
+      <c r="H44">
+        <v>1.48</v>
+      </c>
+      <c r="I44" s="1">
+        <v>40.69</v>
+      </c>
+      <c r="J44">
+        <v>1.51</v>
+      </c>
+      <c r="K44" s="1">
+        <v>41.51</v>
+      </c>
+      <c r="L44" t="s">
+        <v>136</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" t="s">
+        <v>85</v>
+      </c>
+      <c r="E45" t="s">
+        <v>92</v>
+      </c>
+      <c r="F45">
+        <v>23.98</v>
+      </c>
+      <c r="G45" t="s">
+        <v>94</v>
+      </c>
+      <c r="H45">
+        <v>0.65</v>
+      </c>
+      <c r="I45" s="1">
+        <v>15.59</v>
+      </c>
+      <c r="J45">
+        <v>0.66</v>
+      </c>
+      <c r="K45" s="1">
+        <v>15.83</v>
+      </c>
+      <c r="L45" t="s">
+        <v>137</v>
+      </c>
+      <c r="M45">
+        <v>34789</v>
+      </c>
+      <c r="N45" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B46" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" t="s">
+        <v>85</v>
+      </c>
+      <c r="E46" t="s">
+        <v>91</v>
+      </c>
+      <c r="F46">
+        <v>10</v>
+      </c>
+      <c r="G46" t="s">
+        <v>94</v>
+      </c>
+      <c r="H46">
+        <v>1.47</v>
+      </c>
+      <c r="I46" s="1">
+        <v>14.7</v>
+      </c>
+      <c r="J46">
+        <v>1.5</v>
+      </c>
+      <c r="K46" s="1">
+        <v>15</v>
+      </c>
+      <c r="L46" t="s">
+        <v>137</v>
+      </c>
+      <c r="M46">
+        <v>34789</v>
+      </c>
+      <c r="N46" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" t="s">
+        <v>49</v>
+      </c>
+      <c r="D47" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" t="s">
+        <v>93</v>
+      </c>
+      <c r="F47">
+        <v>45.82</v>
+      </c>
+      <c r="G47" t="s">
+        <v>94</v>
+      </c>
+      <c r="H47">
+        <v>1.48</v>
+      </c>
+      <c r="I47" s="1">
+        <v>67.81</v>
+      </c>
+      <c r="J47">
+        <v>1.51</v>
+      </c>
+      <c r="K47" s="1">
+        <v>69.19</v>
+      </c>
+      <c r="L47" t="s">
+        <v>138</v>
+      </c>
+      <c r="M47">
+        <v>187600</v>
+      </c>
+      <c r="N47" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" t="s">
+        <v>86</v>
+      </c>
+      <c r="E48" t="s">
+        <v>91</v>
+      </c>
+      <c r="F48">
+        <v>20</v>
+      </c>
+      <c r="G48" t="s">
+        <v>94</v>
+      </c>
+      <c r="H48">
+        <v>1.47</v>
+      </c>
+      <c r="I48" s="1">
+        <v>29.4</v>
+      </c>
+      <c r="J48">
+        <v>1.5</v>
+      </c>
+      <c r="K48" s="1">
+        <v>30</v>
+      </c>
+      <c r="L48" t="s">
+        <v>139</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" t="s">
+        <v>87</v>
+      </c>
+      <c r="E49" t="s">
+        <v>93</v>
+      </c>
+      <c r="F49">
+        <v>19.97</v>
+      </c>
+      <c r="G49" t="s">
+        <v>94</v>
+      </c>
+      <c r="H49">
+        <v>1.48</v>
+      </c>
+      <c r="I49" s="1">
+        <v>29.56</v>
+      </c>
+      <c r="J49">
+        <v>1.51</v>
+      </c>
+      <c r="K49" s="1">
+        <v>30.15</v>
+      </c>
+      <c r="L49" t="s">
+        <v>140</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B50" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50" t="s">
+        <v>70</v>
+      </c>
+      <c r="E50" t="s">
+        <v>91</v>
+      </c>
+      <c r="F50">
+        <v>39.98</v>
+      </c>
+      <c r="G50" t="s">
+        <v>94</v>
+      </c>
+      <c r="H50">
+        <v>1.47</v>
+      </c>
+      <c r="I50" s="1">
+        <v>58.77</v>
+      </c>
+      <c r="J50">
+        <v>1.5</v>
+      </c>
+      <c r="K50" s="1">
+        <v>59.97</v>
+      </c>
+      <c r="L50" t="s">
+        <v>141</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B51" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" t="s">
+        <v>66</v>
+      </c>
+      <c r="E51" t="s">
+        <v>92</v>
+      </c>
+      <c r="F51">
+        <v>21.82</v>
+      </c>
+      <c r="G51" t="s">
+        <v>94</v>
+      </c>
+      <c r="H51">
+        <v>0.65</v>
+      </c>
+      <c r="I51" s="1">
+        <v>14.18</v>
+      </c>
+      <c r="J51">
+        <v>0.66</v>
+      </c>
+      <c r="K51" s="1">
+        <v>14.4</v>
+      </c>
+      <c r="L51" t="s">
+        <v>142</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B52" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" t="s">
+        <v>56</v>
+      </c>
+      <c r="D52" t="s">
+        <v>88</v>
+      </c>
+      <c r="E52" t="s">
+        <v>93</v>
+      </c>
+      <c r="F52">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>94</v>
+      </c>
+      <c r="H52">
+        <v>1.48</v>
+      </c>
+      <c r="I52" s="1">
+        <v>26.64</v>
+      </c>
+      <c r="J52">
+        <v>1.51</v>
+      </c>
+      <c r="K52" s="1">
+        <v>27.18</v>
+      </c>
+      <c r="L52" t="s">
+        <v>143</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B53" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" t="s">
+        <v>39</v>
+      </c>
+      <c r="D53" t="s">
+        <v>71</v>
+      </c>
+      <c r="E53" t="s">
+        <v>91</v>
+      </c>
+      <c r="F53">
+        <v>32.01</v>
+      </c>
+      <c r="G53" t="s">
+        <v>94</v>
+      </c>
+      <c r="H53">
+        <v>1.47</v>
+      </c>
+      <c r="I53" s="1">
+        <v>47.05</v>
+      </c>
+      <c r="J53">
+        <v>1.5</v>
+      </c>
+      <c r="K53" s="1">
+        <v>48.02</v>
+      </c>
+      <c r="L53" t="s">
+        <v>98</v>
+      </c>
+      <c r="M53">
+        <v>53915</v>
+      </c>
+      <c r="N53" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B54" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54" t="s">
+        <v>89</v>
+      </c>
+      <c r="E54" t="s">
+        <v>92</v>
+      </c>
+      <c r="F54">
+        <v>32.32</v>
+      </c>
+      <c r="G54" t="s">
+        <v>94</v>
+      </c>
+      <c r="H54">
+        <v>0.65</v>
+      </c>
+      <c r="I54" s="1">
+        <v>21.01</v>
+      </c>
+      <c r="J54">
+        <v>0.66</v>
+      </c>
+      <c r="K54" s="1">
+        <v>21.33</v>
+      </c>
+      <c r="L54" t="s">
+        <v>140</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" t="s">
+        <v>37</v>
+      </c>
+      <c r="D55" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" t="s">
+        <v>92</v>
+      </c>
+      <c r="F55">
+        <v>27.56</v>
+      </c>
+      <c r="G55" t="s">
+        <v>94</v>
+      </c>
+      <c r="H55">
+        <v>0.65</v>
+      </c>
+      <c r="I55" s="1">
+        <v>17.91</v>
+      </c>
+      <c r="J55">
+        <v>0.66</v>
+      </c>
+      <c r="K55" s="1">
+        <v>18.19</v>
+      </c>
+      <c r="L55" t="s">
+        <v>144</v>
+      </c>
+      <c r="M55">
+        <v>98150</v>
+      </c>
+      <c r="N55" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B56" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56" t="s">
+        <v>40</v>
+      </c>
+      <c r="D56" t="s">
         <v>72</v>
       </c>
-      <c r="F38">
-        <v>29.96</v>
-      </c>
-      <c r="G38" s="1">
+      <c r="E56" t="s">
+        <v>92</v>
+      </c>
+      <c r="F56">
+        <v>28.58</v>
+      </c>
+      <c r="G56" t="s">
+        <v>94</v>
+      </c>
+      <c r="H56">
         <v>0.65</v>
       </c>
-      <c r="H38">
-        <v>19.47</v>
-      </c>
-      <c r="I38" s="1">
+      <c r="I56" s="1">
+        <v>18.58</v>
+      </c>
+      <c r="J56">
         <v>0.66</v>
       </c>
-      <c r="J38">
-        <v>19.77</v>
-      </c>
-      <c r="K38" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-    </row>
-    <row r="42" spans="1:11">
-      <c r="A42" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B43" s="7">
-        <v>566.84</v>
-      </c>
-      <c r="C43" s="7">
-        <v>20</v>
-      </c>
-      <c r="D43" s="8">
-        <v>0.6511</v>
-      </c>
-      <c r="E43" s="7">
-        <v>369.06</v>
-      </c>
-      <c r="F43" s="7">
-        <v>374.74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B44" s="7">
-        <v>304.78</v>
-      </c>
-      <c r="C44" s="7">
-        <v>9</v>
-      </c>
-      <c r="D44" s="8">
-        <v>1.5002</v>
-      </c>
-      <c r="E44" s="7">
-        <v>457.22</v>
-      </c>
-      <c r="F44" s="7">
-        <v>466.37</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="A45" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B45" s="7">
-        <v>255.2</v>
-      </c>
-      <c r="C45" s="7">
-        <v>5</v>
-      </c>
-      <c r="D45" s="8">
-        <v>1.5109</v>
-      </c>
-      <c r="E45" s="7">
-        <v>385.59</v>
-      </c>
-      <c r="F45" s="7">
-        <v>393.22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
-      <c r="A46" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="7">
+      <c r="K56" s="1">
+        <v>18.86</v>
+      </c>
+      <c r="L56" t="s">
+        <v>145</v>
+      </c>
+      <c r="M56">
+        <v>69501</v>
+      </c>
+      <c r="N56" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B57" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" t="s">
+        <v>49</v>
+      </c>
+      <c r="D57" t="s">
+        <v>81</v>
+      </c>
+      <c r="E57" t="s">
+        <v>93</v>
+      </c>
+      <c r="F57">
+        <v>20.85</v>
+      </c>
+      <c r="G57" t="s">
+        <v>94</v>
+      </c>
+      <c r="H57">
+        <v>1.48</v>
+      </c>
+      <c r="I57" s="1">
+        <v>30.86</v>
+      </c>
+      <c r="J57">
+        <v>1.51</v>
+      </c>
+      <c r="K57" s="1">
+        <v>31.48</v>
+      </c>
+      <c r="L57" t="s">
+        <v>146</v>
+      </c>
+      <c r="M57">
+        <v>187810</v>
+      </c>
+      <c r="N57" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B62" s="7">
+        <v>701.09</v>
+      </c>
+      <c r="C62" s="7">
+        <v>25</v>
+      </c>
+      <c r="D62" s="8">
+        <v>0.6509</v>
+      </c>
+      <c r="E62" s="7">
+        <v>456.33</v>
+      </c>
+      <c r="F62" s="7">
+        <v>463.35</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B63" s="7">
+        <v>513.4</v>
+      </c>
+      <c r="C63" s="7">
+        <v>17</v>
+      </c>
+      <c r="D63" s="8">
+        <v>1.4879</v>
+      </c>
+      <c r="E63" s="7">
+        <v>763.89</v>
+      </c>
+      <c r="F63" s="7">
+        <v>779.3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B64" s="7">
+        <v>436.61</v>
+      </c>
+      <c r="C64" s="7">
+        <v>11</v>
+      </c>
+      <c r="D64" s="8">
+        <v>1.4981</v>
+      </c>
+      <c r="E64" s="7">
+        <v>654.08</v>
+      </c>
+      <c r="F64" s="7">
+        <v>667.14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B65" s="7">
         <v>113.42</v>
       </c>
-      <c r="C46" s="7">
+      <c r="C65" s="7">
         <v>3</v>
       </c>
-      <c r="D46" s="8">
+      <c r="D65" s="8">
         <v>1.7519</v>
       </c>
-      <c r="E46" s="7">
+      <c r="E65" s="7">
         <v>198.7</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F65" s="7">
         <v>203.24</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
-      <c r="A47" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B47" s="10">
-        <v>1240.24</v>
-      </c>
-      <c r="C47" s="10">
-        <v>37</v>
-      </c>
-      <c r="D47" s="8"/>
-      <c r="E47" s="10">
-        <v>1410.57</v>
-      </c>
-      <c r="F47" s="10">
-        <v>1437.57</v>
+    <row r="66" spans="1:6">
+      <c r="A66" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B66" s="10">
+        <v>1764.52</v>
+      </c>
+      <c r="C66" s="10">
+        <v>56</v>
+      </c>
+      <c r="D66" s="8"/>
+      <c r="E66" s="10">
+        <v>2073</v>
+      </c>
+      <c r="F66" s="10">
+        <v>2113.03</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A60:F60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="149">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,75 +55,72 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1120 Пловдив Радиново</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1157 Пловдив Тракия</t>
-  </si>
-  <si>
-    <t>1158 Варна Чайка</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
-  </si>
-  <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>1911 O5 Варна</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1925 HW Trakia, 243 km. Sofia direc</t>
-  </si>
-  <si>
-    <t>1101 София Ихтиман</t>
-  </si>
-  <si>
-    <t>1193 Казанлък</t>
-  </si>
-  <si>
-    <t>1195 243 Тракия Езеро</t>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>Радиново</t>
+  </si>
+  <si>
+    <t>Варна Чайка</t>
+  </si>
+  <si>
+    <t>Тракия</t>
+  </si>
+  <si>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>АМ Тракия</t>
+  </si>
+  <si>
+    <t>Казанлък</t>
+  </si>
+  <si>
+    <t>Ихтиман</t>
+  </si>
+  <si>
+    <t>Тракия Езеро</t>
+  </si>
+  <si>
+    <t>В7721ВВ</t>
   </si>
   <si>
     <t>В1977ВМ</t>
   </si>
   <si>
-    <t>В7721ВВ</t>
+    <t>В0592ВТ</t>
   </si>
   <si>
     <t>В7242ВР</t>
   </si>
   <si>
-    <t>В0592ВТ</t>
-  </si>
-  <si>
     <t>В4814КВ</t>
   </si>
   <si>
     <t>СлужебнаОВ1</t>
   </si>
   <si>
+    <t>В2852РК</t>
+  </si>
+  <si>
+    <t>В7230ВР</t>
+  </si>
+  <si>
+    <t>В8979ВР</t>
+  </si>
+  <si>
     <t>В8974ВР</t>
   </si>
   <si>
     <t>В8985ВР</t>
   </si>
   <si>
-    <t>В7230ВР</t>
-  </si>
-  <si>
-    <t>В2852РК</t>
-  </si>
-  <si>
-    <t>В8979ВР</t>
-  </si>
-  <si>
     <t>В8978ВР</t>
   </si>
   <si>
@@ -139,30 +133,30 @@
     <t>В7224ВР</t>
   </si>
   <si>
+    <t>В7236ВР</t>
+  </si>
+  <si>
     <t>В7233ВР</t>
   </si>
   <si>
     <t>В6565КМ</t>
   </si>
   <si>
-    <t>В7236ВР</t>
-  </si>
-  <si>
     <t>В8853ХК</t>
   </si>
   <si>
+    <t>В6633СН</t>
+  </si>
+  <si>
+    <t>В0805ТР</t>
+  </si>
+  <si>
+    <t>В0591ВТ</t>
+  </si>
+  <si>
     <t>В7106НН</t>
   </si>
   <si>
-    <t>В6633СН</t>
-  </si>
-  <si>
-    <t>В0805ТР</t>
-  </si>
-  <si>
-    <t>В0591ВТ</t>
-  </si>
-  <si>
     <t>В9347РН</t>
   </si>
   <si>
@@ -172,57 +166,57 @@
     <t>В9337НК</t>
   </si>
   <si>
+    <t>В6511КС</t>
+  </si>
+  <si>
     <t>В1422РХ</t>
   </si>
   <si>
+    <t>В2802ТХ</t>
+  </si>
+  <si>
+    <t>В0595ВТ</t>
+  </si>
+  <si>
     <t>В5987РР</t>
   </si>
   <si>
-    <t>В6511КС</t>
-  </si>
-  <si>
-    <t>В2802ТХ</t>
-  </si>
-  <si>
     <t>В1392РК</t>
   </si>
   <si>
-    <t>В0595ВТ</t>
+    <t>78970155027721632</t>
   </si>
   <si>
     <t>78970155027722721</t>
   </si>
   <si>
-    <t>78970155027721632</t>
+    <t>78970155027722622</t>
   </si>
   <si>
     <t>78970155027721616</t>
   </si>
   <si>
-    <t>78970155027722622</t>
-  </si>
-  <si>
     <t>78970155027721483</t>
   </si>
   <si>
     <t>78970155027721764</t>
   </si>
   <si>
+    <t>78970155027721442</t>
+  </si>
+  <si>
+    <t>78970155027721574</t>
+  </si>
+  <si>
+    <t>78970155027721707</t>
+  </si>
+  <si>
     <t>78970155027721665</t>
   </si>
   <si>
     <t>78970155027721715</t>
   </si>
   <si>
-    <t>78970155027721574</t>
-  </si>
-  <si>
-    <t>78970155027721442</t>
-  </si>
-  <si>
-    <t>78970155027721707</t>
-  </si>
-  <si>
     <t>78970155027721699</t>
   </si>
   <si>
@@ -235,30 +229,30 @@
     <t>78970155027721566</t>
   </si>
   <si>
+    <t>78970155027721608</t>
+  </si>
+  <si>
     <t>78970155027721582</t>
   </si>
   <si>
     <t>78970155027721533</t>
   </si>
   <si>
-    <t>78970155027721608</t>
-  </si>
-  <si>
     <t>78970155027721749</t>
   </si>
   <si>
+    <t>78970155027721541</t>
+  </si>
+  <si>
+    <t>78970155027722663</t>
+  </si>
+  <si>
+    <t>78970155027722614</t>
+  </si>
+  <si>
     <t>78970155027721558</t>
   </si>
   <si>
-    <t>78970155027721541</t>
-  </si>
-  <si>
-    <t>78970155027722663</t>
-  </si>
-  <si>
-    <t>78970155027722614</t>
-  </si>
-  <si>
     <t>78970155027721731</t>
   </si>
   <si>
@@ -268,361 +262,187 @@
     <t>78970155027721723</t>
   </si>
   <si>
+    <t>78970155027721517</t>
+  </si>
+  <si>
     <t>78970155027722697</t>
   </si>
   <si>
+    <t>78970155027721434</t>
+  </si>
+  <si>
+    <t>78970155027722648</t>
+  </si>
+  <si>
     <t>78970155027721491</t>
   </si>
   <si>
-    <t>78970155027721517</t>
-  </si>
-  <si>
-    <t>78970155027721434</t>
-  </si>
-  <si>
     <t>78970155027722739</t>
   </si>
   <si>
-    <t>78970155027722648</t>
+    <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>EKO RACING 100</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>11:10:00</t>
-  </si>
-  <si>
-    <t>10:41:00</t>
-  </si>
-  <si>
-    <t>15:30:00</t>
-  </si>
-  <si>
-    <t>14:19:00</t>
-  </si>
-  <si>
-    <t>14:06:00</t>
-  </si>
-  <si>
-    <t>12:13:00</t>
-  </si>
-  <si>
-    <t>08:05:00</t>
-  </si>
-  <si>
-    <t>14:43:00</t>
-  </si>
-  <si>
-    <t>15:03:00</t>
-  </si>
-  <si>
-    <t>11:22:00</t>
-  </si>
-  <si>
-    <t>09:10:00</t>
-  </si>
-  <si>
-    <t>11:38:00</t>
-  </si>
-  <si>
-    <t>10:24:00</t>
-  </si>
-  <si>
-    <t>11:03:00</t>
-  </si>
-  <si>
-    <t>15:51:00</t>
-  </si>
-  <si>
-    <t>12:20:00</t>
-  </si>
-  <si>
-    <t>09:51:00</t>
-  </si>
-  <si>
-    <t>14:09:00</t>
-  </si>
-  <si>
-    <t>09:43:00</t>
-  </si>
-  <si>
-    <t>14:35:00</t>
-  </si>
-  <si>
-    <t>09:32:00</t>
-  </si>
-  <si>
-    <t>15:54:00</t>
-  </si>
-  <si>
-    <t>11:24:00</t>
-  </si>
-  <si>
-    <t>18:34:00</t>
-  </si>
-  <si>
-    <t>14:33:00</t>
-  </si>
-  <si>
-    <t>13:37:00</t>
-  </si>
-  <si>
-    <t>16:26:00</t>
-  </si>
-  <si>
-    <t>10:16:00</t>
-  </si>
-  <si>
-    <t>11:54:00</t>
-  </si>
-  <si>
-    <t>11:08:00</t>
-  </si>
-  <si>
-    <t>17:41:00</t>
-  </si>
-  <si>
-    <t>12:45:00</t>
-  </si>
-  <si>
-    <t>09:46:00</t>
-  </si>
-  <si>
-    <t>10:25:00</t>
-  </si>
-  <si>
-    <t>09:39:00</t>
-  </si>
-  <si>
-    <t>11:35:00</t>
-  </si>
-  <si>
-    <t>10:04:00</t>
-  </si>
-  <si>
-    <t>10:02:00</t>
-  </si>
-  <si>
-    <t>12:53:00</t>
-  </si>
-  <si>
-    <t>11:19:00</t>
-  </si>
-  <si>
-    <t>17:42:00</t>
-  </si>
-  <si>
-    <t>14:34:00</t>
-  </si>
-  <si>
-    <t>15:11:00</t>
-  </si>
-  <si>
-    <t>08:51:00</t>
-  </si>
-  <si>
-    <t>09:03:00</t>
-  </si>
-  <si>
-    <t>14:48:00</t>
-  </si>
-  <si>
-    <t>11:01:00</t>
-  </si>
-  <si>
-    <t>10:03:00</t>
-  </si>
-  <si>
-    <t>18:06:00</t>
-  </si>
-  <si>
-    <t>14:51:00</t>
-  </si>
-  <si>
-    <t>09:23:00</t>
-  </si>
-  <si>
-    <t>18:18:00</t>
-  </si>
-  <si>
-    <t>3233435057 3233435057</t>
-  </si>
-  <si>
-    <t>3233420126 3233420126</t>
-  </si>
-  <si>
-    <t>3233420379 3233420379</t>
-  </si>
-  <si>
-    <t>3233442505 3233442505</t>
-  </si>
-  <si>
-    <t>3233427177 3233427177</t>
-  </si>
-  <si>
-    <t>3233473075 3233473075</t>
-  </si>
-  <si>
-    <t>3233522219 3233522219</t>
-  </si>
-  <si>
-    <t>3233529160 3233529160</t>
-  </si>
-  <si>
-    <t>3233537334 3233537334</t>
-  </si>
-  <si>
-    <t>3233527240 3233527240</t>
-  </si>
-  <si>
-    <t>3233527425 3233527425</t>
-  </si>
-  <si>
-    <t>3233529187 3233529187</t>
-  </si>
-  <si>
-    <t>3233566380 3233566380</t>
-  </si>
-  <si>
-    <t>3233583569 3233583569</t>
-  </si>
-  <si>
-    <t>3233578496 3233578496</t>
-  </si>
-  <si>
-    <t>3233645483 3233645483</t>
-  </si>
-  <si>
-    <t>3233719634 3233719634</t>
-  </si>
-  <si>
-    <t>3233722445 3233722445</t>
-  </si>
-  <si>
-    <t>3233726056 3233726056</t>
-  </si>
-  <si>
-    <t>3233748714 3233748714</t>
-  </si>
-  <si>
-    <t>3233763379 3233763379</t>
-  </si>
-  <si>
-    <t>3233773236 3233773236</t>
-  </si>
-  <si>
-    <t>3233775906 3233775906</t>
-  </si>
-  <si>
-    <t>3233767297 3233767297</t>
-  </si>
-  <si>
-    <t>3233808438 3233808438</t>
-  </si>
-  <si>
-    <t>3233796161 3233796161</t>
-  </si>
-  <si>
-    <t>3233796517 3233796517</t>
-  </si>
-  <si>
-    <t>3233812501 3233812501</t>
-  </si>
-  <si>
-    <t>3233809063 3233809063</t>
-  </si>
-  <si>
-    <t>3233788882 3233788882</t>
-  </si>
-  <si>
-    <t>3233814729 3233814729</t>
-  </si>
-  <si>
-    <t>3233819165 3233819165</t>
-  </si>
-  <si>
-    <t>3233835180 3233835180</t>
-  </si>
-  <si>
-    <t>3233856178 3233856178</t>
-  </si>
-  <si>
-    <t>3233856268 3233856268</t>
-  </si>
-  <si>
-    <t>3233856973 3233856973</t>
-  </si>
-  <si>
-    <t>3233866140 3233866140</t>
-  </si>
-  <si>
-    <t>3233933493 3233933493</t>
-  </si>
-  <si>
-    <t>3233943601 3233943601</t>
-  </si>
-  <si>
-    <t>3233930421 3233930421</t>
-  </si>
-  <si>
-    <t>3233932678 3233932678</t>
-  </si>
-  <si>
-    <t>3233954359 3233954359</t>
-  </si>
-  <si>
-    <t>3234037906 3234037906</t>
-  </si>
-  <si>
-    <t>3234037917 3234037917</t>
-  </si>
-  <si>
-    <t>3234037918 3234037918</t>
-  </si>
-  <si>
-    <t>3234031196 3234031196</t>
-  </si>
-  <si>
-    <t>3234056130 3234056130</t>
-  </si>
-  <si>
-    <t>3234059480 3234059480</t>
-  </si>
-  <si>
-    <t>3234059912 3234059912</t>
-  </si>
-  <si>
-    <t>3234045594 3234045594</t>
-  </si>
-  <si>
-    <t>3234061090 3234061090</t>
-  </si>
-  <si>
-    <t>3234065138 3234065138</t>
-  </si>
-  <si>
-    <t>3234047067 3234047067</t>
-  </si>
-  <si>
-    <t>3234080170 3234080170</t>
-  </si>
-  <si>
-    <t>3234100359 3234100359</t>
-  </si>
-  <si>
-    <t>3234122400 3234122400</t>
+    <t>10:41</t>
+  </si>
+  <si>
+    <t>11:09</t>
+  </si>
+  <si>
+    <t>14:06</t>
+  </si>
+  <si>
+    <t>14:23</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>12:13</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>11:23</t>
+  </si>
+  <si>
+    <t>11:38</t>
+  </si>
+  <si>
+    <t>14:43</t>
+  </si>
+  <si>
+    <t>15:04</t>
+  </si>
+  <si>
+    <t>10:24</t>
+  </si>
+  <si>
+    <t>11:04</t>
+  </si>
+  <si>
+    <t>15:51</t>
+  </si>
+  <si>
+    <t>12:21</t>
+  </si>
+  <si>
+    <t>09:43</t>
+  </si>
+  <si>
+    <t>09:52</t>
+  </si>
+  <si>
+    <t>14:09</t>
+  </si>
+  <si>
+    <t>09:33</t>
+  </si>
+  <si>
+    <t>11:24</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>18:34</t>
+  </si>
+  <si>
+    <t>10:17</t>
+  </si>
+  <si>
+    <t>11:08</t>
+  </si>
+  <si>
+    <t>11:54</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>13:37</t>
+  </si>
+  <si>
+    <t>14:34</t>
+  </si>
+  <si>
+    <t>16:26</t>
+  </si>
+  <si>
+    <t>17:42</t>
+  </si>
+  <si>
+    <t>09:39</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>10:02</t>
+  </si>
+  <si>
+    <t>11:19</t>
+  </si>
+  <si>
+    <t>12:53</t>
+  </si>
+  <si>
+    <t>08:51</t>
+  </si>
+  <si>
+    <t>09:03</t>
+  </si>
+  <si>
+    <t>10:04</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>14:19</t>
+  </si>
+  <si>
+    <t>14:47</t>
+  </si>
+  <si>
+    <t>14:48</t>
+  </si>
+  <si>
+    <t>15:11</t>
+  </si>
+  <si>
+    <t>18:07</t>
+  </si>
+  <si>
+    <t>09:23</t>
+  </si>
+  <si>
+    <t>14:51</t>
+  </si>
+  <si>
+    <t>18:18</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОБЩИНА ВАРНА % 1 - АВТОПАРК</t>
@@ -1042,7 +862,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N66"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -1051,17 +871,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1101,99 +920,90 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F2">
-        <v>24.8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>94</v>
+        <v>39.01</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.53</v>
       </c>
       <c r="H2">
-        <v>1.78</v>
+        <v>59.69</v>
       </c>
       <c r="I2" s="1">
-        <v>44.14</v>
+        <v>1.56</v>
       </c>
       <c r="J2">
-        <v>1.82</v>
-      </c>
-      <c r="K2" s="1">
-        <v>45.14</v>
-      </c>
-      <c r="L2" t="s">
-        <v>95</v>
+        <v>60.86</v>
+      </c>
+      <c r="K2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L2">
+        <v>163974</v>
       </c>
       <c r="M2">
-        <v>315455</v>
-      </c>
-      <c r="N2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>142570</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46189</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F3">
-        <v>39.01</v>
-      </c>
-      <c r="G3" t="s">
-        <v>94</v>
+        <v>24.8</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.78</v>
       </c>
       <c r="H3">
-        <v>1.53</v>
+        <v>44.14</v>
       </c>
       <c r="I3" s="1">
-        <v>59.69</v>
+        <v>1.82</v>
       </c>
       <c r="J3">
-        <v>1.56</v>
-      </c>
-      <c r="K3" s="1">
-        <v>60.86</v>
-      </c>
-      <c r="L3" t="s">
-        <v>96</v>
+        <v>45.14</v>
+      </c>
+      <c r="K3" t="s">
+        <v>93</v>
+      </c>
+      <c r="L3">
+        <v>315455</v>
       </c>
       <c r="M3">
-        <v>163974</v>
-      </c>
-      <c r="N3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>209835</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46189</v>
       </c>
@@ -1201,43 +1011,40 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F4">
-        <v>35.4</v>
-      </c>
-      <c r="G4" t="s">
+        <v>28.13</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H4">
+        <v>18.57</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J4">
+        <v>18.85</v>
+      </c>
+      <c r="K4" t="s">
         <v>94</v>
       </c>
-      <c r="H4">
-        <v>0.66</v>
-      </c>
-      <c r="I4" s="1">
-        <v>23.36</v>
-      </c>
-      <c r="J4">
-        <v>0.67</v>
-      </c>
-      <c r="K4" s="1">
-        <v>23.72</v>
-      </c>
-      <c r="L4" t="s">
-        <v>97</v>
+      <c r="L4">
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>113913</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46189</v>
       </c>
@@ -1245,307 +1052,286 @@
         <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F5">
         <v>24.87</v>
       </c>
-      <c r="G5" t="s">
-        <v>94</v>
+      <c r="G5" s="1">
+        <v>1.78</v>
       </c>
       <c r="H5">
-        <v>1.78</v>
+        <v>44.27</v>
       </c>
       <c r="I5" s="1">
-        <v>44.27</v>
+        <v>1.82</v>
       </c>
       <c r="J5">
-        <v>1.82</v>
-      </c>
-      <c r="K5" s="1">
         <v>45.26</v>
       </c>
-      <c r="L5" t="s">
-        <v>98</v>
+      <c r="K5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L5">
+        <v>315721</v>
       </c>
       <c r="M5">
-        <v>315721</v>
-      </c>
-      <c r="N5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>248364</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="3">
         <v>46189</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F6">
-        <v>28.13</v>
-      </c>
-      <c r="G6" t="s">
-        <v>94</v>
+        <v>35.4</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.66</v>
       </c>
       <c r="H6">
-        <v>0.66</v>
+        <v>23.36</v>
       </c>
       <c r="I6" s="1">
-        <v>18.57</v>
+        <v>0.67</v>
       </c>
       <c r="J6">
-        <v>0.67</v>
-      </c>
-      <c r="K6" s="1">
-        <v>18.85</v>
-      </c>
-      <c r="L6" t="s">
-        <v>99</v>
+        <v>23.72</v>
+      </c>
+      <c r="K6" t="s">
+        <v>96</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>142734</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="3">
         <v>46190</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F7">
         <v>59.63</v>
       </c>
-      <c r="G7" t="s">
-        <v>94</v>
+      <c r="G7" s="1">
+        <v>1.56</v>
       </c>
       <c r="H7">
-        <v>1.56</v>
+        <v>93.02</v>
       </c>
       <c r="I7" s="1">
-        <v>93.02</v>
+        <v>1.59</v>
       </c>
       <c r="J7">
-        <v>1.59</v>
-      </c>
-      <c r="K7" s="1">
         <v>94.81</v>
       </c>
-      <c r="L7" t="s">
-        <v>100</v>
+      <c r="K7" t="s">
+        <v>97</v>
+      </c>
+      <c r="L7">
+        <v>495250</v>
       </c>
       <c r="M7">
-        <v>495250</v>
-      </c>
-      <c r="N7" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>143007</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3">
         <v>46191</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F8">
         <v>36.43</v>
       </c>
-      <c r="G8" t="s">
-        <v>94</v>
+      <c r="G8" s="1">
+        <v>1.55</v>
       </c>
       <c r="H8">
-        <v>1.55</v>
+        <v>56.47</v>
       </c>
       <c r="I8" s="1">
-        <v>56.47</v>
+        <v>1.58</v>
       </c>
       <c r="J8">
-        <v>1.58</v>
-      </c>
-      <c r="K8" s="1">
         <v>57.56</v>
       </c>
-      <c r="L8" t="s">
-        <v>101</v>
+      <c r="K8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L8">
+        <v>605</v>
       </c>
       <c r="M8">
-        <v>605</v>
-      </c>
-      <c r="N8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>201140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="3">
         <v>46191</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F9">
-        <v>29.88</v>
-      </c>
-      <c r="G9" t="s">
-        <v>94</v>
+        <v>60.01</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1.52</v>
       </c>
       <c r="H9">
-        <v>0.65</v>
+        <v>91.22</v>
       </c>
       <c r="I9" s="1">
-        <v>19.42</v>
+        <v>1.55</v>
       </c>
       <c r="J9">
-        <v>0.66</v>
-      </c>
-      <c r="K9" s="1">
-        <v>19.72</v>
-      </c>
-      <c r="L9" t="s">
-        <v>102</v>
+        <v>93.02</v>
+      </c>
+      <c r="K9" t="s">
+        <v>99</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>114757</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="3">
         <v>46191</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F10">
-        <v>29.12</v>
-      </c>
-      <c r="G10" t="s">
-        <v>94</v>
+        <v>22.02</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.65</v>
       </c>
       <c r="H10">
-        <v>0.65</v>
+        <v>14.31</v>
       </c>
       <c r="I10" s="1">
-        <v>18.93</v>
+        <v>0.66</v>
       </c>
       <c r="J10">
-        <v>0.66</v>
-      </c>
-      <c r="K10" s="1">
-        <v>19.22</v>
-      </c>
-      <c r="L10" t="s">
-        <v>103</v>
+        <v>14.53</v>
+      </c>
+      <c r="K10" t="s">
+        <v>100</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>42300</v>
-      </c>
-      <c r="N10" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>114831</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="3">
         <v>46191</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F11">
-        <v>22.02</v>
-      </c>
-      <c r="G11" t="s">
-        <v>94</v>
+        <v>29.67</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0.65</v>
       </c>
       <c r="H11">
-        <v>0.65</v>
+        <v>19.29</v>
       </c>
       <c r="I11" s="1">
-        <v>14.31</v>
+        <v>0.66</v>
       </c>
       <c r="J11">
-        <v>0.66</v>
-      </c>
-      <c r="K11" s="1">
-        <v>14.53</v>
-      </c>
-      <c r="L11" t="s">
-        <v>104</v>
+        <v>19.58</v>
+      </c>
+      <c r="K11" t="s">
+        <v>101</v>
+      </c>
+      <c r="L11">
+        <v>38395</v>
       </c>
       <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>114840</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="3">
         <v>46191</v>
       </c>
@@ -1553,263 +1339,245 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F12">
-        <v>60.01</v>
-      </c>
-      <c r="G12" t="s">
-        <v>94</v>
+        <v>29.88</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.65</v>
       </c>
       <c r="H12">
-        <v>1.52</v>
+        <v>19.42</v>
       </c>
       <c r="I12" s="1">
-        <v>91.22</v>
+        <v>0.66</v>
       </c>
       <c r="J12">
-        <v>1.55</v>
-      </c>
-      <c r="K12" s="1">
-        <v>93.02</v>
-      </c>
-      <c r="L12" t="s">
-        <v>105</v>
+        <v>19.72</v>
+      </c>
+      <c r="K12" t="s">
+        <v>102</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>201384</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="3">
         <v>46191</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F13">
-        <v>29.67</v>
-      </c>
-      <c r="G13" t="s">
-        <v>94</v>
+        <v>29.12</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0.65</v>
       </c>
       <c r="H13">
-        <v>0.65</v>
+        <v>18.93</v>
       </c>
       <c r="I13" s="1">
-        <v>19.29</v>
+        <v>0.66</v>
       </c>
       <c r="J13">
-        <v>0.66</v>
-      </c>
-      <c r="K13" s="1">
-        <v>19.58</v>
-      </c>
-      <c r="L13" t="s">
-        <v>106</v>
+        <v>19.22</v>
+      </c>
+      <c r="K13" t="s">
+        <v>103</v>
+      </c>
+      <c r="L13">
+        <v>42300</v>
       </c>
       <c r="M13">
-        <v>38395</v>
-      </c>
-      <c r="N13" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+        <v>220814</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="3">
         <v>46192</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F14">
         <v>31.38</v>
       </c>
-      <c r="G14" t="s">
-        <v>94</v>
+      <c r="G14" s="1">
+        <v>0.65</v>
       </c>
       <c r="H14">
-        <v>0.65</v>
+        <v>20.4</v>
       </c>
       <c r="I14" s="1">
-        <v>20.4</v>
+        <v>0.66</v>
       </c>
       <c r="J14">
-        <v>0.66</v>
-      </c>
-      <c r="K14" s="1">
         <v>20.71</v>
       </c>
-      <c r="L14" t="s">
-        <v>107</v>
+      <c r="K14" t="s">
+        <v>104</v>
+      </c>
+      <c r="L14">
+        <v>97700</v>
       </c>
       <c r="M14">
-        <v>97700</v>
-      </c>
-      <c r="N14" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+        <v>143711</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="3">
         <v>46192</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F15">
         <v>19.97</v>
       </c>
-      <c r="G15" t="s">
-        <v>94</v>
+      <c r="G15" s="1">
+        <v>1.51</v>
       </c>
       <c r="H15">
-        <v>1.51</v>
+        <v>30.15</v>
       </c>
       <c r="I15" s="1">
-        <v>30.15</v>
+        <v>1.54</v>
       </c>
       <c r="J15">
-        <v>1.54</v>
-      </c>
-      <c r="K15" s="1">
         <v>30.75</v>
       </c>
-      <c r="L15" t="s">
-        <v>108</v>
+      <c r="K15" t="s">
+        <v>105</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+        <v>221172</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="3">
         <v>46192</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F16">
         <v>33.26</v>
       </c>
-      <c r="G16" t="s">
-        <v>94</v>
+      <c r="G16" s="1">
+        <v>1.51</v>
       </c>
       <c r="H16">
-        <v>1.51</v>
+        <v>50.22</v>
       </c>
       <c r="I16" s="1">
-        <v>50.22</v>
+        <v>1.54</v>
       </c>
       <c r="J16">
-        <v>1.54</v>
-      </c>
-      <c r="K16" s="1">
         <v>51.22</v>
       </c>
-      <c r="L16" t="s">
-        <v>109</v>
+      <c r="K16" t="s">
+        <v>106</v>
+      </c>
+      <c r="L16">
+        <v>53415</v>
       </c>
       <c r="M16">
-        <v>53415</v>
-      </c>
-      <c r="N16" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+        <v>118759</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="3">
         <v>46193</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F17">
         <v>10</v>
       </c>
-      <c r="G17" t="s">
-        <v>94</v>
+      <c r="G17" s="1">
+        <v>1.5</v>
       </c>
       <c r="H17">
-        <v>1.5</v>
+        <v>15</v>
       </c>
       <c r="I17" s="1">
-        <v>15</v>
+        <v>1.53</v>
       </c>
       <c r="J17">
-        <v>1.53</v>
-      </c>
-      <c r="K17" s="1">
         <v>15.3</v>
       </c>
-      <c r="L17" t="s">
-        <v>110</v>
+      <c r="K17" t="s">
+        <v>107</v>
+      </c>
+      <c r="L17">
+        <v>69187</v>
       </c>
       <c r="M17">
-        <v>69187</v>
-      </c>
-      <c r="N17" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+        <v>276897</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="3">
         <v>46195</v>
       </c>
@@ -1817,175 +1585,163 @@
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F18">
-        <v>15.42</v>
-      </c>
-      <c r="G18" t="s">
-        <v>94</v>
+        <v>27.42</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.65</v>
       </c>
       <c r="H18">
-        <v>0.65</v>
+        <v>17.82</v>
       </c>
       <c r="I18" s="1">
-        <v>10.02</v>
+        <v>0.66</v>
       </c>
       <c r="J18">
-        <v>0.66</v>
-      </c>
-      <c r="K18" s="1">
-        <v>10.18</v>
-      </c>
-      <c r="L18" t="s">
-        <v>111</v>
+        <v>18.1</v>
+      </c>
+      <c r="K18" t="s">
+        <v>108</v>
+      </c>
+      <c r="L18">
+        <v>76940</v>
       </c>
       <c r="M18">
-        <v>76443</v>
-      </c>
-      <c r="N18" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+        <v>277322</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="3">
         <v>46195</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F19">
-        <v>25</v>
-      </c>
-      <c r="G19" t="s">
-        <v>94</v>
+        <v>15.42</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0.65</v>
       </c>
       <c r="H19">
-        <v>1.48</v>
+        <v>10.02</v>
       </c>
       <c r="I19" s="1">
-        <v>37</v>
+        <v>0.66</v>
       </c>
       <c r="J19">
-        <v>1.51</v>
-      </c>
-      <c r="K19" s="1">
-        <v>37.75</v>
-      </c>
-      <c r="L19" t="s">
-        <v>112</v>
+        <v>10.18</v>
+      </c>
+      <c r="K19" t="s">
+        <v>109</v>
+      </c>
+      <c r="L19">
+        <v>76443</v>
       </c>
       <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+        <v>222276</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="3">
         <v>46195</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F20">
-        <v>27.42</v>
-      </c>
-      <c r="G20" t="s">
-        <v>94</v>
+        <v>25</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1.48</v>
       </c>
       <c r="H20">
-        <v>0.65</v>
+        <v>37</v>
       </c>
       <c r="I20" s="1">
-        <v>17.82</v>
+        <v>1.51</v>
       </c>
       <c r="J20">
-        <v>0.66</v>
-      </c>
-      <c r="K20" s="1">
-        <v>18.1</v>
-      </c>
-      <c r="L20" t="s">
-        <v>113</v>
+        <v>37.75</v>
+      </c>
+      <c r="K20" t="s">
+        <v>110</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>76940</v>
-      </c>
-      <c r="N20" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+        <v>117107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="3">
         <v>46196</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E21" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F21">
-        <v>31.56</v>
-      </c>
-      <c r="G21" t="s">
-        <v>94</v>
+        <v>63.75</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1.73</v>
       </c>
       <c r="H21">
-        <v>0.65</v>
+        <v>110.29</v>
       </c>
       <c r="I21" s="1">
-        <v>20.51</v>
+        <v>1.77</v>
       </c>
       <c r="J21">
-        <v>0.66</v>
-      </c>
-      <c r="K21" s="1">
-        <v>20.83</v>
-      </c>
-      <c r="L21" t="s">
-        <v>114</v>
+        <v>112.84</v>
+      </c>
+      <c r="K21" t="s">
+        <v>111</v>
+      </c>
+      <c r="L21">
+        <v>316200</v>
       </c>
       <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+        <v>222826</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="3">
         <v>46196</v>
       </c>
@@ -1993,263 +1749,245 @@
         <v>19</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F22">
-        <v>63.75</v>
-      </c>
-      <c r="G22" t="s">
-        <v>94</v>
+        <v>56.2</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1.49</v>
       </c>
       <c r="H22">
-        <v>1.73</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="I22" s="1">
-        <v>110.29</v>
+        <v>1.52</v>
       </c>
       <c r="J22">
-        <v>1.77</v>
-      </c>
-      <c r="K22" s="1">
-        <v>112.84</v>
-      </c>
-      <c r="L22" t="s">
-        <v>115</v>
+        <v>85.42</v>
+      </c>
+      <c r="K22" t="s">
+        <v>112</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>316200</v>
-      </c>
-      <c r="N22" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+        <v>277661</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="3">
         <v>46196</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F23">
-        <v>55.78</v>
-      </c>
-      <c r="G23" t="s">
-        <v>94</v>
+        <v>31.56</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0.65</v>
       </c>
       <c r="H23">
-        <v>1.48</v>
+        <v>20.51</v>
       </c>
       <c r="I23" s="1">
-        <v>82.55</v>
+        <v>0.66</v>
       </c>
       <c r="J23">
-        <v>1.51</v>
-      </c>
-      <c r="K23" s="1">
-        <v>84.23</v>
-      </c>
-      <c r="L23" t="s">
-        <v>116</v>
+        <v>20.83</v>
+      </c>
+      <c r="K23" t="s">
+        <v>113</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+        <v>144927</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="3">
         <v>46196</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="E24" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F24">
-        <v>56.2</v>
-      </c>
-      <c r="G24" t="s">
-        <v>94</v>
+        <v>55.78</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1.48</v>
       </c>
       <c r="H24">
-        <v>1.49</v>
+        <v>82.55</v>
       </c>
       <c r="I24" s="1">
-        <v>83.73999999999999</v>
+        <v>1.51</v>
       </c>
       <c r="J24">
-        <v>1.52</v>
-      </c>
-      <c r="K24" s="1">
-        <v>85.42</v>
-      </c>
-      <c r="L24" t="s">
-        <v>117</v>
+        <v>84.23</v>
+      </c>
+      <c r="K24" t="s">
+        <v>114</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+        <v>223076</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="3">
         <v>46196</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F25">
         <v>27.83</v>
       </c>
-      <c r="G25" t="s">
-        <v>94</v>
+      <c r="G25" s="1">
+        <v>0.65</v>
       </c>
       <c r="H25">
-        <v>0.65</v>
+        <v>18.09</v>
       </c>
       <c r="I25" s="1">
-        <v>18.09</v>
+        <v>0.66</v>
       </c>
       <c r="J25">
-        <v>0.66</v>
-      </c>
-      <c r="K25" s="1">
         <v>18.37</v>
       </c>
-      <c r="L25" t="s">
-        <v>118</v>
+      <c r="K25" t="s">
+        <v>115</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+        <v>226743</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="3">
         <v>46197</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E26" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F26">
-        <v>32.73</v>
-      </c>
-      <c r="G26" t="s">
-        <v>94</v>
+        <v>30</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1.48</v>
       </c>
       <c r="H26">
-        <v>0.65</v>
+        <v>44.4</v>
       </c>
       <c r="I26" s="1">
-        <v>21.27</v>
+        <v>1.51</v>
       </c>
       <c r="J26">
-        <v>0.66</v>
-      </c>
-      <c r="K26" s="1">
-        <v>21.6</v>
-      </c>
-      <c r="L26" t="s">
-        <v>119</v>
+        <v>45.3</v>
+      </c>
+      <c r="K26" t="s">
+        <v>116</v>
+      </c>
+      <c r="L26">
+        <v>476400</v>
       </c>
       <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+        <v>223316</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="3">
         <v>46197</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D27" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E27" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F27">
-        <v>56.97</v>
-      </c>
-      <c r="G27" t="s">
-        <v>94</v>
+        <v>31.14</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0.65</v>
       </c>
       <c r="H27">
-        <v>1.48</v>
+        <v>20.24</v>
       </c>
       <c r="I27" s="1">
-        <v>84.31999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="J27">
-        <v>1.51</v>
-      </c>
-      <c r="K27" s="1">
-        <v>86.02</v>
-      </c>
-      <c r="L27" t="s">
-        <v>120</v>
+        <v>20.55</v>
+      </c>
+      <c r="K27" t="s">
+        <v>117</v>
+      </c>
+      <c r="L27">
+        <v>55116</v>
       </c>
       <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+        <v>205352</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="3">
         <v>46197</v>
       </c>
@@ -2257,43 +1995,40 @@
         <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E28" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F28">
-        <v>21.02</v>
-      </c>
-      <c r="G28" t="s">
-        <v>94</v>
+        <v>31.75</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1.48</v>
       </c>
       <c r="H28">
-        <v>0.65</v>
+        <v>46.99</v>
       </c>
       <c r="I28" s="1">
-        <v>13.66</v>
+        <v>1.51</v>
       </c>
       <c r="J28">
-        <v>0.66</v>
-      </c>
-      <c r="K28" s="1">
-        <v>13.87</v>
-      </c>
-      <c r="L28" t="s">
-        <v>121</v>
+        <v>47.94</v>
+      </c>
+      <c r="K28" t="s">
+        <v>118</v>
+      </c>
+      <c r="L28">
+        <v>41001</v>
       </c>
       <c r="M28">
-        <v>77072</v>
-      </c>
-      <c r="N28" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+        <v>118173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="3">
         <v>46197</v>
       </c>
@@ -2301,307 +2036,286 @@
         <v>19</v>
       </c>
       <c r="C29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F29">
-        <v>30</v>
-      </c>
-      <c r="G29" t="s">
-        <v>94</v>
+        <v>33.26</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0.65</v>
       </c>
       <c r="H29">
-        <v>1.48</v>
+        <v>21.62</v>
       </c>
       <c r="I29" s="1">
-        <v>44.4</v>
+        <v>0.66</v>
       </c>
       <c r="J29">
-        <v>1.51</v>
-      </c>
-      <c r="K29" s="1">
-        <v>45.3</v>
-      </c>
-      <c r="L29" t="s">
-        <v>122</v>
+        <v>21.95</v>
+      </c>
+      <c r="K29" t="s">
+        <v>119</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>476400</v>
-      </c>
-      <c r="N29" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+        <v>277959</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="3">
         <v>46197</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E30" t="s">
         <v>91</v>
       </c>
       <c r="F30">
-        <v>31.75</v>
-      </c>
-      <c r="G30" t="s">
-        <v>94</v>
+        <v>56.97</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1.48</v>
       </c>
       <c r="H30">
-        <v>1.48</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="I30" s="1">
-        <v>46.99</v>
+        <v>1.51</v>
       </c>
       <c r="J30">
-        <v>1.51</v>
-      </c>
-      <c r="K30" s="1">
-        <v>47.94</v>
-      </c>
-      <c r="L30" t="s">
-        <v>123</v>
+        <v>86.02</v>
+      </c>
+      <c r="K30" t="s">
+        <v>120</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>41001</v>
-      </c>
-      <c r="N30" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+        <v>145209</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="3">
         <v>46197</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D31" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="E31" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F31">
-        <v>31.14</v>
-      </c>
-      <c r="G31" t="s">
-        <v>94</v>
+        <v>32.73</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0.65</v>
       </c>
       <c r="H31">
-        <v>0.65</v>
+        <v>21.27</v>
       </c>
       <c r="I31" s="1">
-        <v>20.24</v>
+        <v>0.66</v>
       </c>
       <c r="J31">
-        <v>0.66</v>
-      </c>
-      <c r="K31" s="1">
-        <v>20.55</v>
-      </c>
-      <c r="L31" t="s">
-        <v>124</v>
+        <v>21.6</v>
+      </c>
+      <c r="K31" t="s">
+        <v>121</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>55116</v>
-      </c>
-      <c r="N31" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+        <v>171772</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="3">
         <v>46197</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D32" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E32" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F32">
-        <v>21.29</v>
-      </c>
-      <c r="G32" t="s">
-        <v>94</v>
+        <v>21.02</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0.65</v>
       </c>
       <c r="H32">
-        <v>0.65</v>
+        <v>13.66</v>
       </c>
       <c r="I32" s="1">
-        <v>13.84</v>
+        <v>0.66</v>
       </c>
       <c r="J32">
-        <v>0.66</v>
-      </c>
-      <c r="K32" s="1">
-        <v>14.05</v>
-      </c>
-      <c r="L32" t="s">
-        <v>125</v>
+        <v>13.87</v>
+      </c>
+      <c r="K32" t="s">
+        <v>122</v>
+      </c>
+      <c r="L32">
+        <v>77072</v>
       </c>
       <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
+        <v>145299</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="3">
         <v>46197</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D33" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E33" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F33">
-        <v>33.26</v>
-      </c>
-      <c r="G33" t="s">
-        <v>94</v>
+        <v>21.29</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0.65</v>
       </c>
       <c r="H33">
-        <v>0.65</v>
+        <v>13.84</v>
       </c>
       <c r="I33" s="1">
-        <v>21.62</v>
+        <v>0.66</v>
       </c>
       <c r="J33">
-        <v>0.66</v>
-      </c>
-      <c r="K33" s="1">
-        <v>21.95</v>
-      </c>
-      <c r="L33" t="s">
-        <v>126</v>
+        <v>14.05</v>
+      </c>
+      <c r="K33" t="s">
+        <v>123</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
       </c>
       <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+        <v>268637</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="3">
         <v>46198</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D34" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F34">
-        <v>29.02</v>
-      </c>
-      <c r="G34" t="s">
-        <v>94</v>
+        <v>45.97</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1.48</v>
       </c>
       <c r="H34">
-        <v>0.65</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="I34" s="1">
-        <v>18.86</v>
+        <v>1.51</v>
       </c>
       <c r="J34">
-        <v>0.66</v>
-      </c>
-      <c r="K34" s="1">
-        <v>19.15</v>
-      </c>
-      <c r="L34" t="s">
-        <v>127</v>
+        <v>69.41</v>
+      </c>
+      <c r="K34" t="s">
+        <v>124</v>
+      </c>
+      <c r="L34">
+        <v>187520</v>
       </c>
       <c r="M34">
-        <v>97950</v>
-      </c>
-      <c r="N34" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
+        <v>223749</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="3">
         <v>46198</v>
       </c>
       <c r="B35" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F35">
-        <v>31.48</v>
-      </c>
-      <c r="G35" t="s">
-        <v>94</v>
+        <v>29.02</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0.65</v>
       </c>
       <c r="H35">
-        <v>0.65</v>
+        <v>18.86</v>
       </c>
       <c r="I35" s="1">
-        <v>20.46</v>
+        <v>0.66</v>
       </c>
       <c r="J35">
-        <v>0.66</v>
-      </c>
-      <c r="K35" s="1">
-        <v>20.78</v>
-      </c>
-      <c r="L35" t="s">
-        <v>128</v>
+        <v>19.15</v>
+      </c>
+      <c r="K35" t="s">
+        <v>125</v>
+      </c>
+      <c r="L35">
+        <v>97950</v>
       </c>
       <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+        <v>145500</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="3">
         <v>46198</v>
       </c>
@@ -2609,439 +2323,409 @@
         <v>19</v>
       </c>
       <c r="C36" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E36" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F36">
-        <v>45.97</v>
-      </c>
-      <c r="G36" t="s">
-        <v>94</v>
+        <v>29.11</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0.65</v>
       </c>
       <c r="H36">
-        <v>1.48</v>
+        <v>18.92</v>
       </c>
       <c r="I36" s="1">
-        <v>68.04000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="J36">
-        <v>1.51</v>
-      </c>
-      <c r="K36" s="1">
-        <v>69.41</v>
-      </c>
-      <c r="L36" t="s">
-        <v>129</v>
+        <v>19.21</v>
+      </c>
+      <c r="K36" t="s">
+        <v>126</v>
+      </c>
+      <c r="L36">
+        <v>69298</v>
       </c>
       <c r="M36">
-        <v>187520</v>
-      </c>
-      <c r="N36" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
+        <v>278200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="3">
         <v>46198</v>
       </c>
       <c r="B37" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E37" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F37">
-        <v>29.95</v>
-      </c>
-      <c r="G37" t="s">
-        <v>94</v>
+        <v>31.48</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0.65</v>
       </c>
       <c r="H37">
-        <v>0.65</v>
+        <v>20.46</v>
       </c>
       <c r="I37" s="1">
-        <v>19.47</v>
+        <v>0.66</v>
       </c>
       <c r="J37">
-        <v>0.66</v>
-      </c>
-      <c r="K37" s="1">
-        <v>19.77</v>
-      </c>
-      <c r="L37" t="s">
-        <v>130</v>
+        <v>20.78</v>
+      </c>
+      <c r="K37" t="s">
+        <v>104</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
       </c>
       <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
+        <v>223781</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="3">
         <v>46198</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D38" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E38" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F38">
-        <v>29.11</v>
-      </c>
-      <c r="G38" t="s">
-        <v>94</v>
+        <v>29.96</v>
+      </c>
+      <c r="G38" s="1">
+        <v>0.65</v>
       </c>
       <c r="H38">
-        <v>0.65</v>
+        <v>19.47</v>
       </c>
       <c r="I38" s="1">
-        <v>18.92</v>
+        <v>0.66</v>
       </c>
       <c r="J38">
-        <v>0.66</v>
-      </c>
-      <c r="K38" s="1">
-        <v>19.21</v>
-      </c>
-      <c r="L38" t="s">
-        <v>131</v>
+        <v>19.77</v>
+      </c>
+      <c r="K38" t="s">
+        <v>127</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>69298</v>
-      </c>
-      <c r="N38" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+        <v>118703</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="3">
         <v>46199</v>
       </c>
       <c r="B39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D39" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E39" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F39">
         <v>17</v>
       </c>
-      <c r="G39" t="s">
-        <v>94</v>
+      <c r="G39" s="1">
+        <v>1.47</v>
       </c>
       <c r="H39">
-        <v>1.47</v>
+        <v>24.99</v>
       </c>
       <c r="I39" s="1">
-        <v>24.99</v>
+        <v>1.5</v>
       </c>
       <c r="J39">
-        <v>1.5</v>
-      </c>
-      <c r="K39" s="1">
         <v>25.5</v>
       </c>
-      <c r="L39" t="s">
-        <v>132</v>
+      <c r="K39" t="s">
+        <v>128</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
       </c>
       <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
+        <v>224285</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="3">
         <v>46199</v>
       </c>
       <c r="B40" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C40" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D40" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E40" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F40">
-        <v>30.16</v>
-      </c>
-      <c r="G40" t="s">
-        <v>94</v>
+        <v>10</v>
+      </c>
+      <c r="G40" s="1">
+        <v>1.47</v>
       </c>
       <c r="H40">
-        <v>1.47</v>
+        <v>14.7</v>
       </c>
       <c r="I40" s="1">
-        <v>44.34</v>
+        <v>1.5</v>
       </c>
       <c r="J40">
-        <v>1.5</v>
-      </c>
-      <c r="K40" s="1">
-        <v>45.24</v>
-      </c>
-      <c r="L40" t="s">
-        <v>133</v>
+        <v>15</v>
+      </c>
+      <c r="K40" t="s">
+        <v>129</v>
+      </c>
+      <c r="L40">
+        <v>77080</v>
       </c>
       <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+        <v>119269</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="3">
         <v>46199</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E41" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F41">
-        <v>10</v>
-      </c>
-      <c r="G41" t="s">
-        <v>94</v>
+        <v>30.16</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1.47</v>
       </c>
       <c r="H41">
-        <v>1.47</v>
+        <v>44.34</v>
       </c>
       <c r="I41" s="1">
-        <v>14.7</v>
+        <v>1.5</v>
       </c>
       <c r="J41">
-        <v>1.5</v>
-      </c>
-      <c r="K41" s="1">
-        <v>15</v>
-      </c>
-      <c r="L41" t="s">
-        <v>134</v>
+        <v>45.24</v>
+      </c>
+      <c r="K41" t="s">
+        <v>130</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>77080</v>
-      </c>
-      <c r="N41" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+        <v>224430</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="3">
         <v>46199</v>
       </c>
       <c r="B42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D42" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E42" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F42">
         <v>49.47</v>
       </c>
-      <c r="G42" t="s">
-        <v>94</v>
+      <c r="G42" s="1">
+        <v>1.47</v>
       </c>
       <c r="H42">
-        <v>1.47</v>
+        <v>72.72</v>
       </c>
       <c r="I42" s="1">
-        <v>72.72</v>
+        <v>1.5</v>
       </c>
       <c r="J42">
-        <v>1.5</v>
-      </c>
-      <c r="K42" s="1">
         <v>74.2</v>
       </c>
-      <c r="L42" t="s">
-        <v>135</v>
+      <c r="K42" t="s">
+        <v>123</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
       </c>
       <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
+        <v>119534</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="3">
         <v>46200</v>
       </c>
       <c r="B43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E43" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F43">
         <v>49.28</v>
       </c>
-      <c r="G43" t="s">
-        <v>94</v>
+      <c r="G43" s="1">
+        <v>1.48</v>
       </c>
       <c r="H43">
-        <v>1.48</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="I43" s="1">
-        <v>72.93000000000001</v>
+        <v>1.51</v>
       </c>
       <c r="J43">
-        <v>1.51</v>
-      </c>
-      <c r="K43" s="1">
         <v>74.41</v>
       </c>
-      <c r="L43" t="s">
-        <v>97</v>
+      <c r="K43" t="s">
+        <v>96</v>
+      </c>
+      <c r="L43">
+        <v>3172</v>
       </c>
       <c r="M43">
-        <v>3172</v>
-      </c>
-      <c r="N43" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
+        <v>119759</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="3">
         <v>46202</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D44" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E44" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F44">
-        <v>27.49</v>
-      </c>
-      <c r="G44" t="s">
-        <v>94</v>
+        <v>45.82</v>
+      </c>
+      <c r="G44" s="1">
+        <v>1.48</v>
       </c>
       <c r="H44">
-        <v>1.48</v>
+        <v>67.81</v>
       </c>
       <c r="I44" s="1">
-        <v>40.69</v>
+        <v>1.51</v>
       </c>
       <c r="J44">
-        <v>1.51</v>
-      </c>
-      <c r="K44" s="1">
-        <v>41.51</v>
-      </c>
-      <c r="L44" t="s">
-        <v>136</v>
+        <v>69.19</v>
+      </c>
+      <c r="K44" t="s">
+        <v>131</v>
+      </c>
+      <c r="L44">
+        <v>187600</v>
       </c>
       <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
+        <v>225349</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="3">
         <v>46202</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E45" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F45">
-        <v>23.98</v>
-      </c>
-      <c r="G45" t="s">
-        <v>94</v>
+        <v>20</v>
+      </c>
+      <c r="G45" s="1">
+        <v>1.47</v>
       </c>
       <c r="H45">
-        <v>0.65</v>
+        <v>29.4</v>
       </c>
       <c r="I45" s="1">
-        <v>15.59</v>
+        <v>1.5</v>
       </c>
       <c r="J45">
-        <v>0.66</v>
-      </c>
-      <c r="K45" s="1">
-        <v>15.83</v>
-      </c>
-      <c r="L45" t="s">
-        <v>137</v>
+        <v>30</v>
+      </c>
+      <c r="K45" t="s">
+        <v>132</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
       </c>
       <c r="M45">
-        <v>34789</v>
-      </c>
-      <c r="N45" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
+        <v>225351</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="3">
         <v>46202</v>
       </c>
@@ -3049,87 +2733,81 @@
         <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D46" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="E46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F46">
-        <v>10</v>
-      </c>
-      <c r="G46" t="s">
-        <v>94</v>
+        <v>21.82</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0.65</v>
       </c>
       <c r="H46">
-        <v>1.47</v>
+        <v>14.18</v>
       </c>
       <c r="I46" s="1">
-        <v>14.7</v>
+        <v>0.66</v>
       </c>
       <c r="J46">
-        <v>1.5</v>
-      </c>
-      <c r="K46" s="1">
-        <v>15</v>
-      </c>
-      <c r="L46" t="s">
-        <v>137</v>
+        <v>14.4</v>
+      </c>
+      <c r="K46" t="s">
+        <v>133</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
       </c>
       <c r="M46">
-        <v>34789</v>
-      </c>
-      <c r="N46" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
+        <v>120875</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="3">
         <v>46202</v>
       </c>
       <c r="B47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D47" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E47" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F47">
-        <v>45.82</v>
-      </c>
-      <c r="G47" t="s">
-        <v>94</v>
+        <v>39.98</v>
+      </c>
+      <c r="G47" s="1">
+        <v>1.47</v>
       </c>
       <c r="H47">
-        <v>1.48</v>
+        <v>58.77</v>
       </c>
       <c r="I47" s="1">
-        <v>67.81</v>
+        <v>1.5</v>
       </c>
       <c r="J47">
-        <v>1.51</v>
-      </c>
-      <c r="K47" s="1">
-        <v>69.19</v>
-      </c>
-      <c r="L47" t="s">
-        <v>138</v>
+        <v>59.97</v>
+      </c>
+      <c r="K47" t="s">
+        <v>134</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
       </c>
       <c r="M47">
-        <v>187600</v>
-      </c>
-      <c r="N47" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14">
+        <v>225435</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="3">
         <v>46202</v>
       </c>
@@ -3137,441 +2815,411 @@
         <v>19</v>
       </c>
       <c r="C48" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="D48" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E48" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F48">
-        <v>20</v>
-      </c>
-      <c r="G48" t="s">
-        <v>94</v>
+        <v>32.01</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1.47</v>
       </c>
       <c r="H48">
-        <v>1.47</v>
+        <v>47.05</v>
       </c>
       <c r="I48" s="1">
-        <v>29.4</v>
+        <v>1.5</v>
       </c>
       <c r="J48">
-        <v>1.5</v>
-      </c>
-      <c r="K48" s="1">
-        <v>30</v>
-      </c>
-      <c r="L48" t="s">
-        <v>139</v>
+        <v>48.02</v>
+      </c>
+      <c r="K48" t="s">
+        <v>135</v>
+      </c>
+      <c r="L48">
+        <v>53915</v>
       </c>
       <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
+        <v>279325</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="3">
         <v>46202</v>
       </c>
       <c r="B49" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D49" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E49" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F49">
-        <v>19.97</v>
-      </c>
-      <c r="G49" t="s">
-        <v>94</v>
+        <v>27.49</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1.48</v>
       </c>
       <c r="H49">
-        <v>1.48</v>
+        <v>40.69</v>
       </c>
       <c r="I49" s="1">
-        <v>29.56</v>
+        <v>1.51</v>
       </c>
       <c r="J49">
-        <v>1.51</v>
-      </c>
-      <c r="K49" s="1">
-        <v>30.15</v>
-      </c>
-      <c r="L49" t="s">
-        <v>140</v>
+        <v>41.51</v>
+      </c>
+      <c r="K49" t="s">
+        <v>121</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
       </c>
       <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
+        <v>146517</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="3">
         <v>46202</v>
       </c>
       <c r="B50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C50" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D50" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E50" t="s">
         <v>91</v>
       </c>
       <c r="F50">
-        <v>39.98</v>
-      </c>
-      <c r="G50" t="s">
-        <v>94</v>
+        <v>19.97</v>
+      </c>
+      <c r="G50" s="1">
+        <v>1.48</v>
       </c>
       <c r="H50">
-        <v>1.47</v>
+        <v>29.56</v>
       </c>
       <c r="I50" s="1">
-        <v>58.77</v>
+        <v>1.51</v>
       </c>
       <c r="J50">
-        <v>1.5</v>
-      </c>
-      <c r="K50" s="1">
-        <v>59.97</v>
-      </c>
-      <c r="L50" t="s">
-        <v>141</v>
+        <v>30.15</v>
+      </c>
+      <c r="K50" t="s">
+        <v>136</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
       </c>
       <c r="M50">
-        <v>0</v>
-      </c>
-      <c r="N50" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
+        <v>225561</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="3">
         <v>46202</v>
       </c>
       <c r="B51" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C51" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D51" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="E51" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F51">
-        <v>21.82</v>
-      </c>
-      <c r="G51" t="s">
-        <v>94</v>
+        <v>32.32</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0.65</v>
       </c>
       <c r="H51">
-        <v>0.65</v>
+        <v>21.01</v>
       </c>
       <c r="I51" s="1">
-        <v>14.18</v>
+        <v>0.66</v>
       </c>
       <c r="J51">
-        <v>0.66</v>
-      </c>
-      <c r="K51" s="1">
-        <v>14.4</v>
-      </c>
-      <c r="L51" t="s">
-        <v>142</v>
+        <v>21.33</v>
+      </c>
+      <c r="K51" t="s">
+        <v>137</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
       </c>
       <c r="M51">
-        <v>0</v>
-      </c>
-      <c r="N51" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
+        <v>122253</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="3">
         <v>46202</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D52" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E52" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F52">
-        <v>18</v>
-      </c>
-      <c r="G52" t="s">
-        <v>94</v>
+        <v>23.98</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0.65</v>
       </c>
       <c r="H52">
-        <v>1.48</v>
+        <v>15.59</v>
       </c>
       <c r="I52" s="1">
-        <v>26.64</v>
+        <v>0.66</v>
       </c>
       <c r="J52">
-        <v>1.51</v>
-      </c>
-      <c r="K52" s="1">
-        <v>27.18</v>
-      </c>
-      <c r="L52" t="s">
-        <v>143</v>
+        <v>15.83</v>
+      </c>
+      <c r="K52" t="s">
+        <v>138</v>
+      </c>
+      <c r="L52">
+        <v>34789</v>
       </c>
       <c r="M52">
-        <v>0</v>
-      </c>
-      <c r="N52" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14">
+        <v>146532</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="3">
         <v>46202</v>
       </c>
       <c r="B53" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D53" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="E53" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F53">
-        <v>32.01</v>
-      </c>
-      <c r="G53" t="s">
-        <v>94</v>
+        <v>10</v>
+      </c>
+      <c r="G53" s="1">
+        <v>1.47</v>
       </c>
       <c r="H53">
-        <v>1.47</v>
+        <v>14.7</v>
       </c>
       <c r="I53" s="1">
-        <v>47.05</v>
+        <v>1.5</v>
       </c>
       <c r="J53">
-        <v>1.5</v>
-      </c>
-      <c r="K53" s="1">
-        <v>48.02</v>
-      </c>
-      <c r="L53" t="s">
-        <v>98</v>
+        <v>15</v>
+      </c>
+      <c r="K53" t="s">
+        <v>138</v>
+      </c>
+      <c r="L53">
+        <v>34789</v>
       </c>
       <c r="M53">
-        <v>53915</v>
-      </c>
-      <c r="N53" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
+        <v>146533</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="3">
         <v>46202</v>
       </c>
       <c r="B54" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C54" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D54" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E54" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F54">
-        <v>32.32</v>
-      </c>
-      <c r="G54" t="s">
-        <v>94</v>
+        <v>18</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1.48</v>
       </c>
       <c r="H54">
-        <v>0.65</v>
+        <v>26.64</v>
       </c>
       <c r="I54" s="1">
-        <v>21.01</v>
+        <v>1.51</v>
       </c>
       <c r="J54">
-        <v>0.66</v>
-      </c>
-      <c r="K54" s="1">
-        <v>21.33</v>
-      </c>
-      <c r="L54" t="s">
-        <v>140</v>
+        <v>27.18</v>
+      </c>
+      <c r="K54" t="s">
+        <v>139</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
       </c>
       <c r="M54">
-        <v>0</v>
-      </c>
-      <c r="N54" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14">
+        <v>121213</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="3">
         <v>46203</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C55" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D55" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E55" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F55">
-        <v>27.56</v>
-      </c>
-      <c r="G55" t="s">
-        <v>94</v>
+        <v>28.58</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0.65</v>
       </c>
       <c r="H55">
-        <v>0.65</v>
+        <v>18.58</v>
       </c>
       <c r="I55" s="1">
-        <v>17.91</v>
+        <v>0.66</v>
       </c>
       <c r="J55">
-        <v>0.66</v>
-      </c>
-      <c r="K55" s="1">
-        <v>18.19</v>
-      </c>
-      <c r="L55" t="s">
-        <v>144</v>
+        <v>18.86</v>
+      </c>
+      <c r="K55" t="s">
+        <v>140</v>
+      </c>
+      <c r="L55">
+        <v>69501</v>
       </c>
       <c r="M55">
-        <v>98150</v>
-      </c>
-      <c r="N55" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14">
+        <v>225819</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" s="3">
         <v>46203</v>
       </c>
       <c r="B56" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D56" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E56" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F56">
-        <v>28.58</v>
-      </c>
-      <c r="G56" t="s">
-        <v>94</v>
+        <v>27.56</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0.65</v>
       </c>
       <c r="H56">
-        <v>0.65</v>
+        <v>17.91</v>
       </c>
       <c r="I56" s="1">
-        <v>18.58</v>
+        <v>0.66</v>
       </c>
       <c r="J56">
-        <v>0.66</v>
-      </c>
-      <c r="K56" s="1">
-        <v>18.86</v>
-      </c>
-      <c r="L56" t="s">
-        <v>145</v>
+        <v>18.19</v>
+      </c>
+      <c r="K56" t="s">
+        <v>141</v>
+      </c>
+      <c r="L56">
+        <v>98150</v>
       </c>
       <c r="M56">
-        <v>69501</v>
-      </c>
-      <c r="N56" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
+        <v>146907</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" s="3">
         <v>46203</v>
       </c>
       <c r="B57" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C57" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D57" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E57" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F57">
         <v>20.85</v>
       </c>
-      <c r="G57" t="s">
-        <v>94</v>
+      <c r="G57" s="1">
+        <v>1.48</v>
       </c>
       <c r="H57">
-        <v>1.48</v>
+        <v>30.86</v>
       </c>
       <c r="I57" s="1">
-        <v>30.86</v>
+        <v>1.51</v>
       </c>
       <c r="J57">
-        <v>1.51</v>
-      </c>
-      <c r="K57" s="1">
         <v>31.48</v>
       </c>
-      <c r="L57" t="s">
-        <v>146</v>
+      <c r="K57" t="s">
+        <v>142</v>
+      </c>
+      <c r="L57">
+        <v>187810</v>
       </c>
       <c r="M57">
-        <v>187810</v>
-      </c>
-      <c r="N57" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14">
+        <v>279760</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
       <c r="A60" s="4" t="s">
-        <v>203</v>
+        <v>143</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -3579,32 +3227,32 @@
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:13">
       <c r="A61" s="5" t="s">
-        <v>204</v>
+        <v>144</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>205</v>
+        <v>145</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>206</v>
+        <v>146</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>207</v>
+        <v>147</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13">
       <c r="A62" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B62" s="7">
-        <v>701.09</v>
+        <v>701.1</v>
       </c>
       <c r="C62" s="7">
         <v>25</v>
@@ -3619,9 +3267,9 @@
         <v>463.35</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:13">
       <c r="A63" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B63" s="7">
         <v>513.4</v>
@@ -3639,9 +3287,9 @@
         <v>779.3</v>
       </c>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:13">
       <c r="A64" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B64" s="7">
         <v>436.61</v>
@@ -3661,7 +3309,7 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B65" s="7">
         <v>113.42</v>
@@ -3681,10 +3329,10 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="9" t="s">
-        <v>208</v>
+        <v>148</v>
       </c>
       <c r="B66" s="10">
-        <v>1764.52</v>
+        <v>1764.53</v>
       </c>
       <c r="C66" s="10">
         <v>56</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
@@ -572,7 +572,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -3136,7 +3136,7 @@
         <v>20</v>
       </c>
       <c r="D53" s="8">
-        <v>1.5074</v>
+        <v>1.507389</v>
       </c>
       <c r="E53" s="7">
         <v>803.74</v>
@@ -3156,7 +3156,7 @@
         <v>18</v>
       </c>
       <c r="D54" s="8">
-        <v>0.6303</v>
+        <v>0.630337</v>
       </c>
       <c r="E54" s="7">
         <v>308.55</v>
@@ -3176,7 +3176,7 @@
         <v>9</v>
       </c>
       <c r="D55" s="8">
-        <v>1.6749</v>
+        <v>1.67488</v>
       </c>
       <c r="E55" s="7">
         <v>689.95</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="184">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -964,7 +967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -977,13 +980,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1026,2078 +1029,2222 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F2">
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
         <v>0.62</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>12.4</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>0.63</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>12.6</v>
       </c>
-      <c r="L2" t="s">
-        <v>85</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N2">
         <v>50882</v>
       </c>
-      <c r="N2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F3">
-        <v>9.949999999999999</v>
+        <v>9.952999999999999</v>
       </c>
       <c r="G3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H3">
+        <v>1.369</v>
+      </c>
+      <c r="I3" s="1">
         <v>1.47</v>
       </c>
-      <c r="I3" s="1">
-        <v>14.63</v>
-      </c>
       <c r="J3">
+        <v>14.63091</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.5</v>
       </c>
-      <c r="K3" s="1">
-        <v>14.92</v>
-      </c>
-      <c r="L3" t="s">
-        <v>86</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>14.9295</v>
+      </c>
+      <c r="M3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N3">
         <v>42800</v>
       </c>
-      <c r="N3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46219</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F4">
         <v>31.88</v>
       </c>
       <c r="G4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H4">
+        <v>1.369</v>
+      </c>
+      <c r="I4" s="1">
         <v>1.47</v>
       </c>
-      <c r="I4" s="1">
-        <v>46.86</v>
-      </c>
       <c r="J4">
+        <v>46.8636</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.5</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>47.82</v>
       </c>
-      <c r="L4" t="s">
-        <v>87</v>
-      </c>
-      <c r="M4">
+      <c r="M4" t="s">
+        <v>88</v>
+      </c>
+      <c r="N4">
         <v>41689</v>
       </c>
-      <c r="N4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46220</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F5">
-        <v>76.95999999999999</v>
+        <v>76.95699999999999</v>
       </c>
       <c r="G5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H5">
+        <v>1.499</v>
+      </c>
+      <c r="I5" s="1">
         <v>1.6</v>
       </c>
-      <c r="I5" s="1">
-        <v>123.14</v>
-      </c>
       <c r="J5">
+        <v>123.1312</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.63</v>
       </c>
-      <c r="K5" s="1">
-        <v>125.44</v>
-      </c>
-      <c r="L5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="1">
+        <v>125.43991</v>
+      </c>
+      <c r="M5" t="s">
+        <v>89</v>
+      </c>
+      <c r="N5">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>46220</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F6">
-        <v>40.8</v>
+        <v>40.801</v>
       </c>
       <c r="G6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H6">
+        <v>1.369</v>
+      </c>
+      <c r="I6" s="1">
         <v>1.48</v>
       </c>
-      <c r="I6" s="1">
-        <v>60.38</v>
-      </c>
       <c r="J6">
+        <v>60.38548</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.51</v>
       </c>
-      <c r="K6" s="1">
-        <v>61.61</v>
-      </c>
-      <c r="L6" t="s">
-        <v>89</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="1">
+        <v>61.60951</v>
+      </c>
+      <c r="M6" t="s">
+        <v>90</v>
+      </c>
+      <c r="N6">
         <v>164612</v>
       </c>
-      <c r="N6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3">
         <v>46220</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F7">
-        <v>60.24</v>
+        <v>60.239</v>
       </c>
       <c r="G7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H7">
+        <v>1.499</v>
+      </c>
+      <c r="I7" s="1">
         <v>1.6</v>
       </c>
-      <c r="I7" s="1">
-        <v>96.38</v>
-      </c>
       <c r="J7">
+        <v>96.3824</v>
+      </c>
+      <c r="K7" s="1">
         <v>1.63</v>
       </c>
-      <c r="K7" s="1">
-        <v>98.19</v>
-      </c>
-      <c r="L7" t="s">
-        <v>90</v>
-      </c>
-      <c r="M7">
+      <c r="L7" s="1">
+        <v>98.18957</v>
+      </c>
+      <c r="M7" t="s">
+        <v>91</v>
+      </c>
+      <c r="N7">
         <v>0</v>
       </c>
-      <c r="N7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3">
         <v>46220</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F8">
         <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H8">
+        <v>1.369</v>
+      </c>
+      <c r="I8" s="1">
         <v>1.48</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>37</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>1.51</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>37.75</v>
       </c>
-      <c r="L8" t="s">
-        <v>91</v>
-      </c>
-      <c r="M8">
+      <c r="M8" t="s">
+        <v>92</v>
+      </c>
+      <c r="N8">
         <v>0</v>
       </c>
-      <c r="N8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3">
         <v>46220</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F9">
-        <v>22.61</v>
+        <v>22.609</v>
       </c>
       <c r="G9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H9">
+        <v>1.369</v>
+      </c>
+      <c r="I9" s="1">
         <v>1.48</v>
       </c>
-      <c r="I9" s="1">
-        <v>33.46</v>
-      </c>
       <c r="J9">
+        <v>33.46132</v>
+      </c>
+      <c r="K9" s="1">
         <v>1.51</v>
       </c>
-      <c r="K9" s="1">
-        <v>34.14</v>
-      </c>
-      <c r="L9" t="s">
-        <v>92</v>
-      </c>
-      <c r="M9">
+      <c r="L9" s="1">
+        <v>34.13959</v>
+      </c>
+      <c r="M9" t="s">
+        <v>93</v>
+      </c>
+      <c r="N9">
         <v>29444</v>
       </c>
-      <c r="N9" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="3">
         <v>46223</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F10">
-        <v>27.78</v>
+        <v>27.781</v>
       </c>
       <c r="G10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
         <v>0.63</v>
       </c>
-      <c r="I10" s="1">
-        <v>17.5</v>
-      </c>
       <c r="J10">
+        <v>17.50203</v>
+      </c>
+      <c r="K10" s="1">
         <v>0.64</v>
       </c>
-      <c r="K10" s="1">
-        <v>17.78</v>
-      </c>
-      <c r="L10" t="s">
-        <v>93</v>
-      </c>
-      <c r="M10">
+      <c r="L10" s="1">
+        <v>17.77984</v>
+      </c>
+      <c r="M10" t="s">
+        <v>94</v>
+      </c>
+      <c r="N10">
         <v>0</v>
       </c>
-      <c r="N10" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="3">
         <v>46223</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F11">
-        <v>48.74</v>
+        <v>48.738</v>
       </c>
       <c r="G11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H11">
+        <v>1.546</v>
+      </c>
+      <c r="I11" s="1">
         <v>1.65</v>
       </c>
-      <c r="I11" s="1">
-        <v>80.42</v>
-      </c>
       <c r="J11">
+        <v>80.4177</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.68</v>
       </c>
-      <c r="K11" s="1">
-        <v>81.88</v>
-      </c>
-      <c r="L11" t="s">
-        <v>94</v>
-      </c>
-      <c r="M11">
+      <c r="L11" s="1">
+        <v>81.87984</v>
+      </c>
+      <c r="M11" t="s">
+        <v>95</v>
+      </c>
+      <c r="N11">
         <v>188375</v>
       </c>
-      <c r="N11" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="3">
         <v>46223</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F12">
         <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H12">
+        <v>1.389</v>
+      </c>
+      <c r="I12" s="1">
         <v>1.5</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>30</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>1.53</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>30.6</v>
       </c>
-      <c r="L12" t="s">
-        <v>95</v>
-      </c>
-      <c r="M12">
+      <c r="M12" t="s">
+        <v>96</v>
+      </c>
+      <c r="N12">
         <v>55175</v>
       </c>
-      <c r="N12" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="3">
         <v>46224</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F13">
         <v>10</v>
       </c>
       <c r="G13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H13">
+        <v>1.389</v>
+      </c>
+      <c r="I13" s="1">
         <v>1.5</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>15</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>1.53</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>15.3</v>
       </c>
-      <c r="L13" t="s">
-        <v>96</v>
-      </c>
-      <c r="M13">
+      <c r="M13" t="s">
+        <v>97</v>
+      </c>
+      <c r="N13">
         <v>99000</v>
       </c>
-      <c r="N13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="3">
         <v>46224</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F14">
-        <v>29.98</v>
+        <v>29.984</v>
       </c>
       <c r="G14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1">
         <v>0.63</v>
       </c>
-      <c r="I14" s="1">
-        <v>18.89</v>
-      </c>
       <c r="J14">
+        <v>18.88992</v>
+      </c>
+      <c r="K14" s="1">
         <v>0.64</v>
       </c>
-      <c r="K14" s="1">
-        <v>19.19</v>
-      </c>
-      <c r="L14" t="s">
-        <v>97</v>
-      </c>
-      <c r="M14">
+      <c r="L14" s="1">
+        <v>19.18976</v>
+      </c>
+      <c r="M14" t="s">
+        <v>98</v>
+      </c>
+      <c r="N14">
         <v>99000</v>
       </c>
-      <c r="N14" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="3">
         <v>46225</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F15">
         <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H15">
+        <v>1.401</v>
+      </c>
+      <c r="I15" s="1">
         <v>1.51</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15">
         <v>37.75</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="1">
         <v>1.54</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>38.5</v>
       </c>
-      <c r="L15" t="s">
-        <v>98</v>
-      </c>
-      <c r="M15">
+      <c r="M15" t="s">
+        <v>99</v>
+      </c>
+      <c r="N15">
         <v>0</v>
       </c>
-      <c r="N15" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="3">
         <v>46226</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F16">
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1">
         <v>0.63</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16">
         <v>12.6</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="1">
         <v>0.64</v>
       </c>
-      <c r="K16" s="1">
+      <c r="L16" s="1">
         <v>12.8</v>
       </c>
-      <c r="L16" t="s">
-        <v>99</v>
-      </c>
-      <c r="M16">
+      <c r="M16" t="s">
+        <v>100</v>
+      </c>
+      <c r="N16">
         <v>51017</v>
       </c>
-      <c r="N16" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="3">
         <v>46226</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F17">
-        <v>39.58</v>
+        <v>39.578</v>
       </c>
       <c r="G17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H17">
+        <v>1.401</v>
+      </c>
+      <c r="I17" s="1">
         <v>1.51</v>
       </c>
-      <c r="I17" s="1">
-        <v>59.77</v>
-      </c>
       <c r="J17">
+        <v>59.76278</v>
+      </c>
+      <c r="K17" s="1">
         <v>1.54</v>
       </c>
-      <c r="K17" s="1">
-        <v>60.95</v>
-      </c>
-      <c r="L17" t="s">
-        <v>89</v>
-      </c>
-      <c r="M17">
+      <c r="L17" s="1">
+        <v>60.95012</v>
+      </c>
+      <c r="M17" t="s">
+        <v>90</v>
+      </c>
+      <c r="N17">
         <v>0</v>
       </c>
-      <c r="N17" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="3">
         <v>46226</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F18">
-        <v>17.34</v>
+        <v>17.338</v>
       </c>
       <c r="G18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H18">
+        <v>1.401</v>
+      </c>
+      <c r="I18" s="1">
         <v>1.51</v>
       </c>
-      <c r="I18" s="1">
-        <v>26.18</v>
-      </c>
       <c r="J18">
+        <v>26.18038</v>
+      </c>
+      <c r="K18" s="1">
         <v>1.54</v>
       </c>
-      <c r="K18" s="1">
-        <v>26.7</v>
-      </c>
-      <c r="L18" t="s">
-        <v>100</v>
-      </c>
-      <c r="M18">
+      <c r="L18" s="1">
+        <v>26.70052</v>
+      </c>
+      <c r="M18" t="s">
+        <v>101</v>
+      </c>
+      <c r="N18">
         <v>42900</v>
       </c>
-      <c r="N18" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="3">
         <v>46226</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F19">
-        <v>32.58</v>
+        <v>32.578</v>
       </c>
       <c r="G19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1">
         <v>0.63</v>
       </c>
-      <c r="I19" s="1">
-        <v>20.53</v>
-      </c>
       <c r="J19">
+        <v>20.52414</v>
+      </c>
+      <c r="K19" s="1">
         <v>0.64</v>
       </c>
-      <c r="K19" s="1">
-        <v>20.85</v>
-      </c>
-      <c r="L19" t="s">
-        <v>101</v>
-      </c>
-      <c r="M19">
+      <c r="L19" s="1">
+        <v>20.84992</v>
+      </c>
+      <c r="M19" t="s">
+        <v>102</v>
+      </c>
+      <c r="N19">
         <v>0</v>
       </c>
-      <c r="N19" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="3">
         <v>46226</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F20">
-        <v>19.98</v>
+        <v>19.984</v>
       </c>
       <c r="G20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1">
         <v>0.63</v>
       </c>
-      <c r="I20" s="1">
-        <v>12.59</v>
-      </c>
       <c r="J20">
+        <v>12.58992</v>
+      </c>
+      <c r="K20" s="1">
         <v>0.64</v>
       </c>
-      <c r="K20" s="1">
-        <v>12.79</v>
-      </c>
-      <c r="L20" t="s">
-        <v>102</v>
-      </c>
-      <c r="M20">
+      <c r="L20" s="1">
+        <v>12.78976</v>
+      </c>
+      <c r="M20" t="s">
+        <v>103</v>
+      </c>
+      <c r="N20">
         <v>0</v>
       </c>
-      <c r="N20" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="3">
         <v>46226</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F21">
-        <v>24.98</v>
+        <v>24.984</v>
       </c>
       <c r="G21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1">
         <v>0.63</v>
       </c>
-      <c r="I21" s="1">
-        <v>15.74</v>
-      </c>
       <c r="J21">
+        <v>15.73992</v>
+      </c>
+      <c r="K21" s="1">
         <v>0.64</v>
       </c>
-      <c r="K21" s="1">
-        <v>15.99</v>
-      </c>
-      <c r="L21" t="s">
-        <v>103</v>
-      </c>
-      <c r="M21">
+      <c r="L21" s="1">
+        <v>15.98976</v>
+      </c>
+      <c r="M21" t="s">
+        <v>104</v>
+      </c>
+      <c r="N21">
         <v>77590</v>
       </c>
-      <c r="N21" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="3">
         <v>46226</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F22">
-        <v>33.53</v>
+        <v>33.531</v>
       </c>
       <c r="G22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1">
         <v>0.63</v>
       </c>
-      <c r="I22" s="1">
-        <v>21.12</v>
-      </c>
       <c r="J22">
+        <v>21.12453</v>
+      </c>
+      <c r="K22" s="1">
         <v>0.64</v>
       </c>
-      <c r="K22" s="1">
-        <v>21.46</v>
-      </c>
-      <c r="L22" t="s">
-        <v>104</v>
-      </c>
-      <c r="M22">
+      <c r="L22" s="1">
+        <v>21.45984</v>
+      </c>
+      <c r="M22" t="s">
+        <v>105</v>
+      </c>
+      <c r="N22">
         <v>43150</v>
       </c>
-      <c r="N22" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="3">
         <v>46227</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F23">
-        <v>27.59</v>
+        <v>27.594</v>
       </c>
       <c r="G23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1">
         <v>0.63</v>
       </c>
-      <c r="I23" s="1">
-        <v>17.38</v>
-      </c>
       <c r="J23">
+        <v>17.38422</v>
+      </c>
+      <c r="K23" s="1">
         <v>0.64</v>
       </c>
-      <c r="K23" s="1">
-        <v>17.66</v>
-      </c>
-      <c r="L23" t="s">
-        <v>105</v>
-      </c>
-      <c r="M23">
+      <c r="L23" s="1">
+        <v>17.66016</v>
+      </c>
+      <c r="M23" t="s">
+        <v>106</v>
+      </c>
+      <c r="N23">
         <v>256</v>
       </c>
-      <c r="N23" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="3">
         <v>46227</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F24">
-        <v>18.05</v>
+        <v>18.047</v>
       </c>
       <c r="G24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24" s="1">
         <v>0.63</v>
       </c>
-      <c r="I24" s="1">
-        <v>11.37</v>
-      </c>
       <c r="J24">
+        <v>11.36961</v>
+      </c>
+      <c r="K24" s="1">
         <v>0.64</v>
       </c>
-      <c r="K24" s="1">
-        <v>11.55</v>
-      </c>
-      <c r="L24" t="s">
-        <v>106</v>
-      </c>
-      <c r="M24">
+      <c r="L24" s="1">
+        <v>11.55008</v>
+      </c>
+      <c r="M24" t="s">
+        <v>107</v>
+      </c>
+      <c r="N24">
         <v>0</v>
       </c>
-      <c r="N24" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" s="3">
         <v>46227</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F25">
-        <v>33.88</v>
+        <v>33.883</v>
       </c>
       <c r="G25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H25">
+        <v>1.401</v>
+      </c>
+      <c r="I25" s="1">
         <v>1.51</v>
       </c>
-      <c r="I25" s="1">
-        <v>51.16</v>
-      </c>
       <c r="J25">
+        <v>51.16333</v>
+      </c>
+      <c r="K25" s="1">
         <v>1.54</v>
       </c>
-      <c r="K25" s="1">
-        <v>52.18</v>
-      </c>
-      <c r="L25" t="s">
-        <v>107</v>
-      </c>
-      <c r="M25">
+      <c r="L25" s="1">
+        <v>52.17982</v>
+      </c>
+      <c r="M25" t="s">
+        <v>108</v>
+      </c>
+      <c r="N25">
         <v>0</v>
       </c>
-      <c r="N25" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="3">
         <v>46227</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F26">
-        <v>32.33</v>
+        <v>32.328</v>
       </c>
       <c r="G26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1">
         <v>0.63</v>
       </c>
-      <c r="I26" s="1">
-        <v>20.37</v>
-      </c>
       <c r="J26">
+        <v>20.36664</v>
+      </c>
+      <c r="K26" s="1">
         <v>0.64</v>
       </c>
-      <c r="K26" s="1">
-        <v>20.69</v>
-      </c>
-      <c r="L26" t="s">
-        <v>108</v>
-      </c>
-      <c r="M26">
+      <c r="L26" s="1">
+        <v>20.68992</v>
+      </c>
+      <c r="M26" t="s">
+        <v>109</v>
+      </c>
+      <c r="N26">
         <v>0</v>
       </c>
-      <c r="N26" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" s="3">
         <v>46227</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F27">
-        <v>19.05</v>
+        <v>19.045</v>
       </c>
       <c r="G27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1">
         <v>0.65</v>
       </c>
-      <c r="I27" s="1">
-        <v>12.38</v>
-      </c>
       <c r="J27">
+        <v>12.37925</v>
+      </c>
+      <c r="K27" s="1">
         <v>0.66</v>
       </c>
-      <c r="K27" s="1">
-        <v>12.57</v>
-      </c>
-      <c r="L27" t="s">
-        <v>109</v>
-      </c>
-      <c r="M27">
+      <c r="L27" s="1">
+        <v>12.5697</v>
+      </c>
+      <c r="M27" t="s">
+        <v>110</v>
+      </c>
+      <c r="N27">
         <v>4350</v>
       </c>
-      <c r="N27" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="O27" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" s="3">
         <v>46230</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F28">
-        <v>54.97</v>
+        <v>54.971</v>
       </c>
       <c r="G28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H28">
+        <v>1.619</v>
+      </c>
+      <c r="I28" s="1">
         <v>1.72</v>
       </c>
-      <c r="I28" s="1">
-        <v>94.55</v>
-      </c>
       <c r="J28">
+        <v>94.55012000000001</v>
+      </c>
+      <c r="K28" s="1">
         <v>1.75</v>
       </c>
-      <c r="K28" s="1">
-        <v>96.2</v>
-      </c>
-      <c r="L28" t="s">
-        <v>110</v>
-      </c>
-      <c r="M28">
+      <c r="L28" s="1">
+        <v>96.19925000000001</v>
+      </c>
+      <c r="M28" t="s">
+        <v>111</v>
+      </c>
+      <c r="N28">
         <v>0</v>
       </c>
-      <c r="N28" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" s="3">
         <v>46230</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F29">
         <v>10</v>
       </c>
       <c r="G29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H29">
+        <v>1.401</v>
+      </c>
+      <c r="I29" s="1">
         <v>1.53</v>
       </c>
-      <c r="I29" s="1">
+      <c r="J29">
         <v>15.3</v>
       </c>
-      <c r="J29">
+      <c r="K29" s="1">
         <v>1.56</v>
       </c>
-      <c r="K29" s="1">
+      <c r="L29" s="1">
         <v>15.6</v>
       </c>
-      <c r="L29" t="s">
-        <v>111</v>
-      </c>
-      <c r="M29">
+      <c r="M29" t="s">
+        <v>112</v>
+      </c>
+      <c r="N29">
         <v>77809</v>
       </c>
-      <c r="N29" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="O29" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" s="3">
         <v>46230</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F30">
-        <v>32.34</v>
+        <v>32.344</v>
       </c>
       <c r="G30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30" s="1">
         <v>0.63</v>
       </c>
-      <c r="I30" s="1">
-        <v>20.37</v>
-      </c>
       <c r="J30">
+        <v>20.37672</v>
+      </c>
+      <c r="K30" s="1">
         <v>0.64</v>
       </c>
-      <c r="K30" s="1">
-        <v>20.7</v>
-      </c>
-      <c r="L30" t="s">
-        <v>112</v>
-      </c>
-      <c r="M30">
+      <c r="L30" s="1">
+        <v>20.70016</v>
+      </c>
+      <c r="M30" t="s">
+        <v>113</v>
+      </c>
+      <c r="N30">
         <v>0</v>
       </c>
-      <c r="N30" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="O30" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" s="3">
         <v>46230</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F31">
-        <v>32.24</v>
+        <v>32.237</v>
       </c>
       <c r="G31" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H31">
+        <v>1.401</v>
+      </c>
+      <c r="I31" s="1">
         <v>1.53</v>
       </c>
-      <c r="I31" s="1">
-        <v>49.33</v>
-      </c>
       <c r="J31">
+        <v>49.32261</v>
+      </c>
+      <c r="K31" s="1">
         <v>1.56</v>
       </c>
-      <c r="K31" s="1">
-        <v>50.29</v>
-      </c>
-      <c r="L31" t="s">
-        <v>113</v>
-      </c>
-      <c r="M31">
+      <c r="L31" s="1">
+        <v>50.28972</v>
+      </c>
+      <c r="M31" t="s">
+        <v>114</v>
+      </c>
+      <c r="N31">
         <v>42035</v>
       </c>
-      <c r="N31" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="O31" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" s="3">
         <v>46231</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E32" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F32">
         <v>25</v>
       </c>
       <c r="G32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H32">
+        <v>1.441</v>
+      </c>
+      <c r="I32" s="1">
         <v>1.53</v>
       </c>
-      <c r="I32" s="1">
+      <c r="J32">
         <v>38.25</v>
       </c>
-      <c r="J32">
+      <c r="K32" s="1">
         <v>1.56</v>
       </c>
-      <c r="K32" s="1">
+      <c r="L32" s="1">
         <v>39</v>
       </c>
-      <c r="L32" t="s">
-        <v>114</v>
-      </c>
-      <c r="M32">
+      <c r="M32" t="s">
+        <v>115</v>
+      </c>
+      <c r="N32">
         <v>476750</v>
       </c>
-      <c r="N32" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="O32" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" s="3">
         <v>46231</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E33" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F33">
-        <v>28.83</v>
+        <v>28.828</v>
       </c>
       <c r="G33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33" s="1">
         <v>0.63</v>
       </c>
-      <c r="I33" s="1">
-        <v>18.16</v>
-      </c>
       <c r="J33">
+        <v>18.16164</v>
+      </c>
+      <c r="K33" s="1">
         <v>0.64</v>
       </c>
-      <c r="K33" s="1">
-        <v>18.45</v>
-      </c>
-      <c r="L33" t="s">
-        <v>115</v>
-      </c>
-      <c r="M33">
+      <c r="L33" s="1">
+        <v>18.44992</v>
+      </c>
+      <c r="M33" t="s">
+        <v>116</v>
+      </c>
+      <c r="N33">
         <v>69975</v>
       </c>
-      <c r="N33" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="O33" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34" s="3">
         <v>46231</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E34" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F34">
-        <v>20.01</v>
+        <v>20.011</v>
       </c>
       <c r="G34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H34">
+        <v>1.653</v>
+      </c>
+      <c r="I34" s="1">
         <v>1.72</v>
       </c>
-      <c r="I34" s="1">
-        <v>34.42</v>
-      </c>
       <c r="J34">
+        <v>34.41892</v>
+      </c>
+      <c r="K34" s="1">
         <v>1.75</v>
       </c>
-      <c r="K34" s="1">
-        <v>35.02</v>
-      </c>
-      <c r="L34" t="s">
-        <v>116</v>
-      </c>
-      <c r="M34">
+      <c r="L34" s="1">
+        <v>35.01925</v>
+      </c>
+      <c r="M34" t="s">
+        <v>117</v>
+      </c>
+      <c r="N34">
         <v>0</v>
       </c>
-      <c r="N34" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="O34" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" s="3">
         <v>46231</v>
       </c>
       <c r="B35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E35" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F35">
-        <v>36.78</v>
+        <v>36.783</v>
       </c>
       <c r="G35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H35">
+        <v>1.653</v>
+      </c>
+      <c r="I35" s="1">
         <v>1.72</v>
       </c>
-      <c r="I35" s="1">
-        <v>63.26</v>
-      </c>
       <c r="J35">
+        <v>63.26676</v>
+      </c>
+      <c r="K35" s="1">
         <v>1.75</v>
       </c>
-      <c r="K35" s="1">
-        <v>64.37</v>
-      </c>
-      <c r="L35" t="s">
-        <v>117</v>
-      </c>
-      <c r="M35">
+      <c r="L35" s="1">
+        <v>64.37025</v>
+      </c>
+      <c r="M35" t="s">
+        <v>118</v>
+      </c>
+      <c r="N35">
         <v>188700</v>
       </c>
-      <c r="N35" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="O35" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36" s="3">
         <v>46232</v>
       </c>
       <c r="B36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F36">
-        <v>29.16</v>
+        <v>29.161</v>
       </c>
       <c r="G36" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H36">
+        <v>1.449</v>
+      </c>
+      <c r="I36" s="1">
         <v>1.52</v>
       </c>
-      <c r="I36" s="1">
-        <v>44.32</v>
-      </c>
       <c r="J36">
+        <v>44.32472</v>
+      </c>
+      <c r="K36" s="1">
         <v>1.55</v>
       </c>
-      <c r="K36" s="1">
-        <v>45.2</v>
-      </c>
-      <c r="L36" t="s">
-        <v>118</v>
-      </c>
-      <c r="M36">
+      <c r="L36" s="1">
+        <v>45.19955</v>
+      </c>
+      <c r="M36" t="s">
+        <v>119</v>
+      </c>
+      <c r="N36">
         <v>55321</v>
       </c>
-      <c r="N36" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="O36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" s="3">
         <v>46232</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F37">
-        <v>53.97</v>
+        <v>53.968</v>
       </c>
       <c r="G37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H37">
+        <v>1.449</v>
+      </c>
+      <c r="I37" s="1">
         <v>1.52</v>
       </c>
-      <c r="I37" s="1">
-        <v>82.03</v>
-      </c>
       <c r="J37">
+        <v>82.03136000000001</v>
+      </c>
+      <c r="K37" s="1">
         <v>1.55</v>
       </c>
-      <c r="K37" s="1">
-        <v>83.65000000000001</v>
-      </c>
-      <c r="L37" t="s">
-        <v>119</v>
-      </c>
-      <c r="M37">
+      <c r="L37" s="1">
+        <v>83.6504</v>
+      </c>
+      <c r="M37" t="s">
+        <v>120</v>
+      </c>
+      <c r="N37">
         <v>0</v>
       </c>
-      <c r="N37" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="O37" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" s="3">
         <v>46232</v>
       </c>
       <c r="B38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F38">
         <v>20</v>
       </c>
       <c r="G38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H38">
+        <v>1.449</v>
+      </c>
+      <c r="I38" s="1">
         <v>1.52</v>
       </c>
-      <c r="I38" s="1">
+      <c r="J38">
         <v>30.4</v>
       </c>
-      <c r="J38">
+      <c r="K38" s="1">
         <v>1.55</v>
       </c>
-      <c r="K38" s="1">
+      <c r="L38" s="1">
         <v>31</v>
       </c>
-      <c r="L38" t="s">
-        <v>120</v>
-      </c>
-      <c r="M38">
+      <c r="M38" t="s">
+        <v>121</v>
+      </c>
+      <c r="N38">
         <v>0</v>
       </c>
-      <c r="N38" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="O38" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" s="3">
         <v>46232</v>
       </c>
       <c r="B39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D39" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E39" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F39">
-        <v>31.45</v>
+        <v>31.453</v>
       </c>
       <c r="G39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39" s="1">
         <v>0.63</v>
       </c>
-      <c r="I39" s="1">
-        <v>19.81</v>
-      </c>
       <c r="J39">
+        <v>19.81539</v>
+      </c>
+      <c r="K39" s="1">
         <v>0.64</v>
       </c>
-      <c r="K39" s="1">
-        <v>20.13</v>
-      </c>
-      <c r="L39" t="s">
-        <v>121</v>
-      </c>
-      <c r="M39">
+      <c r="L39" s="1">
+        <v>20.12992</v>
+      </c>
+      <c r="M39" t="s">
+        <v>122</v>
+      </c>
+      <c r="N39">
         <v>99353</v>
       </c>
-      <c r="N39" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="O39" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
       <c r="A40" s="3">
         <v>46232</v>
       </c>
       <c r="B40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E40" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F40">
-        <v>26.91</v>
+        <v>26.906</v>
       </c>
       <c r="G40" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40" s="1">
         <v>0.63</v>
       </c>
-      <c r="I40" s="1">
-        <v>16.95</v>
-      </c>
       <c r="J40">
+        <v>16.95078</v>
+      </c>
+      <c r="K40" s="1">
         <v>0.64</v>
       </c>
-      <c r="K40" s="1">
-        <v>17.22</v>
-      </c>
-      <c r="L40" t="s">
-        <v>122</v>
-      </c>
-      <c r="M40">
+      <c r="L40" s="1">
+        <v>17.21984</v>
+      </c>
+      <c r="M40" t="s">
+        <v>123</v>
+      </c>
+      <c r="N40">
         <v>38940</v>
       </c>
-      <c r="N40" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="O40" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
       <c r="A41" s="3">
         <v>46232</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D41" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E41" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F41">
-        <v>49.98</v>
+        <v>49.983</v>
       </c>
       <c r="G41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H41">
+        <v>1.674</v>
+      </c>
+      <c r="I41" s="1">
         <v>1.72</v>
       </c>
-      <c r="I41" s="1">
-        <v>85.97</v>
-      </c>
       <c r="J41">
+        <v>85.97076</v>
+      </c>
+      <c r="K41" s="1">
         <v>1.75</v>
       </c>
-      <c r="K41" s="1">
-        <v>87.45999999999999</v>
-      </c>
-      <c r="L41" t="s">
-        <v>123</v>
-      </c>
-      <c r="M41">
+      <c r="L41" s="1">
+        <v>87.47024999999999</v>
+      </c>
+      <c r="M41" t="s">
+        <v>124</v>
+      </c>
+      <c r="N41">
         <v>0</v>
       </c>
-      <c r="N41" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="O41" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42" s="3">
         <v>46233</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D42" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E42" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F42">
-        <v>31.64</v>
+        <v>31.641</v>
       </c>
       <c r="G42" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42" s="1">
         <v>0.63</v>
       </c>
-      <c r="I42" s="1">
-        <v>19.93</v>
-      </c>
       <c r="J42">
+        <v>19.93383</v>
+      </c>
+      <c r="K42" s="1">
         <v>0.64</v>
       </c>
-      <c r="K42" s="1">
-        <v>20.25</v>
-      </c>
-      <c r="L42" t="s">
-        <v>124</v>
-      </c>
-      <c r="M42">
+      <c r="L42" s="1">
+        <v>20.25024</v>
+      </c>
+      <c r="M42" t="s">
+        <v>125</v>
+      </c>
+      <c r="N42">
         <v>77268</v>
       </c>
-      <c r="N42" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="O42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43" s="3">
         <v>46233</v>
       </c>
       <c r="B43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D43" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E43" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F43">
-        <v>41.24</v>
+        <v>41.239</v>
       </c>
       <c r="G43" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H43">
+        <v>1.449</v>
+      </c>
+      <c r="I43" s="1">
         <v>1.52</v>
       </c>
-      <c r="I43" s="1">
-        <v>62.68</v>
-      </c>
       <c r="J43">
+        <v>62.68328</v>
+      </c>
+      <c r="K43" s="1">
         <v>1.55</v>
       </c>
-      <c r="K43" s="1">
-        <v>63.92</v>
-      </c>
-      <c r="L43" t="s">
-        <v>124</v>
-      </c>
-      <c r="M43">
+      <c r="L43" s="1">
+        <v>63.92045</v>
+      </c>
+      <c r="M43" t="s">
+        <v>125</v>
+      </c>
+      <c r="N43">
         <v>0</v>
       </c>
-      <c r="N43" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
+      <c r="O43" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" s="3">
         <v>46233</v>
       </c>
       <c r="B44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D44" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F44">
-        <v>13.25</v>
+        <v>13.252</v>
       </c>
       <c r="G44" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H44">
+        <v>1.449</v>
+      </c>
+      <c r="I44" s="1">
         <v>1.52</v>
       </c>
-      <c r="I44" s="1">
-        <v>20.14</v>
-      </c>
       <c r="J44">
+        <v>20.14304</v>
+      </c>
+      <c r="K44" s="1">
         <v>1.55</v>
       </c>
-      <c r="K44" s="1">
-        <v>20.54</v>
-      </c>
-      <c r="L44" t="s">
-        <v>125</v>
-      </c>
-      <c r="M44">
+      <c r="L44" s="1">
+        <v>20.5406</v>
+      </c>
+      <c r="M44" t="s">
+        <v>126</v>
+      </c>
+      <c r="N44">
         <v>0</v>
       </c>
-      <c r="N44" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="O44" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" s="3">
         <v>46234</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F45">
-        <v>32.48</v>
+        <v>32.484</v>
       </c>
       <c r="G45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45" s="1">
         <v>0.63</v>
       </c>
-      <c r="I45" s="1">
-        <v>20.46</v>
-      </c>
       <c r="J45">
+        <v>20.46492</v>
+      </c>
+      <c r="K45" s="1">
         <v>0.64</v>
       </c>
-      <c r="K45" s="1">
-        <v>20.79</v>
-      </c>
-      <c r="L45" t="s">
-        <v>126</v>
-      </c>
-      <c r="M45">
+      <c r="L45" s="1">
+        <v>20.78976</v>
+      </c>
+      <c r="M45" t="s">
+        <v>127</v>
+      </c>
+      <c r="N45">
         <v>44100</v>
       </c>
-      <c r="N45" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
+      <c r="O45" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
       <c r="A46" s="3">
         <v>46234</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D46" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E46" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F46">
         <v>30</v>
       </c>
       <c r="G46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H46">
+        <v>1.689</v>
+      </c>
+      <c r="I46" s="1">
         <v>1.74</v>
       </c>
-      <c r="I46" s="1">
+      <c r="J46">
         <v>52.2</v>
       </c>
-      <c r="J46">
+      <c r="K46" s="1">
         <v>1.77</v>
       </c>
-      <c r="K46" s="1">
+      <c r="L46" s="1">
         <v>53.1</v>
       </c>
-      <c r="L46" t="s">
-        <v>127</v>
-      </c>
-      <c r="M46">
+      <c r="M46" t="s">
+        <v>128</v>
+      </c>
+      <c r="N46">
         <v>188800</v>
       </c>
-      <c r="N46" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="O46" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" s="3">
         <v>46234</v>
       </c>
       <c r="B47" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D47" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E47" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F47">
         <v>34.26</v>
       </c>
       <c r="G47" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H47">
+        <v>1.689</v>
+      </c>
+      <c r="I47" s="1">
         <v>1.74</v>
       </c>
-      <c r="I47" s="1">
-        <v>59.61</v>
-      </c>
       <c r="J47">
+        <v>59.6124</v>
+      </c>
+      <c r="K47" s="1">
         <v>1.77</v>
       </c>
-      <c r="K47" s="1">
-        <v>60.64</v>
-      </c>
-      <c r="L47" t="s">
-        <v>128</v>
-      </c>
-      <c r="M47">
+      <c r="L47" s="1">
+        <v>60.6402</v>
+      </c>
+      <c r="M47" t="s">
+        <v>129</v>
+      </c>
+      <c r="N47">
         <v>0</v>
       </c>
-      <c r="N47" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="O47" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48" s="3">
         <v>46234</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E48" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F48">
-        <v>32.3</v>
+        <v>32.303</v>
       </c>
       <c r="G48" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H48">
+        <v>1.459</v>
+      </c>
+      <c r="I48" s="1">
         <v>1.52</v>
       </c>
-      <c r="I48" s="1">
-        <v>49.1</v>
-      </c>
       <c r="J48">
+        <v>49.10056</v>
+      </c>
+      <c r="K48" s="1">
         <v>1.55</v>
       </c>
-      <c r="K48" s="1">
-        <v>50.06</v>
-      </c>
-      <c r="L48" t="s">
-        <v>129</v>
-      </c>
-      <c r="M48">
+      <c r="L48" s="1">
+        <v>50.06965</v>
+      </c>
+      <c r="M48" t="s">
+        <v>130</v>
+      </c>
+      <c r="N48">
         <v>42428</v>
       </c>
-      <c r="N48" t="s">
-        <v>176</v>
+      <c r="O48" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -3107,59 +3254,59 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B53" s="7">
-        <v>533.2</v>
+        <v>533.202</v>
       </c>
       <c r="C53" s="7">
         <v>20</v>
       </c>
       <c r="D53" s="8">
-        <v>1.507389</v>
+        <v>1.507409</v>
       </c>
       <c r="E53" s="7">
-        <v>803.74</v>
+        <v>803.75</v>
       </c>
       <c r="F53" s="7">
-        <v>819.73</v>
+        <v>819.75</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B54" s="7">
-        <v>489.5</v>
+        <v>489.512</v>
       </c>
       <c r="C54" s="7">
         <v>18</v>
       </c>
       <c r="D54" s="8">
-        <v>0.630337</v>
+        <v>0.63037</v>
       </c>
       <c r="E54" s="7">
-        <v>308.55</v>
+        <v>308.57</v>
       </c>
       <c r="F54" s="7">
         <v>313.47</v>
@@ -3167,40 +3314,40 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B55" s="7">
-        <v>411.94</v>
+        <v>411.942</v>
       </c>
       <c r="C55" s="7">
         <v>9</v>
       </c>
       <c r="D55" s="8">
-        <v>1.67488</v>
+        <v>1.674872</v>
       </c>
       <c r="E55" s="7">
         <v>689.95</v>
       </c>
       <c r="F55" s="7">
-        <v>702.3</v>
+        <v>702.3099999999999</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B56" s="10">
-        <v>1434.64</v>
+        <v>1434.656</v>
       </c>
       <c r="C56" s="10">
         <v>47</v>
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="10">
-        <v>1802.24</v>
+        <v>1802.27</v>
       </c>
       <c r="F56" s="10">
-        <v>1835.5</v>
+        <v>1835.53</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="183">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -573,9 +570,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -669,10 +666,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -967,7 +964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -980,13 +977,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1029,2222 +1026,2078 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F2">
         <v>20</v>
       </c>
       <c r="G2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2">
+        <v>0.62</v>
+      </c>
+      <c r="I2" s="1">
+        <v>12.4</v>
+      </c>
+      <c r="J2">
+        <v>0.63</v>
+      </c>
+      <c r="K2" s="1">
+        <v>12.6</v>
+      </c>
+      <c r="L2" t="s">
         <v>85</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="J2">
-        <v>12.4</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="L2" s="1">
-        <v>12.6</v>
-      </c>
-      <c r="M2" t="s">
-        <v>86</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>50882</v>
       </c>
-      <c r="O2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F3">
         <v>9.952999999999999</v>
       </c>
       <c r="G3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H3">
-        <v>1.369</v>
+        <v>1.47</v>
       </c>
       <c r="I3" s="1">
-        <v>1.47</v>
+        <v>14.631</v>
       </c>
       <c r="J3">
-        <v>14.63091</v>
+        <v>1.5</v>
       </c>
       <c r="K3" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L3" s="1">
-        <v>14.9295</v>
-      </c>
-      <c r="M3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N3">
+        <v>14.93</v>
+      </c>
+      <c r="L3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M3">
         <v>42800</v>
       </c>
-      <c r="O3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46219</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F4">
         <v>31.88</v>
       </c>
       <c r="G4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H4">
-        <v>1.369</v>
+        <v>1.47</v>
       </c>
       <c r="I4" s="1">
-        <v>1.47</v>
+        <v>46.864</v>
       </c>
       <c r="J4">
-        <v>46.8636</v>
+        <v>1.5</v>
       </c>
       <c r="K4" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L4" s="1">
         <v>47.82</v>
       </c>
-      <c r="M4" t="s">
-        <v>88</v>
-      </c>
-      <c r="N4">
+      <c r="L4" t="s">
+        <v>87</v>
+      </c>
+      <c r="M4">
         <v>41689</v>
       </c>
-      <c r="O4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46220</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F5">
         <v>76.95699999999999</v>
       </c>
       <c r="G5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5">
-        <v>1.499</v>
+        <v>1.6</v>
       </c>
       <c r="I5" s="1">
-        <v>1.6</v>
+        <v>123.131</v>
       </c>
       <c r="J5">
-        <v>123.1312</v>
+        <v>1.63</v>
       </c>
       <c r="K5" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L5" s="1">
-        <v>125.43991</v>
-      </c>
-      <c r="M5" t="s">
-        <v>89</v>
-      </c>
-      <c r="N5">
+        <v>125.44</v>
+      </c>
+      <c r="L5" t="s">
+        <v>88</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46220</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F6">
         <v>40.801</v>
       </c>
       <c r="G6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H6">
-        <v>1.369</v>
+        <v>1.48</v>
       </c>
       <c r="I6" s="1">
-        <v>1.48</v>
+        <v>60.385</v>
       </c>
       <c r="J6">
-        <v>60.38548</v>
+        <v>1.51</v>
       </c>
       <c r="K6" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L6" s="1">
-        <v>61.60951</v>
-      </c>
-      <c r="M6" t="s">
-        <v>90</v>
-      </c>
-      <c r="N6">
+        <v>61.61</v>
+      </c>
+      <c r="L6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M6">
         <v>164612</v>
       </c>
-      <c r="O6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46220</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F7">
         <v>60.239</v>
       </c>
       <c r="G7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H7">
-        <v>1.499</v>
+        <v>1.6</v>
       </c>
       <c r="I7" s="1">
-        <v>1.6</v>
+        <v>96.38200000000001</v>
       </c>
       <c r="J7">
-        <v>96.3824</v>
+        <v>1.63</v>
       </c>
       <c r="K7" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L7" s="1">
-        <v>98.18957</v>
-      </c>
-      <c r="M7" t="s">
-        <v>91</v>
-      </c>
-      <c r="N7">
+        <v>98.19</v>
+      </c>
+      <c r="L7" t="s">
+        <v>90</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46220</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F8">
         <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H8">
-        <v>1.369</v>
+        <v>1.48</v>
       </c>
       <c r="I8" s="1">
-        <v>1.48</v>
+        <v>37</v>
       </c>
       <c r="J8">
-        <v>37</v>
+        <v>1.51</v>
       </c>
       <c r="K8" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L8" s="1">
         <v>37.75</v>
       </c>
-      <c r="M8" t="s">
-        <v>92</v>
-      </c>
-      <c r="N8">
+      <c r="L8" t="s">
+        <v>91</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46220</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F9">
         <v>22.609</v>
       </c>
       <c r="G9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H9">
-        <v>1.369</v>
+        <v>1.48</v>
       </c>
       <c r="I9" s="1">
-        <v>1.48</v>
+        <v>33.461</v>
       </c>
       <c r="J9">
-        <v>33.46132</v>
+        <v>1.51</v>
       </c>
       <c r="K9" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L9" s="1">
-        <v>34.13959</v>
-      </c>
-      <c r="M9" t="s">
-        <v>93</v>
-      </c>
-      <c r="N9">
+        <v>34.14</v>
+      </c>
+      <c r="L9" t="s">
+        <v>92</v>
+      </c>
+      <c r="M9">
         <v>29444</v>
       </c>
-      <c r="O9" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46223</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F10">
         <v>27.781</v>
       </c>
       <c r="G10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I10" s="1">
-        <v>0.63</v>
+        <v>17.502</v>
       </c>
       <c r="J10">
-        <v>17.50203</v>
+        <v>0.64</v>
       </c>
       <c r="K10" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L10" s="1">
-        <v>17.77984</v>
-      </c>
-      <c r="M10" t="s">
-        <v>94</v>
-      </c>
-      <c r="N10">
+        <v>17.78</v>
+      </c>
+      <c r="L10" t="s">
+        <v>93</v>
+      </c>
+      <c r="M10">
         <v>0</v>
       </c>
-      <c r="O10" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46223</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F11">
         <v>48.738</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H11">
-        <v>1.546</v>
+        <v>1.65</v>
       </c>
       <c r="I11" s="1">
-        <v>1.65</v>
+        <v>80.41800000000001</v>
       </c>
       <c r="J11">
-        <v>80.4177</v>
+        <v>1.68</v>
       </c>
       <c r="K11" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L11" s="1">
-        <v>81.87984</v>
-      </c>
-      <c r="M11" t="s">
-        <v>95</v>
-      </c>
-      <c r="N11">
+        <v>81.88</v>
+      </c>
+      <c r="L11" t="s">
+        <v>94</v>
+      </c>
+      <c r="M11">
         <v>188375</v>
       </c>
-      <c r="O11" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46223</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F12">
         <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H12">
-        <v>1.389</v>
+        <v>1.5</v>
       </c>
       <c r="I12" s="1">
-        <v>1.5</v>
+        <v>30</v>
       </c>
       <c r="J12">
-        <v>30</v>
+        <v>1.53</v>
       </c>
       <c r="K12" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L12" s="1">
         <v>30.6</v>
       </c>
-      <c r="M12" t="s">
-        <v>96</v>
-      </c>
-      <c r="N12">
+      <c r="L12" t="s">
+        <v>95</v>
+      </c>
+      <c r="M12">
         <v>55175</v>
       </c>
-      <c r="O12" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>46224</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F13">
         <v>10</v>
       </c>
       <c r="G13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H13">
-        <v>1.389</v>
+        <v>1.5</v>
       </c>
       <c r="I13" s="1">
-        <v>1.5</v>
+        <v>15</v>
       </c>
       <c r="J13">
-        <v>15</v>
+        <v>1.53</v>
       </c>
       <c r="K13" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L13" s="1">
         <v>15.3</v>
       </c>
-      <c r="M13" t="s">
-        <v>97</v>
-      </c>
-      <c r="N13">
+      <c r="L13" t="s">
+        <v>96</v>
+      </c>
+      <c r="M13">
         <v>99000</v>
       </c>
-      <c r="O13" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="N13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>46224</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F14">
         <v>29.984</v>
       </c>
       <c r="G14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I14" s="1">
-        <v>0.63</v>
+        <v>18.89</v>
       </c>
       <c r="J14">
-        <v>18.88992</v>
+        <v>0.64</v>
       </c>
       <c r="K14" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L14" s="1">
-        <v>19.18976</v>
-      </c>
-      <c r="M14" t="s">
-        <v>98</v>
-      </c>
-      <c r="N14">
+        <v>19.19</v>
+      </c>
+      <c r="L14" t="s">
+        <v>97</v>
+      </c>
+      <c r="M14">
         <v>99000</v>
       </c>
-      <c r="O14" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="N14" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>46225</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F15">
         <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H15">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I15" s="1">
-        <v>1.51</v>
+        <v>37.75</v>
       </c>
       <c r="J15">
-        <v>37.75</v>
+        <v>1.54</v>
       </c>
       <c r="K15" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L15" s="1">
         <v>38.5</v>
       </c>
-      <c r="M15" t="s">
-        <v>99</v>
-      </c>
-      <c r="N15">
+      <c r="L15" t="s">
+        <v>98</v>
+      </c>
+      <c r="M15">
         <v>0</v>
       </c>
-      <c r="O15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="N15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
         <v>46226</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F16">
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I16" s="1">
-        <v>0.63</v>
+        <v>12.6</v>
       </c>
       <c r="J16">
-        <v>12.6</v>
+        <v>0.64</v>
       </c>
       <c r="K16" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L16" s="1">
         <v>12.8</v>
       </c>
-      <c r="M16" t="s">
-        <v>100</v>
-      </c>
-      <c r="N16">
+      <c r="L16" t="s">
+        <v>99</v>
+      </c>
+      <c r="M16">
         <v>51017</v>
       </c>
-      <c r="O16" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="N16" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="3">
         <v>46226</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F17">
         <v>39.578</v>
       </c>
       <c r="G17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H17">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I17" s="1">
-        <v>1.51</v>
+        <v>59.763</v>
       </c>
       <c r="J17">
-        <v>59.76278</v>
+        <v>1.54</v>
       </c>
       <c r="K17" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L17" s="1">
-        <v>60.95012</v>
-      </c>
-      <c r="M17" t="s">
-        <v>90</v>
-      </c>
-      <c r="N17">
+        <v>60.95</v>
+      </c>
+      <c r="L17" t="s">
+        <v>89</v>
+      </c>
+      <c r="M17">
         <v>0</v>
       </c>
-      <c r="O17" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="N17" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="3">
         <v>46226</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F18">
         <v>17.338</v>
       </c>
       <c r="G18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H18">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I18" s="1">
-        <v>1.51</v>
+        <v>26.18</v>
       </c>
       <c r="J18">
-        <v>26.18038</v>
+        <v>1.54</v>
       </c>
       <c r="K18" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L18" s="1">
-        <v>26.70052</v>
-      </c>
-      <c r="M18" t="s">
-        <v>101</v>
-      </c>
-      <c r="N18">
+        <v>26.701</v>
+      </c>
+      <c r="L18" t="s">
+        <v>100</v>
+      </c>
+      <c r="M18">
         <v>42900</v>
       </c>
-      <c r="O18" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="N18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="3">
         <v>46226</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F19">
         <v>32.578</v>
       </c>
       <c r="G19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I19" s="1">
-        <v>0.63</v>
+        <v>20.524</v>
       </c>
       <c r="J19">
-        <v>20.52414</v>
+        <v>0.64</v>
       </c>
       <c r="K19" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L19" s="1">
-        <v>20.84992</v>
-      </c>
-      <c r="M19" t="s">
-        <v>102</v>
-      </c>
-      <c r="N19">
+        <v>20.85</v>
+      </c>
+      <c r="L19" t="s">
+        <v>101</v>
+      </c>
+      <c r="M19">
         <v>0</v>
       </c>
-      <c r="O19" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="N19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="3">
         <v>46226</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F20">
         <v>19.984</v>
       </c>
       <c r="G20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I20" s="1">
-        <v>0.63</v>
+        <v>12.59</v>
       </c>
       <c r="J20">
-        <v>12.58992</v>
+        <v>0.64</v>
       </c>
       <c r="K20" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L20" s="1">
-        <v>12.78976</v>
-      </c>
-      <c r="M20" t="s">
-        <v>103</v>
-      </c>
-      <c r="N20">
+        <v>12.79</v>
+      </c>
+      <c r="L20" t="s">
+        <v>102</v>
+      </c>
+      <c r="M20">
         <v>0</v>
       </c>
-      <c r="O20" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="N20" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="3">
         <v>46226</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F21">
         <v>24.984</v>
       </c>
       <c r="G21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I21" s="1">
-        <v>0.63</v>
+        <v>15.74</v>
       </c>
       <c r="J21">
-        <v>15.73992</v>
+        <v>0.64</v>
       </c>
       <c r="K21" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L21" s="1">
-        <v>15.98976</v>
-      </c>
-      <c r="M21" t="s">
-        <v>104</v>
-      </c>
-      <c r="N21">
+        <v>15.99</v>
+      </c>
+      <c r="L21" t="s">
+        <v>103</v>
+      </c>
+      <c r="M21">
         <v>77590</v>
       </c>
-      <c r="O21" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="N21" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="3">
         <v>46226</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F22">
         <v>33.531</v>
       </c>
       <c r="G22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I22" s="1">
-        <v>0.63</v>
+        <v>21.125</v>
       </c>
       <c r="J22">
-        <v>21.12453</v>
+        <v>0.64</v>
       </c>
       <c r="K22" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L22" s="1">
-        <v>21.45984</v>
-      </c>
-      <c r="M22" t="s">
-        <v>105</v>
-      </c>
-      <c r="N22">
+        <v>21.46</v>
+      </c>
+      <c r="L22" t="s">
+        <v>104</v>
+      </c>
+      <c r="M22">
         <v>43150</v>
       </c>
-      <c r="O22" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="N22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="3">
         <v>46227</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F23">
         <v>27.594</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I23" s="1">
-        <v>0.63</v>
+        <v>17.384</v>
       </c>
       <c r="J23">
-        <v>17.38422</v>
+        <v>0.64</v>
       </c>
       <c r="K23" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L23" s="1">
-        <v>17.66016</v>
-      </c>
-      <c r="M23" t="s">
-        <v>106</v>
-      </c>
-      <c r="N23">
+        <v>17.66</v>
+      </c>
+      <c r="L23" t="s">
+        <v>105</v>
+      </c>
+      <c r="M23">
         <v>256</v>
       </c>
-      <c r="O23" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+      <c r="N23" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="3">
         <v>46227</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F24">
         <v>18.047</v>
       </c>
       <c r="G24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I24" s="1">
-        <v>0.63</v>
+        <v>11.37</v>
       </c>
       <c r="J24">
-        <v>11.36961</v>
+        <v>0.64</v>
       </c>
       <c r="K24" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L24" s="1">
-        <v>11.55008</v>
-      </c>
-      <c r="M24" t="s">
-        <v>107</v>
-      </c>
-      <c r="N24">
+        <v>11.55</v>
+      </c>
+      <c r="L24" t="s">
+        <v>106</v>
+      </c>
+      <c r="M24">
         <v>0</v>
       </c>
-      <c r="O24" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="N24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="3">
         <v>46227</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F25">
         <v>33.883</v>
       </c>
       <c r="G25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H25">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I25" s="1">
-        <v>1.51</v>
+        <v>51.163</v>
       </c>
       <c r="J25">
-        <v>51.16333</v>
+        <v>1.54</v>
       </c>
       <c r="K25" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L25" s="1">
-        <v>52.17982</v>
-      </c>
-      <c r="M25" t="s">
-        <v>108</v>
-      </c>
-      <c r="N25">
+        <v>52.18</v>
+      </c>
+      <c r="L25" t="s">
+        <v>107</v>
+      </c>
+      <c r="M25">
         <v>0</v>
       </c>
-      <c r="O25" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="N25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="3">
         <v>46227</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F26">
         <v>32.328</v>
       </c>
       <c r="G26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I26" s="1">
-        <v>0.63</v>
+        <v>20.367</v>
       </c>
       <c r="J26">
-        <v>20.36664</v>
+        <v>0.64</v>
       </c>
       <c r="K26" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L26" s="1">
-        <v>20.68992</v>
-      </c>
-      <c r="M26" t="s">
-        <v>109</v>
-      </c>
-      <c r="N26">
+        <v>20.69</v>
+      </c>
+      <c r="L26" t="s">
+        <v>108</v>
+      </c>
+      <c r="M26">
         <v>0</v>
       </c>
-      <c r="O26" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+      <c r="N26" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="3">
         <v>46227</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F27">
         <v>19.045</v>
       </c>
       <c r="G27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="I27" s="1">
-        <v>0.65</v>
+        <v>12.379</v>
       </c>
       <c r="J27">
-        <v>12.37925</v>
+        <v>0.66</v>
       </c>
       <c r="K27" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="L27" s="1">
-        <v>12.5697</v>
-      </c>
-      <c r="M27" t="s">
-        <v>110</v>
-      </c>
-      <c r="N27">
+        <v>12.57</v>
+      </c>
+      <c r="L27" t="s">
+        <v>109</v>
+      </c>
+      <c r="M27">
         <v>4350</v>
       </c>
-      <c r="O27" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+      <c r="N27" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="3">
         <v>46230</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F28">
         <v>54.971</v>
       </c>
       <c r="G28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H28">
-        <v>1.619</v>
+        <v>1.72</v>
       </c>
       <c r="I28" s="1">
-        <v>1.72</v>
+        <v>94.55</v>
       </c>
       <c r="J28">
-        <v>94.55012000000001</v>
+        <v>1.75</v>
       </c>
       <c r="K28" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L28" s="1">
-        <v>96.19925000000001</v>
-      </c>
-      <c r="M28" t="s">
-        <v>111</v>
-      </c>
-      <c r="N28">
+        <v>96.199</v>
+      </c>
+      <c r="L28" t="s">
+        <v>110</v>
+      </c>
+      <c r="M28">
         <v>0</v>
       </c>
-      <c r="O28" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="N28" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="3">
         <v>46230</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F29">
         <v>10</v>
       </c>
       <c r="G29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H29">
-        <v>1.401</v>
+        <v>1.53</v>
       </c>
       <c r="I29" s="1">
-        <v>1.53</v>
+        <v>15.3</v>
       </c>
       <c r="J29">
-        <v>15.3</v>
+        <v>1.56</v>
       </c>
       <c r="K29" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L29" s="1">
         <v>15.6</v>
       </c>
-      <c r="M29" t="s">
-        <v>112</v>
-      </c>
-      <c r="N29">
+      <c r="L29" t="s">
+        <v>111</v>
+      </c>
+      <c r="M29">
         <v>77809</v>
       </c>
-      <c r="O29" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="N29" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="3">
         <v>46230</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F30">
         <v>32.344</v>
       </c>
       <c r="G30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I30" s="1">
-        <v>0.63</v>
+        <v>20.377</v>
       </c>
       <c r="J30">
-        <v>20.37672</v>
+        <v>0.64</v>
       </c>
       <c r="K30" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L30" s="1">
-        <v>20.70016</v>
-      </c>
-      <c r="M30" t="s">
-        <v>113</v>
-      </c>
-      <c r="N30">
+        <v>20.7</v>
+      </c>
+      <c r="L30" t="s">
+        <v>112</v>
+      </c>
+      <c r="M30">
         <v>0</v>
       </c>
-      <c r="O30" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="N30" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="3">
         <v>46230</v>
       </c>
       <c r="B31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E31" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F31">
         <v>32.237</v>
       </c>
       <c r="G31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H31">
-        <v>1.401</v>
+        <v>1.53</v>
       </c>
       <c r="I31" s="1">
-        <v>1.53</v>
+        <v>49.323</v>
       </c>
       <c r="J31">
-        <v>49.32261</v>
+        <v>1.56</v>
       </c>
       <c r="K31" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L31" s="1">
-        <v>50.28972</v>
-      </c>
-      <c r="M31" t="s">
-        <v>114</v>
-      </c>
-      <c r="N31">
+        <v>50.29</v>
+      </c>
+      <c r="L31" t="s">
+        <v>113</v>
+      </c>
+      <c r="M31">
         <v>42035</v>
       </c>
-      <c r="O31" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+      <c r="N31" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="3">
         <v>46231</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F32">
         <v>25</v>
       </c>
       <c r="G32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H32">
-        <v>1.441</v>
+        <v>1.53</v>
       </c>
       <c r="I32" s="1">
-        <v>1.53</v>
+        <v>38.25</v>
       </c>
       <c r="J32">
-        <v>38.25</v>
+        <v>1.56</v>
       </c>
       <c r="K32" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L32" s="1">
         <v>39</v>
       </c>
-      <c r="M32" t="s">
-        <v>115</v>
-      </c>
-      <c r="N32">
+      <c r="L32" t="s">
+        <v>114</v>
+      </c>
+      <c r="M32">
         <v>476750</v>
       </c>
-      <c r="O32" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+      <c r="N32" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="3">
         <v>46231</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F33">
         <v>28.828</v>
       </c>
       <c r="G33" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I33" s="1">
-        <v>0.63</v>
+        <v>18.162</v>
       </c>
       <c r="J33">
-        <v>18.16164</v>
+        <v>0.64</v>
       </c>
       <c r="K33" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L33" s="1">
-        <v>18.44992</v>
-      </c>
-      <c r="M33" t="s">
-        <v>116</v>
-      </c>
-      <c r="N33">
+        <v>18.45</v>
+      </c>
+      <c r="L33" t="s">
+        <v>115</v>
+      </c>
+      <c r="M33">
         <v>69975</v>
       </c>
-      <c r="O33" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+      <c r="N33" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="3">
         <v>46231</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F34">
         <v>20.011</v>
       </c>
       <c r="G34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H34">
-        <v>1.653</v>
+        <v>1.72</v>
       </c>
       <c r="I34" s="1">
-        <v>1.72</v>
+        <v>34.419</v>
       </c>
       <c r="J34">
-        <v>34.41892</v>
+        <v>1.75</v>
       </c>
       <c r="K34" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L34" s="1">
-        <v>35.01925</v>
-      </c>
-      <c r="M34" t="s">
-        <v>117</v>
-      </c>
-      <c r="N34">
+        <v>35.019</v>
+      </c>
+      <c r="L34" t="s">
+        <v>116</v>
+      </c>
+      <c r="M34">
         <v>0</v>
       </c>
-      <c r="O34" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
+      <c r="N34" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="3">
         <v>46231</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E35" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F35">
         <v>36.783</v>
       </c>
       <c r="G35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H35">
-        <v>1.653</v>
+        <v>1.72</v>
       </c>
       <c r="I35" s="1">
-        <v>1.72</v>
+        <v>63.267</v>
       </c>
       <c r="J35">
-        <v>63.26676</v>
+        <v>1.75</v>
       </c>
       <c r="K35" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L35" s="1">
-        <v>64.37025</v>
-      </c>
-      <c r="M35" t="s">
-        <v>118</v>
-      </c>
-      <c r="N35">
+        <v>64.37</v>
+      </c>
+      <c r="L35" t="s">
+        <v>117</v>
+      </c>
+      <c r="M35">
         <v>188700</v>
       </c>
-      <c r="O35" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="N35" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="3">
         <v>46232</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F36">
         <v>29.161</v>
       </c>
       <c r="G36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H36">
-        <v>1.449</v>
+        <v>1.52</v>
       </c>
       <c r="I36" s="1">
-        <v>1.52</v>
+        <v>44.325</v>
       </c>
       <c r="J36">
-        <v>44.32472</v>
+        <v>1.55</v>
       </c>
       <c r="K36" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L36" s="1">
-        <v>45.19955</v>
-      </c>
-      <c r="M36" t="s">
-        <v>119</v>
-      </c>
-      <c r="N36">
+        <v>45.2</v>
+      </c>
+      <c r="L36" t="s">
+        <v>118</v>
+      </c>
+      <c r="M36">
         <v>55321</v>
       </c>
-      <c r="O36" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
+      <c r="N36" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" s="3">
         <v>46232</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F37">
         <v>53.968</v>
       </c>
       <c r="G37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H37">
-        <v>1.449</v>
+        <v>1.52</v>
       </c>
       <c r="I37" s="1">
-        <v>1.52</v>
+        <v>82.03100000000001</v>
       </c>
       <c r="J37">
-        <v>82.03136000000001</v>
+        <v>1.55</v>
       </c>
       <c r="K37" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L37" s="1">
-        <v>83.6504</v>
-      </c>
-      <c r="M37" t="s">
-        <v>120</v>
-      </c>
-      <c r="N37">
+        <v>83.65000000000001</v>
+      </c>
+      <c r="L37" t="s">
+        <v>119</v>
+      </c>
+      <c r="M37">
         <v>0</v>
       </c>
-      <c r="O37" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+      <c r="N37" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="3">
         <v>46232</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F38">
         <v>20</v>
       </c>
       <c r="G38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H38">
-        <v>1.449</v>
+        <v>1.52</v>
       </c>
       <c r="I38" s="1">
-        <v>1.52</v>
+        <v>30.4</v>
       </c>
       <c r="J38">
-        <v>30.4</v>
+        <v>1.55</v>
       </c>
       <c r="K38" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L38" s="1">
         <v>31</v>
       </c>
-      <c r="M38" t="s">
-        <v>121</v>
-      </c>
-      <c r="N38">
+      <c r="L38" t="s">
+        <v>120</v>
+      </c>
+      <c r="M38">
         <v>0</v>
       </c>
-      <c r="O38" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+      <c r="N38" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" s="3">
         <v>46232</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D39" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F39">
         <v>31.453</v>
       </c>
       <c r="G39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I39" s="1">
-        <v>0.63</v>
+        <v>19.815</v>
       </c>
       <c r="J39">
-        <v>19.81539</v>
+        <v>0.64</v>
       </c>
       <c r="K39" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L39" s="1">
-        <v>20.12992</v>
-      </c>
-      <c r="M39" t="s">
-        <v>122</v>
-      </c>
-      <c r="N39">
+        <v>20.13</v>
+      </c>
+      <c r="L39" t="s">
+        <v>121</v>
+      </c>
+      <c r="M39">
         <v>99353</v>
       </c>
-      <c r="O39" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="N39" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" s="3">
         <v>46232</v>
       </c>
       <c r="B40" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F40">
         <v>26.906</v>
       </c>
       <c r="G40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I40" s="1">
-        <v>0.63</v>
+        <v>16.951</v>
       </c>
       <c r="J40">
-        <v>16.95078</v>
+        <v>0.64</v>
       </c>
       <c r="K40" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L40" s="1">
-        <v>17.21984</v>
-      </c>
-      <c r="M40" t="s">
-        <v>123</v>
-      </c>
-      <c r="N40">
+        <v>17.22</v>
+      </c>
+      <c r="L40" t="s">
+        <v>122</v>
+      </c>
+      <c r="M40">
         <v>38940</v>
       </c>
-      <c r="O40" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15">
+      <c r="N40" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" s="3">
         <v>46232</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F41">
         <v>49.983</v>
       </c>
       <c r="G41" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H41">
-        <v>1.674</v>
+        <v>1.72</v>
       </c>
       <c r="I41" s="1">
-        <v>1.72</v>
+        <v>85.971</v>
       </c>
       <c r="J41">
-        <v>85.97076</v>
+        <v>1.75</v>
       </c>
       <c r="K41" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L41" s="1">
-        <v>87.47024999999999</v>
-      </c>
-      <c r="M41" t="s">
-        <v>124</v>
-      </c>
-      <c r="N41">
+        <v>87.47</v>
+      </c>
+      <c r="L41" t="s">
+        <v>123</v>
+      </c>
+      <c r="M41">
         <v>0</v>
       </c>
-      <c r="O41" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
+      <c r="N41" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" s="3">
         <v>46233</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E42" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F42">
         <v>31.641</v>
       </c>
       <c r="G42" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I42" s="1">
-        <v>0.63</v>
+        <v>19.934</v>
       </c>
       <c r="J42">
-        <v>19.93383</v>
+        <v>0.64</v>
       </c>
       <c r="K42" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L42" s="1">
-        <v>20.25024</v>
-      </c>
-      <c r="M42" t="s">
-        <v>125</v>
-      </c>
-      <c r="N42">
+        <v>20.25</v>
+      </c>
+      <c r="L42" t="s">
+        <v>124</v>
+      </c>
+      <c r="M42">
         <v>77268</v>
       </c>
-      <c r="O42" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
+      <c r="N42" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" s="3">
         <v>46233</v>
       </c>
       <c r="B43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F43">
         <v>41.239</v>
       </c>
       <c r="G43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H43">
-        <v>1.449</v>
+        <v>1.52</v>
       </c>
       <c r="I43" s="1">
-        <v>1.52</v>
+        <v>62.683</v>
       </c>
       <c r="J43">
-        <v>62.68328</v>
+        <v>1.55</v>
       </c>
       <c r="K43" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L43" s="1">
-        <v>63.92045</v>
-      </c>
-      <c r="M43" t="s">
-        <v>125</v>
-      </c>
-      <c r="N43">
+        <v>63.92</v>
+      </c>
+      <c r="L43" t="s">
+        <v>124</v>
+      </c>
+      <c r="M43">
         <v>0</v>
       </c>
-      <c r="O43" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+      <c r="N43" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" s="3">
         <v>46233</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E44" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F44">
         <v>13.252</v>
       </c>
       <c r="G44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H44">
-        <v>1.449</v>
+        <v>1.52</v>
       </c>
       <c r="I44" s="1">
-        <v>1.52</v>
+        <v>20.143</v>
       </c>
       <c r="J44">
-        <v>20.14304</v>
+        <v>1.55</v>
       </c>
       <c r="K44" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L44" s="1">
-        <v>20.5406</v>
-      </c>
-      <c r="M44" t="s">
-        <v>126</v>
-      </c>
-      <c r="N44">
+        <v>20.541</v>
+      </c>
+      <c r="L44" t="s">
+        <v>125</v>
+      </c>
+      <c r="M44">
         <v>0</v>
       </c>
-      <c r="O44" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15">
+      <c r="N44" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" s="3">
         <v>46234</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F45">
         <v>32.484</v>
       </c>
       <c r="G45" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I45" s="1">
-        <v>0.63</v>
+        <v>20.465</v>
       </c>
       <c r="J45">
-        <v>20.46492</v>
+        <v>0.64</v>
       </c>
       <c r="K45" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L45" s="1">
-        <v>20.78976</v>
-      </c>
-      <c r="M45" t="s">
-        <v>127</v>
-      </c>
-      <c r="N45">
+        <v>20.79</v>
+      </c>
+      <c r="L45" t="s">
+        <v>126</v>
+      </c>
+      <c r="M45">
         <v>44100</v>
       </c>
-      <c r="O45" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="N45" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" s="3">
         <v>46234</v>
       </c>
       <c r="B46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E46" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F46">
         <v>30</v>
       </c>
       <c r="G46" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H46">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I46" s="1">
-        <v>1.74</v>
+        <v>52.2</v>
       </c>
       <c r="J46">
-        <v>52.2</v>
+        <v>1.77</v>
       </c>
       <c r="K46" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L46" s="1">
         <v>53.1</v>
       </c>
-      <c r="M46" t="s">
-        <v>128</v>
-      </c>
-      <c r="N46">
+      <c r="L46" t="s">
+        <v>127</v>
+      </c>
+      <c r="M46">
         <v>188800</v>
       </c>
-      <c r="O46" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="N46" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" s="3">
         <v>46234</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F47">
         <v>34.26</v>
       </c>
       <c r="G47" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H47">
-        <v>1.689</v>
+        <v>1.74</v>
       </c>
       <c r="I47" s="1">
-        <v>1.74</v>
+        <v>59.612</v>
       </c>
       <c r="J47">
-        <v>59.6124</v>
+        <v>1.77</v>
       </c>
       <c r="K47" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L47" s="1">
-        <v>60.6402</v>
-      </c>
-      <c r="M47" t="s">
-        <v>129</v>
-      </c>
-      <c r="N47">
+        <v>60.64</v>
+      </c>
+      <c r="L47" t="s">
+        <v>128</v>
+      </c>
+      <c r="M47">
         <v>0</v>
       </c>
-      <c r="O47" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="N47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" s="3">
         <v>46234</v>
       </c>
       <c r="B48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F48">
         <v>32.303</v>
       </c>
       <c r="G48" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H48">
-        <v>1.459</v>
+        <v>1.52</v>
       </c>
       <c r="I48" s="1">
-        <v>1.52</v>
+        <v>49.101</v>
       </c>
       <c r="J48">
-        <v>49.10056</v>
+        <v>1.55</v>
       </c>
       <c r="K48" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L48" s="1">
-        <v>50.06965</v>
-      </c>
-      <c r="M48" t="s">
-        <v>130</v>
-      </c>
-      <c r="N48">
+        <v>50.07</v>
+      </c>
+      <c r="L48" t="s">
+        <v>129</v>
+      </c>
+      <c r="M48">
         <v>42428</v>
       </c>
-      <c r="O48" t="s">
-        <v>177</v>
+      <c r="N48" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -3254,87 +3107,87 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="C52" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="D52" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>182</v>
-      </c>
       <c r="E52" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B53" s="7">
         <v>533.202</v>
       </c>
-      <c r="C53" s="7">
+      <c r="C53" s="8">
         <v>20</v>
       </c>
       <c r="D53" s="8">
-        <v>1.507409</v>
-      </c>
-      <c r="E53" s="7">
-        <v>803.75</v>
-      </c>
-      <c r="F53" s="7">
-        <v>819.75</v>
+        <v>1.507</v>
+      </c>
+      <c r="E53" s="8">
+        <v>803.753</v>
+      </c>
+      <c r="F53" s="8">
+        <v>819.752</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B54" s="7">
         <v>489.512</v>
       </c>
-      <c r="C54" s="7">
+      <c r="C54" s="8">
         <v>18</v>
       </c>
       <c r="D54" s="8">
-        <v>0.63037</v>
-      </c>
-      <c r="E54" s="7">
-        <v>308.57</v>
-      </c>
-      <c r="F54" s="7">
+        <v>0.63</v>
+      </c>
+      <c r="E54" s="8">
+        <v>308.575</v>
+      </c>
+      <c r="F54" s="8">
         <v>313.47</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B55" s="7">
         <v>411.942</v>
       </c>
-      <c r="C55" s="7">
+      <c r="C55" s="8">
         <v>9</v>
       </c>
       <c r="D55" s="8">
-        <v>1.674872</v>
-      </c>
-      <c r="E55" s="7">
+        <v>1.675</v>
+      </c>
+      <c r="E55" s="8">
         <v>689.95</v>
       </c>
-      <c r="F55" s="7">
-        <v>702.3099999999999</v>
+      <c r="F55" s="8">
+        <v>702.308</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B56" s="10">
         <v>1434.656</v>
@@ -3344,7 +3197,7 @@
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="10">
-        <v>1802.27</v>
+        <v>1802.278</v>
       </c>
       <c r="F56" s="10">
         <v>1835.53</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 1 - АВТОПАРК/ОБЩИНА ВАРНА % 1 - АВТОПАРК.xlsx
@@ -1011,10 +1011,10 @@
         <v>85</v>
       </c>
       <c r="H2" s="1">
-        <v>1.409</v>
+        <v>1.53</v>
       </c>
       <c r="I2" s="1">
-        <v>24.784</v>
+        <v>26.913</v>
       </c>
       <c r="J2" s="1">
         <v>1.56</v>
@@ -1055,10 +1055,10 @@
         <v>85</v>
       </c>
       <c r="H3" s="1">
-        <v>1.409</v>
+        <v>1.53</v>
       </c>
       <c r="I3" s="1">
-        <v>14.09</v>
+        <v>15.3</v>
       </c>
       <c r="J3" s="1">
         <v>1.56</v>
@@ -1099,10 +1099,10 @@
         <v>85</v>
       </c>
       <c r="H4" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I4" s="1">
-        <v>18.147</v>
+        <v>11.914</v>
       </c>
       <c r="J4" s="1">
         <v>0.66</v>
@@ -1143,10 +1143,10 @@
         <v>85</v>
       </c>
       <c r="H5" s="1">
-        <v>1.409</v>
+        <v>1.53</v>
       </c>
       <c r="I5" s="1">
-        <v>14.09</v>
+        <v>15.3</v>
       </c>
       <c r="J5" s="1">
         <v>1.56</v>
@@ -1187,10 +1187,10 @@
         <v>85</v>
       </c>
       <c r="H6" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I6" s="1">
-        <v>27.552</v>
+        <v>18.09</v>
       </c>
       <c r="J6" s="1">
         <v>0.66</v>
@@ -1231,10 +1231,10 @@
         <v>85</v>
       </c>
       <c r="H7" s="1">
-        <v>1.409</v>
+        <v>1.53</v>
       </c>
       <c r="I7" s="1">
-        <v>35.225</v>
+        <v>38.25</v>
       </c>
       <c r="J7" s="1">
         <v>1.56</v>
@@ -1275,10 +1275,10 @@
         <v>85</v>
       </c>
       <c r="H8" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I8" s="1">
-        <v>26.69</v>
+        <v>17.524</v>
       </c>
       <c r="J8" s="1">
         <v>0.66</v>
@@ -1319,10 +1319,10 @@
         <v>85</v>
       </c>
       <c r="H9" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I9" s="1">
-        <v>80.563</v>
+        <v>85.03100000000001</v>
       </c>
       <c r="J9" s="1">
         <v>1.8</v>
@@ -1363,10 +1363,10 @@
         <v>85</v>
       </c>
       <c r="H10" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I10" s="1">
-        <v>27.304</v>
+        <v>17.927</v>
       </c>
       <c r="J10" s="1">
         <v>0.66</v>
@@ -1407,10 +1407,10 @@
         <v>85</v>
       </c>
       <c r="H11" s="1">
-        <v>1.429</v>
+        <v>1.53</v>
       </c>
       <c r="I11" s="1">
-        <v>14.29</v>
+        <v>15.3</v>
       </c>
       <c r="J11" s="1">
         <v>1.56</v>
@@ -1451,10 +1451,10 @@
         <v>85</v>
       </c>
       <c r="H12" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I12" s="1">
-        <v>29.7</v>
+        <v>19.5</v>
       </c>
       <c r="J12" s="1">
         <v>0.66</v>
@@ -1495,10 +1495,10 @@
         <v>85</v>
       </c>
       <c r="H13" s="1">
-        <v>1.677</v>
+        <v>1.79</v>
       </c>
       <c r="I13" s="1">
-        <v>75.012</v>
+        <v>80.06699999999999</v>
       </c>
       <c r="J13" s="1">
         <v>1.82</v>
@@ -1539,10 +1539,10 @@
         <v>85</v>
       </c>
       <c r="H14" s="1">
-        <v>1.429</v>
+        <v>1.53</v>
       </c>
       <c r="I14" s="1">
-        <v>45.271</v>
+        <v>48.47</v>
       </c>
       <c r="J14" s="1">
         <v>1.56</v>
@@ -1583,10 +1583,10 @@
         <v>85</v>
       </c>
       <c r="H15" s="1">
-        <v>1.429</v>
+        <v>1.53</v>
       </c>
       <c r="I15" s="1">
-        <v>71.45</v>
+        <v>76.5</v>
       </c>
       <c r="J15" s="1">
         <v>1.56</v>
@@ -1627,10 +1627,10 @@
         <v>85</v>
       </c>
       <c r="H16" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I16" s="1">
-        <v>35.62</v>
+        <v>23.387</v>
       </c>
       <c r="J16" s="1">
         <v>0.66</v>
@@ -1671,10 +1671,10 @@
         <v>85</v>
       </c>
       <c r="H17" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I17" s="1">
-        <v>33.957</v>
+        <v>22.295</v>
       </c>
       <c r="J17" s="1">
         <v>0.66</v>
@@ -1715,10 +1715,10 @@
         <v>85</v>
       </c>
       <c r="H18" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I18" s="1">
-        <v>30.779</v>
+        <v>20.208</v>
       </c>
       <c r="J18" s="1">
         <v>0.66</v>
@@ -1759,10 +1759,10 @@
         <v>85</v>
       </c>
       <c r="H19" s="1">
-        <v>1.429</v>
+        <v>1.54</v>
       </c>
       <c r="I19" s="1">
-        <v>35.725</v>
+        <v>38.5</v>
       </c>
       <c r="J19" s="1">
         <v>1.57</v>
@@ -1803,10 +1803,10 @@
         <v>85</v>
       </c>
       <c r="H20" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I20" s="1">
-        <v>26.869</v>
+        <v>17.641</v>
       </c>
       <c r="J20" s="1">
         <v>0.66</v>
@@ -1847,10 +1847,10 @@
         <v>85</v>
       </c>
       <c r="H21" s="1">
-        <v>1.429</v>
+        <v>1.54</v>
       </c>
       <c r="I21" s="1">
-        <v>47.386</v>
+        <v>51.066</v>
       </c>
       <c r="J21" s="1">
         <v>1.57</v>
@@ -1891,10 +1891,10 @@
         <v>85</v>
       </c>
       <c r="H22" s="1">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="I22" s="1">
-        <v>51.257</v>
+        <v>54.618</v>
       </c>
       <c r="J22" s="1">
         <v>1.85</v>
@@ -1935,10 +1935,10 @@
         <v>85</v>
       </c>
       <c r="H23" s="1">
-        <v>1.439</v>
+        <v>1.54</v>
       </c>
       <c r="I23" s="1">
-        <v>36.047</v>
+        <v>38.577</v>
       </c>
       <c r="J23" s="1">
         <v>1.57</v>
@@ -1979,10 +1979,10 @@
         <v>85</v>
       </c>
       <c r="H24" s="1">
-        <v>1.439</v>
+        <v>1.54</v>
       </c>
       <c r="I24" s="1">
-        <v>60.136</v>
+        <v>64.357</v>
       </c>
       <c r="J24" s="1">
         <v>1.57</v>
@@ -2023,10 +2023,10 @@
         <v>85</v>
       </c>
       <c r="H25" s="1">
-        <v>1.439</v>
+        <v>1.54</v>
       </c>
       <c r="I25" s="1">
-        <v>46.638</v>
+        <v>49.911</v>
       </c>
       <c r="J25" s="1">
         <v>1.57</v>
@@ -2067,10 +2067,10 @@
         <v>85</v>
       </c>
       <c r="H26" s="1">
-        <v>1.439</v>
+        <v>1.54</v>
       </c>
       <c r="I26" s="1">
-        <v>67.532</v>
+        <v>72.27200000000001</v>
       </c>
       <c r="J26" s="1">
         <v>1.57</v>
@@ -2111,10 +2111,10 @@
         <v>85</v>
       </c>
       <c r="H27" s="1">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="I27" s="1">
-        <v>14.59</v>
+        <v>15.5</v>
       </c>
       <c r="J27" s="1">
         <v>1.58</v>
@@ -2155,10 +2155,10 @@
         <v>85</v>
       </c>
       <c r="H28" s="1">
-        <v>1.459</v>
+        <v>1.56</v>
       </c>
       <c r="I28" s="1">
-        <v>55.063</v>
+        <v>58.874</v>
       </c>
       <c r="J28" s="1">
         <v>1.59</v>
@@ -2199,10 +2199,10 @@
         <v>85</v>
       </c>
       <c r="H29" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I29" s="1">
-        <v>25.166</v>
+        <v>16.523</v>
       </c>
       <c r="J29" s="1">
         <v>0.66</v>
@@ -2243,10 +2243,10 @@
         <v>85</v>
       </c>
       <c r="H30" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I30" s="1">
-        <v>26.463</v>
+        <v>17.374</v>
       </c>
       <c r="J30" s="1">
         <v>0.66</v>
@@ -2287,10 +2287,10 @@
         <v>85</v>
       </c>
       <c r="H31" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I31" s="1">
-        <v>85.95</v>
+        <v>91</v>
       </c>
       <c r="J31" s="1">
         <v>1.85</v>
@@ -2331,10 +2331,10 @@
         <v>85</v>
       </c>
       <c r="H32" s="1">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="I32" s="1">
-        <v>27.809</v>
+        <v>29.543</v>
       </c>
       <c r="J32" s="1">
         <v>1.58</v>
@@ -2375,10 +2375,10 @@
         <v>85</v>
       </c>
       <c r="H33" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I33" s="1">
-        <v>19.78</v>
+        <v>12.987</v>
       </c>
       <c r="J33" s="1">
         <v>0.66</v>
@@ -2419,10 +2419,10 @@
         <v>85</v>
       </c>
       <c r="H34" s="1">
-        <v>1.459</v>
+        <v>1.56</v>
       </c>
       <c r="I34" s="1">
-        <v>14.575</v>
+        <v>15.584</v>
       </c>
       <c r="J34" s="1">
         <v>1.59</v>
@@ -2463,10 +2463,10 @@
         <v>85</v>
       </c>
       <c r="H35" s="1">
-        <v>1.459</v>
+        <v>1.56</v>
       </c>
       <c r="I35" s="1">
-        <v>49.095</v>
+        <v>52.494</v>
       </c>
       <c r="J35" s="1">
         <v>1.59</v>
@@ -2507,10 +2507,10 @@
         <v>85</v>
       </c>
       <c r="H36" s="1">
-        <v>1.459</v>
+        <v>1.56</v>
       </c>
       <c r="I36" s="1">
-        <v>58.36</v>
+        <v>62.4</v>
       </c>
       <c r="J36" s="1">
         <v>1.59</v>
@@ -2551,10 +2551,10 @@
         <v>85</v>
       </c>
       <c r="H37" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I37" s="1">
-        <v>51.57</v>
+        <v>54.6</v>
       </c>
       <c r="J37" s="1">
         <v>1.85</v>
@@ -2595,10 +2595,10 @@
         <v>85</v>
       </c>
       <c r="H38" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I38" s="1">
-        <v>42.975</v>
+        <v>45.5</v>
       </c>
       <c r="J38" s="1">
         <v>1.85</v>
@@ -2639,10 +2639,10 @@
         <v>85</v>
       </c>
       <c r="H39" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I39" s="1">
-        <v>66.577</v>
+        <v>70.489</v>
       </c>
       <c r="J39" s="1">
         <v>1.85</v>
@@ -2683,10 +2683,10 @@
         <v>85</v>
       </c>
       <c r="H40" s="1">
-        <v>1.459</v>
+        <v>1.57</v>
       </c>
       <c r="I40" s="1">
-        <v>14.59</v>
+        <v>15.7</v>
       </c>
       <c r="J40" s="1">
         <v>1.6</v>
@@ -2727,10 +2727,10 @@
         <v>85</v>
       </c>
       <c r="H41" s="1">
-        <v>1.459</v>
+        <v>1.58</v>
       </c>
       <c r="I41" s="1">
-        <v>19.872</v>
+        <v>21.52</v>
       </c>
       <c r="J41" s="1">
         <v>1.61</v>
@@ -2771,10 +2771,10 @@
         <v>85</v>
       </c>
       <c r="H42" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I42" s="1">
-        <v>103.209</v>
+        <v>108.672</v>
       </c>
       <c r="J42" s="1">
         <v>1.84</v>
@@ -2815,10 +2815,10 @@
         <v>85</v>
       </c>
       <c r="H43" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I43" s="1">
-        <v>27.116</v>
+        <v>17.804</v>
       </c>
       <c r="J43" s="1">
         <v>0.66</v>
@@ -2877,10 +2877,10 @@
         <v>21</v>
       </c>
       <c r="D48" s="9">
-        <v>1.4392</v>
+        <v>1.54379</v>
       </c>
       <c r="E48" s="7">
-        <v>766.62</v>
+        <v>822.33</v>
       </c>
       <c r="F48" s="7">
         <v>838.3099999999999</v>
@@ -2897,10 +2897,10 @@
         <v>13</v>
       </c>
       <c r="D49" s="9">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="E49" s="7">
-        <v>355.14</v>
+        <v>233.17</v>
       </c>
       <c r="F49" s="7">
         <v>236.76</v>
@@ -2917,10 +2917,10 @@
         <v>8</v>
       </c>
       <c r="D50" s="9">
-        <v>1.70606</v>
+        <v>1.8067</v>
       </c>
       <c r="E50" s="7">
-        <v>557.11</v>
+        <v>589.98</v>
       </c>
       <c r="F50" s="7">
         <v>599.77</v>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D51" s="9"/>
       <c r="E51" s="11">
-        <v>1678.87</v>
+        <v>1645.48</v>
       </c>
       <c r="F51" s="11">
         <v>1674.84</v>
